--- a/outputs/ICS-2026-计算传播学精选.xlsx
+++ b/outputs/ICS-2026-计算传播学精选.xlsx
@@ -1,20 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="筛选说明" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="明确纳入" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="待全文确认" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="完整筛选记录" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="筛选说明" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="明确纳入" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="待全文确认" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="完整筛选记录" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'明确纳入'!$A$1:$S$32</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'待全文确认'!$A$1:$S$12</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'明确纳入'!$A$1:$S$36</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'待全文确认'!$A$1:$S$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'完整筛选记录'!$A$1:$X$160</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -521,7 +521,7 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>31</v>
+        <v>35</v>
       </c>
     </row>
     <row r="4">
@@ -531,7 +531,7 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -541,7 +541,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>117</v>
+        <v>124</v>
       </c>
     </row>
     <row r="6">
@@ -600,7 +600,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>本轮依据原工作簿的标题与摘要筛选；未取得全文，不代表已经精读。</t>
+          <t>先依据标题与摘要筛选；11 篇待定论文另经 Taylor &amp; Francis 出版方网页人工核查方法。网页核查不等于已归档 PDF 或完成精读。</t>
         </is>
       </c>
     </row>
@@ -627,7 +627,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S32"/>
+  <dimension ref="A1:S36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -804,7 +804,7 @@
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>议题符合，且摘要明确显示：主题建模、文本社群检测与时间比较。</t>
+          <t>议题符合，且方法证据显示：主题建模、文本社群检测与时间比较。</t>
         </is>
       </c>
       <c r="M2" s="2" t="inlineStr">
@@ -899,7 +899,7 @@
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>议题符合，且摘要明确显示：Meta 广告库全集、投放支出与受众定向数据。</t>
+          <t>议题符合，且方法证据显示：Meta 广告库全集、投放支出与受众定向数据。</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr">
@@ -994,7 +994,7 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>议题符合，且摘要明确显示：Facebook 捐赠数字痕迹，并含预注册题序实验。</t>
+          <t>议题符合，且方法证据显示：Facebook 捐赠数字痕迹，并含预注册题序实验。</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>议题符合，且摘要明确显示：LLM 分类、动态提及网络与图机器学习。</t>
+          <t>议题符合，且方法证据显示：LLM 分类、动态提及网络与图机器学习。</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -1130,11 +1130,11 @@
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>26</v>
-      </c>
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t>黄色</t>
+        <v>23</v>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
@@ -1144,72 +1144,64 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>摘要明确</t>
+          <t>出版方全文方法明确</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>The echoes from social media: modeling how filter bubbles and network structure shape echo chamber emergence</t>
+          <t>Did you make this for me? A two-country study on individuals’ perceptions of tailoring in online political ads</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>社交媒体的回声：研究信息茧房和网络结构如何影响回音室效应的形成</t>
+          <t>这是你为我准备的吗？一项关于个人对在线政治广告中定制化内容感知的跨国研究</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>Cristina Chueca Del Cerro</t>
+          <t>Christina Gahn, J.G. Vrielink, Sanne Kruikemeier</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>计算传播学</t>
+          <t>量化分析</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>社交媒体；过滤气泡；回音室；仿真模拟；意见动态</t>
+          <t>政治广告；定制化；在线广告</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>计算模拟</t>
+          <t>数据捐赠＋数字痕迹</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>议题符合，且摘要明确显示：基于代理的社会模拟，操控网络同质性与选择性暴露。</t>
+          <t>议题符合，且方法证据显示：移动经验抽样与真实政治广告截图的数据捐赠。</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>通过agent-based模型整合社交网络与意见动态，模拟不同同质性和选择性暴露条件下回音室的形成，发现信息暴露显著影响回音室涌现，而算法过滤不一定保证其持续。</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>社交媒体中的“回音室”现象及其对社会两极分化的影晌，是政治学文献中一个备受争议的话题。关于这些强化特定观点的社群在多大程度上存在，以及它们如何加剧社会两极分化并削弱社会凝聚力，目前尚无定论。本文采用了一种社会模拟方法，结合政治传播和社会影响理论来解释“回音室”是如何在社交媒体平台上形成的。所开发的基于代理的模型将个人的社会网络（线上和线下）与观点动态相结合，以厘清社交媒体算法和社会网络结构各自的作用。模拟实验分别操控了两个变量：（1）个人网络中的同质性或群体相似性；（2）通过社交媒体上的信息过滤机制（即“信息泡沫”）所导致的选择性信息暴露程度。研究发现，个体的信息获取方式显著影响了“回音室”的形成，尤其是在最初由随机人群组成的网络中，人们周围的人具有较大的多样性。然而，即使人为制造了“回音室”，在存在信息过滤算法的情况下，这些回音室也无法长期持续存在。总体而言，我们需要重新审视我们对“回音室”现象的理解，以及导致这一现象的机制。</t>
-        </is>
-      </c>
-      <c r="O6" s="2" t="inlineStr">
-        <is>
-          <t>The extent of echo chambers in social media and their impact on polarization is an open debate in the political science literature. There is mixed evidence about the extent to which these opinion-reinforcement communities exist and contribute to polarization and the erosion of social cohesion. This paper employs a social simulation approach that draws on political communication and social influence theories to explain how echo chambers can emerge on social media platforms. The agent-based model developed here integrates individual social networks (online and offline) with opinion dynamics to untangle the respective roles of social media algorithms and social network structures. Simulation conditions separately manipulated (1) the homophily or group similarity in personal networks and (2) the level of selective exposure to confirming information through filter bubbles on social media. We found that individuals’ information exposure significantly influenced echo chamber emergence, particularly in initially random social networks where people are surrounded by a diverse group of others. At the same time, artificially creating echo chambers did not ensure their persistence over time in the presence of filtering algorithms. Overall, we need to reconsider how we understand echo chambers and the mechanisms responsible for this phenomenon.</t>
-        </is>
-      </c>
+          <t>跨国研究个体对在线政治广告定制化程度的感知及其影响，属于政治传播领域。</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr"/>
+      <c r="O6" s="2" t="inlineStr"/>
       <c r="P6" s="6" t="inlineStr">
         <is>
-          <t>10.1080/1369118x.2026.2695177</t>
+          <t>10.1080/1369118x.2026.2703856</t>
         </is>
       </c>
       <c r="Q6" s="6" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1080/1369118x.2026.2695177</t>
+          <t>https://doi.org/10.1080/1369118x.2026.2703856</t>
         </is>
       </c>
       <c r="R6" s="2" t="inlineStr">
@@ -1225,7 +1217,7 @@
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
@@ -1244,22 +1236,22 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>Measuring partisan community dynamics: a longitudinal analysis of affective engagement in pro-Bolsonaro Facebook networks</t>
+          <t>The echoes from social media: modeling how filter bubbles and network structure shape echo chamber emergence</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>测量党派社区动态：对支持博索纳罗的Facebook网络中情感参与度的纵向分析</t>
+          <t>社交媒体的回声：研究信息茧房和网络结构如何影响回音室效应的形成</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>Giada Marino, Bruna Almeida Paroni, Fabio Giglietto</t>
+          <t>Cristina Chueca Del Cerro</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -1269,42 +1261,42 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>社交媒体；政治极化；LLM；情感分析；网络分析</t>
+          <t>社交媒体；过滤气泡；回音室；仿真模拟；意见动态</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>大规模平台数据＋LLM</t>
+          <t>计算模拟</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>议题符合，且摘要明确显示：1200 万条 Facebook 帖文、LLM 分类、时间序列与回归。</t>
+          <t>议题符合，且方法证据显示：基于代理的社会模拟，操控网络同质性与选择性暴露。</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>研究2021-2023年巴西亲博尔索纳罗Facebook群组的纵向情感参与模式，使用LLM分类和回归分析发现重大政治事件导致情感极化波动，挑战了传播极化稳定性的假设。</t>
+          <t>通过agent-based模型整合社交网络与意见动态，模拟不同同质性和选择性暴露条件下回音室的形成，发现信息暴露显著影响回音室涌现，而算法过滤不一定保证其持续。</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>本文研究了重大政治事件如何影响一个极度党派化的、支持博索纳罗的Facebook账户群体中的情感参与模式。这类极端党派化的社群通常被描述为“回音室”，其参与模式具有可预测性，但这一假设很少通过纵向研究来验证。我们采用了一种混合方法论，结合了基于大型语言模型（LLM）的内容分类、时间序列分析和回归建模技术，分析了2021年至2023年间来自53个巴西支持博索纳罗的群组和页面的1200多万条帖子。我们构建了两个行为指标：情感极化指数（用于衡量积极与消极情绪的反应），以及参与平衡指数（用于衡量评论与分享之间的互动）。研究结果表明，这些极端党派化的社群在参与模式上表现出惊人的不稳定性，这与传统理论中认为极化现象是一致的观点相矛盾。2023年，随着卢拉的就职以及1月的未遂政变，这些社群出现了显著变化：情绪强度下降，内部辩论增多，反对声音减弱。这些发现表明，参与动态不仅仅受固定意识形态立场的影响，还受到重大政治事件和情境变化的影响。本研究通过其纵向研究方法和机器学习技术在政治主体识别方面的应用，为理解数字政治极化的动态本质提供了新的见解。</t>
+          <t>社交媒体中的“回音室”现象及其对社会两极分化的影晌，是政治学文献中一个备受争议的话题。关于这些强化特定观点的社群在多大程度上存在，以及它们如何加剧社会两极分化并削弱社会凝聚力，目前尚无定论。本文采用了一种社会模拟方法，结合政治传播和社会影响理论来解释“回音室”是如何在社交媒体平台上形成的。所开发的基于代理的模型将个人的社会网络（线上和线下）与观点动态相结合，以厘清社交媒体算法和社会网络结构各自的作用。模拟实验分别操控了两个变量：（1）个人网络中的同质性或群体相似性；（2）通过社交媒体上的信息过滤机制（即“信息泡沫”）所导致的选择性信息暴露程度。研究发现，个体的信息获取方式显著影响了“回音室”的形成，尤其是在最初由随机人群组成的网络中，人们周围的人具有较大的多样性。然而，即使人为制造了“回音室”，在存在信息过滤算法的情况下，这些回音室也无法长期持续存在。总体而言，我们需要重新审视我们对“回音室”现象的理解，以及导致这一现象的机制。</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>This study examines how major political events shape affective engagement patterns in a hyperpartisan pro-Bolsonaro network of Facebook accounts. Hyperpartisan communities are often characterized as impermeable echo chambers with predictable engagement patterns, yet this assumption has rarely been tested longitudinally. Using a mixed-methods approach combining LLM-based content classification, time series analysis, and regression modeling, we analyze over 12 million posts from 53 Brazilian pro-Bolsonaro groups and pages across 2021–2023. Two behavioral indices were constructed: the Emotional Polarization Index measuring love-versus-angry reactions, and the Engagement Balance Index capturing comment-versus-share interactions. Results show that hyperpartisan communities displayed surprisingly unstable engagement patterns over time, contradicting traditional theories that assume polarization as consistent. A major shift occurred in 2023 around Lula's inauguration and the January coup attempt, marked by declining emotional intensity, increased internal debate, and weakening opposition responses. These findings suggest that engagement dynamics extend beyond fixed ideological positions, shaped by major political events and contextual changes. The study contributes methodologically through its longitudinal approach and use of machine learning for political actor recognition, offering new insights into the dynamic nature of digital political polarization.</t>
+          <t>The extent of echo chambers in social media and their impact on polarization is an open debate in the political science literature. There is mixed evidence about the extent to which these opinion-reinforcement communities exist and contribute to polarization and the erosion of social cohesion. This paper employs a social simulation approach that draws on political communication and social influence theories to explain how echo chambers can emerge on social media platforms. The agent-based model developed here integrates individual social networks (online and offline) with opinion dynamics to untangle the respective roles of social media algorithms and social network structures. Simulation conditions separately manipulated (1) the homophily or group similarity in personal networks and (2) the level of selective exposure to confirming information through filter bubbles on social media. We found that individuals’ information exposure significantly influenced echo chamber emergence, particularly in initially random social networks where people are surrounded by a diverse group of others. At the same time, artificially creating echo chambers did not ensure their persistence over time in the presence of filtering algorithms. Overall, we need to reconsider how we understand echo chambers and the mechanisms responsible for this phenomenon.</t>
         </is>
       </c>
       <c r="P7" s="6" t="inlineStr">
         <is>
-          <t>10.1080/1369118x.2026.2696929</t>
+          <t>10.1080/1369118x.2026.2695177</t>
         </is>
       </c>
       <c r="Q7" s="6" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1080/1369118x.2026.2696929</t>
+          <t>https://doi.org/10.1080/1369118x.2026.2695177</t>
         </is>
       </c>
       <c r="R7" s="2" t="inlineStr">
@@ -1320,7 +1312,7 @@
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
@@ -1339,22 +1331,22 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>Linking names with frames: the interplay of moral entities and moral frames in Chinese online gender debates</t>
+          <t>Measuring partisan community dynamics: a longitudinal analysis of affective engagement in pro-Bolsonaro Facebook networks</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>将名称与框架联系起来：道德实体与道德框架在中国网络性别辩论中的相互作用</t>
+          <t>测量党派社区动态：对支持博索纳罗的Facebook网络中情感参与度的纵向分析</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>Pianpian Wang, Qinyan Xie, Hui Li, Fengqian Chen, Jiayi Luo</t>
+          <t>Giada Marino, Bruna Almeida Paroni, Fabio Giglietto</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1364,42 +1356,42 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>社交媒体分析；词嵌入；道德框架；性别辩论</t>
+          <t>社交媒体；政治极化；LLM；情感分析；网络分析</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>计算文本分析</t>
+          <t>大规模平台数据＋LLM</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>议题符合，且摘要明确显示：在线评论的词嵌入与语义距离测量。</t>
+          <t>议题符合，且方法证据显示：1200 万条 Facebook 帖文、LLM 分类、时间序列与回归。</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>该研究通过词嵌入分析中国三起性别暴力事件评论，考察道德实体扩展与道德框架采用的关系，发现性别特定术语更贴近道德基础，而中性术语侧重程序性评价，揭示道德边界建构机制。</t>
+          <t>研究2021-2023年巴西亲博尔索纳罗Facebook群组的纵向情感参与模式，使用LLM分类和回归分析发现重大政治事件导致情感极化波动，挑战了传播极化稳定性的假设。</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>本文探讨了在线性别辩论中道德实体的扩展与道德框架的采纳之间的关系。通过对中国三起重大性别暴力事件的相关评论进行大规模分析，我们研究了不同指称术语如何构建道德实体以及这些术语与道德评价之间的关联。通过使用词嵌入分析技术，我们量化了指称术语与道德范畴之间的语义相似性。研究结果表明，与性别相关的术语更紧密地与道德基础相契合，这表明人们的道德取向更加宽泛且两极分化。相比之下，性别中立的术语主要引发程序性评价，关注的是行为者的角色而非其性别身份。这一发现表明，通过性别中立术语将道德关注范围扩展到外部群体，可以扩大被纳入道德评判的对象范围；而道德框架则明确了为何以及如何对这一扩展后的对象进行评判，从而使得道德评判在多样性和道德强度上都得到了增强。本研究为道德边界构建的机制提供了话语层面的证据，有助于进一步理解道德实体与道德框架的结合如何推动女权主义话语的道德化进程。</t>
+          <t>本文研究了重大政治事件如何影响一个极度党派化的、支持博索纳罗的Facebook账户群体中的情感参与模式。这类极端党派化的社群通常被描述为“回音室”，其参与模式具有可预测性，但这一假设很少通过纵向研究来验证。我们采用了一种混合方法论，结合了基于大型语言模型（LLM）的内容分类、时间序列分析和回归建模技术，分析了2021年至2023年间来自53个巴西支持博索纳罗的群组和页面的1200多万条帖子。我们构建了两个行为指标：情感极化指数（用于衡量积极与消极情绪的反应），以及参与平衡指数（用于衡量评论与分享之间的互动）。研究结果表明，这些极端党派化的社群在参与模式上表现出惊人的不稳定性，这与传统理论中认为极化现象是一致的观点相矛盾。2023年，随着卢拉的就职以及1月的未遂政变，这些社群出现了显著变化：情绪强度下降，内部辩论增多，反对声音减弱。这些发现表明，参与动态不仅仅受固定意识形态立场的影响，还受到重大政治事件和情境变化的影响。本研究通过其纵向研究方法和机器学习技术在政治主体识别方面的应用，为理解数字政治极化的动态本质提供了新的见解。</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>This study examines how moral-entity expansion in online gender debates is associated with the adoption of moral frames. Using a large-scale analysis of comments from three major gender-based violence incidents in China, we explore how different referential terms construct moral entities and relate to moral evaluations. Employing word embedding analysis, we quantified the semantic proximity between referential terms and moral axes. The results show that gender-specific terms align more closely with moral foundations, suggesting a broader, more polarised moral orientation. In contrast, gender-neutral terms primarily activate procedural evaluations, focusing on the roles of actors rather than their gender identities. This result suggests that entity expansion toward out-group members via GST broadens the scope of who is under moral consideration, while frames specify why and how that widened target should be judged, thereby leading to moralisation that is amplified in both its diversity and moral charge. This study contributes to the literature on moral expansiveness by providing discourse-level evidence of how moral boundaries are constructed. It also helps explain how the coupling of moral entities and moral frames leads to the moralisation of feminist discourse.</t>
+          <t>This study examines how major political events shape affective engagement patterns in a hyperpartisan pro-Bolsonaro network of Facebook accounts. Hyperpartisan communities are often characterized as impermeable echo chambers with predictable engagement patterns, yet this assumption has rarely been tested longitudinally. Using a mixed-methods approach combining LLM-based content classification, time series analysis, and regression modeling, we analyze over 12 million posts from 53 Brazilian pro-Bolsonaro groups and pages across 2021–2023. Two behavioral indices were constructed: the Emotional Polarization Index measuring love-versus-angry reactions, and the Engagement Balance Index capturing comment-versus-share interactions. Results show that hyperpartisan communities displayed surprisingly unstable engagement patterns over time, contradicting traditional theories that assume polarization as consistent. A major shift occurred in 2023 around Lula's inauguration and the January coup attempt, marked by declining emotional intensity, increased internal debate, and weakening opposition responses. These findings suggest that engagement dynamics extend beyond fixed ideological positions, shaped by major political events and contextual changes. The study contributes methodologically through its longitudinal approach and use of machine learning for political actor recognition, offering new insights into the dynamic nature of digital political polarization.</t>
         </is>
       </c>
       <c r="P8" s="6" t="inlineStr">
         <is>
-          <t>10.1080/1369118x.2026.2699262</t>
+          <t>10.1080/1369118x.2026.2696929</t>
         </is>
       </c>
       <c r="Q8" s="6" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1080/1369118x.2026.2699262</t>
+          <t>https://doi.org/10.1080/1369118x.2026.2696929</t>
         </is>
       </c>
       <c r="R8" s="2" t="inlineStr">
@@ -1415,7 +1407,7 @@
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
@@ -1434,22 +1426,22 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>Weapon, wonder or both? Political framings of AI in global north and south media</t>
+          <t>Linking names with frames: the interplay of moral entities and moral frames in Chinese online gender debates</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>武器、奇迹，还是两者兼而有之？全球北方和南方媒体中对人工智能的政治解读</t>
+          <t>将名称与框架联系起来：道德实体与道德框架在中国网络性别辩论中的相互作用</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>Bárbara Maria Farias Mota</t>
+          <t>Pianpian Wang, Qinyan Xie, Hui Li, Fengqian Chen, Jiayi Luo</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -1459,7 +1451,7 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>AI；媒体框架；主题建模；情感分析；比较研究</t>
+          <t>社交媒体分析；词嵌入；道德框架；性别辩论</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -1469,32 +1461,32 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>议题符合，且摘要明确显示：6829 篇新闻的主题建模与情感分析。</t>
+          <t>议题符合，且方法证据显示：在线评论的词嵌入与语义距离测量。</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>分析2010-2024年全球南北12家报纸6829篇AI报道，结合主题建模与情感分析，揭示政治化阶段及南北情绪差异，强调地缘政治对AI叙事的影响。</t>
+          <t>该研究通过词嵌入分析中国三起性别暴力事件评论，考察道德实体扩展与道德框架采用的关系，发现性别特定术语更贴近道德基础，而中性术语侧重程序性评价，揭示道德边界建构机制。</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>随着人工智能（AI）越来越被视为一项政治基础设施和一种决策技术，它有可能重塑各种机构并重新配置权力关系，媒体报道在塑造公众对其风险和机遇的理解方面发挥着关键作用。本研究探讨了全球北方和南方的主流媒体如何从政治角度来报道AI，重点分析了这对数字治理和公众舆论的影响。在以往研究的基础上（这些研究虽然分析了AI的报道内容，但对其政治和情感维度探讨不足），本研究对比分析了来自欧洲、北美、非洲以及亚洲和大洋洲的12家报纸在2010年至2024年间发布的6,829篇新闻文章，采用了主题建模和情感分析的方法。研究结果揭示了三个时间阶段：初始阶段（2010–2016年）、通过危机实现政治化（2017–2021年）以及指数级加速发展阶段（2022–2024年），其中剑桥分析公司丑闻（2018年）和ChatGPT的推出（2022年）是两个重要的转折点。研究共发现了15个主题框架，其中“社交媒体与技术影响”（16.03%）、“技术与数字经济”（12.54%）以及“中美关系与贸易”（11.41%）最为突出。北方的媒体在报道中表现出更悲观的态度，41.7%的标题被归类为负面内容；相比之下，南方的媒体则更为乐观，51.5%的标题带有积极色彩。研究表明，关于AI的媒体叙事受到地缘政治争端、不同的风险认知以及技术力量不对称性的影响，因此亟需制定公平、透明且符合伦理标准的AI监管机制。</t>
+          <t>本文探讨了在线性别辩论中道德实体的扩展与道德框架的采纳之间的关系。通过对中国三起重大性别暴力事件的相关评论进行大规模分析，我们研究了不同指称术语如何构建道德实体以及这些术语与道德评价之间的关联。通过使用词嵌入分析技术，我们量化了指称术语与道德范畴之间的语义相似性。研究结果表明，与性别相关的术语更紧密地与道德基础相契合，这表明人们的道德取向更加宽泛且两极分化。相比之下，性别中立的术语主要引发程序性评价，关注的是行为者的角色而非其性别身份。这一发现表明，通过性别中立术语将道德关注范围扩展到外部群体，可以扩大被纳入道德评判的对象范围；而道德框架则明确了为何以及如何对这一扩展后的对象进行评判，从而使得道德评判在多样性和道德强度上都得到了增强。本研究为道德边界构建的机制提供了话语层面的证据，有助于进一步理解道德实体与道德框架的结合如何推动女权主义话语的道德化进程。</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>As artificial intelligence (AI) is increasingly understood as a political infrastructure and a decision-making technology with the potential to reshape institutions and reconfigure power relations, media coverage plays a key role in shaping public understanding of its risks and opportunities. This study examines how mainstream media outlets in the Global North and Global South politically frame AI, emphasising the implications for digital governance and public opinion. Building on prior work that analyse AI coverage but leaves its political and emotional dimensions underexplored, the research presents a comparative analysis of 6,829 news articles (2010–2024) across twelve newspapers from Europe, North America, Africa, and Asia and Oceania, combining topic modelling and sentiment analysis. The results reveal three temporal phases: an incipient phase (2010–2016), politicisation through crises (2017–2021), and exponential acceleration (2022–2024), with salient inflection points following the Cambridge Analytica scandal (2018) and the launch of ChatGPT (2022). Fifteen thematic frames emerged, dominated by Social Media and Tech Impact (16.03 per cent), Technology and the Digital Economy (12.54 per cent), and China–US Relations and Trade (11.41 per cent). Media outlets in the North display higher levels of pessimistic coverage , with 41.7 per cent of headlines classified as negative. In contrast, media in the South express a more optimistic tone, with 51.5 per cent of headlines being positive. The study demonstrates that media narratives about AI are shaped by geopolitical disputes, differing risk perceptions, and asymmetries in technological power, stressing the need for fair, transparent and ethical AI regulation.</t>
+          <t>This study examines how moral-entity expansion in online gender debates is associated with the adoption of moral frames. Using a large-scale analysis of comments from three major gender-based violence incidents in China, we explore how different referential terms construct moral entities and relate to moral evaluations. Employing word embedding analysis, we quantified the semantic proximity between referential terms and moral axes. The results show that gender-specific terms align more closely with moral foundations, suggesting a broader, more polarised moral orientation. In contrast, gender-neutral terms primarily activate procedural evaluations, focusing on the roles of actors rather than their gender identities. This result suggests that entity expansion toward out-group members via GST broadens the scope of who is under moral consideration, while frames specify why and how that widened target should be judged, thereby leading to moralisation that is amplified in both its diversity and moral charge. This study contributes to the literature on moral expansiveness by providing discourse-level evidence of how moral boundaries are constructed. It also helps explain how the coupling of moral entities and moral frames leads to the moralisation of feminist discourse.</t>
         </is>
       </c>
       <c r="P9" s="6" t="inlineStr">
         <is>
-          <t>10.1080/1369118x.2026.2691775</t>
+          <t>10.1080/1369118x.2026.2699262</t>
         </is>
       </c>
       <c r="Q9" s="6" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1080/1369118x.2026.2691775</t>
+          <t>https://doi.org/10.1080/1369118x.2026.2699262</t>
         </is>
       </c>
       <c r="R9" s="2" t="inlineStr">
@@ -1510,11 +1502,11 @@
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>49</v>
-      </c>
-      <c r="B10" s="7" t="inlineStr">
-        <is>
-          <t>棕色</t>
+        <v>43</v>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>黄色</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
@@ -1529,22 +1521,22 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>Inaccuracies, omissions, and bullshit: 2024 U.S. elections through the eyes of ChatGPT</t>
+          <t>Weapon, wonder or both? Political framings of AI in global north and south media</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>不准确之处、遗漏内容以及胡言乱语：ChatGPT眼中的2024年美国大选</t>
+          <t>武器、奇迹，还是两者兼而有之？全球北方和南方媒体中对人工智能的政治解读</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>Heesoo Jang, Shannon C. McGregor, Lorcan Neill</t>
+          <t>Bárbara Maria Farias Mota</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1554,42 +1546,42 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>生成式AI；大语言模型；选举 misinformation；平台治理；计算审计</t>
+          <t>AI；媒体框架；主题建模；情感分析；比较研究</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>生成式 AI 审计</t>
+          <t>计算文本分析</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>议题符合，且摘要明确显示：对 ChatGPT-4o mini 选举回答进行系统审计。</t>
+          <t>议题符合，且方法证据显示：6829 篇新闻的主题建模与情感分析。</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>通过审计ChatGPT-4o mini在2024年美国大选前的输出，发现其存在不准确、遗漏和胡扯等问题，提出从 curative governance 到 generative governance 的转变，揭示生成式AI对民主信息环境的潜在危害。</t>
+          <t>分析2010-2024年全球南北12家报纸6829篇AI报道，结合主题建模与情感分析，揭示政治化阶段及南北情绪差异，强调地缘政治对AI叙事的影响。</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>本研究评估了2024年美国大选期间，生成式人工智能（AI）在政治和选举相关领域所产生的内容的准确性、质量及其潜在影响。我们将社交媒体平台的治理和内容审核理论应用于AI领域，探讨了大型语言模型（LLMs）及其所有者公司如何塑造和影响政治信息环境。研究指出，从社交媒体向生成式AI的转变标志着平台权力的一种根本性演变——即从“选择性治理”（通过筛选人类言论来提供信息）转向“生成性治理”（通过生成内容来提供信息）。通过采用一种新颖的混合方法审计手段，分析了ChatGPT-4在选举日前不到两周内生成的关于政治和选举的文本，发现ChatGPT在关键选举期间未能为用户提供准确、可靠和可信的信息。我们的分析识别并归纳了ChatGPT回答中存在的各种危害民主制度的因素，包括信息不准确、避重就轻的表述、虚假内容以及关键信息的遗漏，这些现象表明该技术尚不适用于民主选举环境。本研究强调了在生成式AI领域建立新的问责机制的必要性，尤其是在现有行业自律措施无法有效保护民主信息环境的情况下。</t>
+          <t>随着人工智能（AI）越来越被视为一项政治基础设施和一种决策技术，它有可能重塑各种机构并重新配置权力关系，媒体报道在塑造公众对其风险和机遇的理解方面发挥着关键作用。本研究探讨了全球北方和南方的主流媒体如何从政治角度来报道AI，重点分析了这对数字治理和公众舆论的影响。在以往研究的基础上（这些研究虽然分析了AI的报道内容，但对其政治和情感维度探讨不足），本研究对比分析了来自欧洲、北美、非洲以及亚洲和大洋洲的12家报纸在2010年至2024年间发布的6,829篇新闻文章，采用了主题建模和情感分析的方法。研究结果揭示了三个时间阶段：初始阶段（2010–2016年）、通过危机实现政治化（2017–2021年）以及指数级加速发展阶段（2022–2024年），其中剑桥分析公司丑闻（2018年）和ChatGPT的推出（2022年）是两个重要的转折点。研究共发现了15个主题框架，其中“社交媒体与技术影响”（16.03%）、“技术与数字经济”（12.54%）以及“中美关系与贸易”（11.41%）最为突出。北方的媒体在报道中表现出更悲观的态度，41.7%的标题被归类为负面内容；相比之下，南方的媒体则更为乐观，51.5%的标题带有积极色彩。研究表明，关于AI的媒体叙事受到地缘政治争端、不同的风险认知以及技术力量不对称性的影响，因此亟需制定公平、透明且符合伦理标准的AI监管机制。</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>This study evaluated the accuracy, quality, and implications of outputs produced by generative artificial intelligences (AI) related to politics and electoral processes during the 2024 United States elections. We extend social media platform governance and content moderation theories to the study of AI, illustrating how large language models (LLMs), and the companies that own these technologies, shape and influence political information environments. Notably, we argue that the shift from social media to generative AI represents a fundamental evolution in platform power: a move from curative governance (providing information by sorting human speech) to generative governance (providing information by generating speech). Through a novel mixed-methods audit approach to studying ChatGPT-4o mini outputs regarding politics and elections collected less than two weeks before election day, we find that ChatGPT largely failed to provide users with accurate, reliable, and trustworthy information during a crucial election period. Our analysis identifies and categorizes potential democratic harms embedded in ChatGPT’s responses – such as inaccuracies, hedging, bullshit, and omissions – that paint a picture of a technology ill-equipped for democratic elections. This study illustrates the need for new frameworks for accountability in generative AI, particularly as voluntary industry safeguards fail to protect democratic information environments.</t>
+          <t>As artificial intelligence (AI) is increasingly understood as a political infrastructure and a decision-making technology with the potential to reshape institutions and reconfigure power relations, media coverage plays a key role in shaping public understanding of its risks and opportunities. This study examines how mainstream media outlets in the Global North and Global South politically frame AI, emphasising the implications for digital governance and public opinion. Building on prior work that analyse AI coverage but leaves its political and emotional dimensions underexplored, the research presents a comparative analysis of 6,829 news articles (2010–2024) across twelve newspapers from Europe, North America, Africa, and Asia and Oceania, combining topic modelling and sentiment analysis. The results reveal three temporal phases: an incipient phase (2010–2016), politicisation through crises (2017–2021), and exponential acceleration (2022–2024), with salient inflection points following the Cambridge Analytica scandal (2018) and the launch of ChatGPT (2022). Fifteen thematic frames emerged, dominated by Social Media and Tech Impact (16.03 per cent), Technology and the Digital Economy (12.54 per cent), and China–US Relations and Trade (11.41 per cent). Media outlets in the North display higher levels of pessimistic coverage , with 41.7 per cent of headlines classified as negative. In contrast, media in the South express a more optimistic tone, with 51.5 per cent of headlines being positive. The study demonstrates that media narratives about AI are shaped by geopolitical disputes, differing risk perceptions, and asymmetries in technological power, stressing the need for fair, transparent and ethical AI regulation.</t>
         </is>
       </c>
       <c r="P10" s="6" t="inlineStr">
         <is>
-          <t>10.1080/1369118x.2026.2685121</t>
+          <t>10.1080/1369118x.2026.2691775</t>
         </is>
       </c>
       <c r="Q10" s="6" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1080/1369118x.2026.2685121</t>
+          <t>https://doi.org/10.1080/1369118x.2026.2691775</t>
         </is>
       </c>
       <c r="R10" s="2" t="inlineStr">
@@ -1605,11 +1597,11 @@
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>55</v>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>无</t>
+        <v>49</v>
+      </c>
+      <c r="B11" s="7" t="inlineStr">
+        <is>
+          <t>棕色</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
@@ -1624,22 +1616,22 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>Latent communicative figurations: mapping quasi-visible strategic relational structures on Facebook</t>
+          <t>Inaccuracies, omissions, and bullshit: 2024 U.S. elections through the eyes of ChatGPT</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>潜在的沟通模式：在Facebook上映射几乎可视化的战略关系结构</t>
+          <t>不准确之处、遗漏内容以及胡言乱语：ChatGPT眼中的2024年美国大选</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>Chamil Rathnayake, Daniel D. Suthers</t>
+          <t>Heesoo Jang, Shannon C. McGregor, Lorcan Neill</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1649,42 +1641,42 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>社交媒体；网络分析；Facebook；传播结构</t>
+          <t>生成式AI；大语言模型；选举 misinformation；平台治理；计算审计</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>网络分析</t>
+          <t>生成式 AI 审计</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>议题符合，且摘要明确显示：Facebook 品牌帖文构成的四个二部网络。</t>
+          <t>议题符合，且方法证据显示：对 ChatGPT-4o mini 选举回答进行系统审计。</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>本文提出潜在传播构型概念，利用Facebook可再生能源相关品牌帖子构建双模网络，揭示战略伙伴与页面间的隐性关系，并探讨平台逻辑对新闻媒体角色的影响。</t>
+          <t>通过审计ChatGPT-4o mini在2024年美国大选前的输出，发现其存在不准确、遗漏和胡扯等问题，提出从 curative governance 到 generative governance 的转变，揭示生成式AI对民主信息环境的潜在危害。</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>本文探讨了“潜在的沟通结构”（latent communicative figurations）的概念。这些结构是通过社交媒体的功能（例如合作伙伴广告系统所提供的功能）形成的、近乎可视化的关系网络。我们认为，这些潜在的沟通结构得以实现，得益于平台所提供的功能，这些功能使得用户能够控制内容的可见性，从而建立潜在的联系，进而动员合作伙伴共同创建和发布符合特定战略目标的社交媒体内容。研究提出了一种系统化的方法，用于分析两种类型的行为者的定位：合作伙伴（投资者）和页面（发布内容的主体）。这两种行为者位于平台设计者与更广泛的网络公众之间。研究以与可再生能源相关的品牌化Facebook帖子为例，构建了四个双边网络，揭示了这些网络中的潜在关系结构及主导行为者。研究结果表明，主要形成了以组织和专业行为者为主体的潜在联系网络，这些网络能够引发公众对可再生能源问题的关注。研究还发现了一个双重过程：一方面是行为的“去制度化”（deinstitutionalisation），另一方面是行为的“再制度化”（reinstitutionalisation）——例如新闻媒体等传统机构的行为者需要转变其传统角色，以适应以盈利为导向的社交媒体平台逻辑。这种转变过程中存在的矛盾（即行为者需要在战略合作伙伴的期望与公众利益之间找到平衡）揭示了网络化社交环境中的根本对立关系。</t>
+          <t>本研究评估了2024年美国大选期间，生成式人工智能（AI）在政治和选举相关领域所产生的内容的准确性、质量及其潜在影响。我们将社交媒体平台的治理和内容审核理论应用于AI领域，探讨了大型语言模型（LLMs）及其所有者公司如何塑造和影响政治信息环境。研究指出，从社交媒体向生成式AI的转变标志着平台权力的一种根本性演变——即从“选择性治理”（通过筛选人类言论来提供信息）转向“生成性治理”（通过生成内容来提供信息）。通过采用一种新颖的混合方法审计手段，分析了ChatGPT-4在选举日前不到两周内生成的关于政治和选举的文本，发现ChatGPT在关键选举期间未能为用户提供准确、可靠和可信的信息。我们的分析识别并归纳了ChatGPT回答中存在的各种危害民主制度的因素，包括信息不准确、避重就轻的表述、虚假内容以及关键信息的遗漏，这些现象表明该技术尚不适用于民主选举环境。本研究强调了在生成式AI领域建立新的问责机制的必要性，尤其是在现有行业自律措施无法有效保护民主信息环境的情况下。</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>This study conceptualises latent communicative figurations, which are quasi-visible relational structures formed through social media affordances, for example as provided by partnership advertisement systems. We argue that latent communicative figurations are facilitated by platform affordances that enable the curation of visibility, allowing actors to form latent ties for mobilising partners to create and publish social media content that serve specific strategic interests. A systematic approach is proposed to map the positionality of two types of actors – partners (investors) and pages – who contribute to latent communicative figurations, situated between platform designers and the broader networked publics. A sample of branded Facebook posts related to renewable energy is used to construct four bi-partite networks, revealing the structure of latent relations and dominant actors within them. The results show the emergence of a primarily organisational and professional set of latent ties, which mobilises public reactions surrounding renewable energy. The results evidence a dual process of deinstitutionalisation and reinstitutionalisation where actors such as news media transition from their conventional roles to those that are demanded by profit-driven platform logics. The tensions inherent in this transition – where actors must balance the expectations of strategic partners against the public interest – reveal the fundamental antagonisms within networked social environments.</t>
+          <t>This study evaluated the accuracy, quality, and implications of outputs produced by generative artificial intelligences (AI) related to politics and electoral processes during the 2024 United States elections. We extend social media platform governance and content moderation theories to the study of AI, illustrating how large language models (LLMs), and the companies that own these technologies, shape and influence political information environments. Notably, we argue that the shift from social media to generative AI represents a fundamental evolution in platform power: a move from curative governance (providing information by sorting human speech) to generative governance (providing information by generating speech). Through a novel mixed-methods audit approach to studying ChatGPT-4o mini outputs regarding politics and elections collected less than two weeks before election day, we find that ChatGPT largely failed to provide users with accurate, reliable, and trustworthy information during a crucial election period. Our analysis identifies and categorizes potential democratic harms embedded in ChatGPT’s responses – such as inaccuracies, hedging, bullshit, and omissions – that paint a picture of a technology ill-equipped for democratic elections. This study illustrates the need for new frameworks for accountability in generative AI, particularly as voluntary industry safeguards fail to protect democratic information environments.</t>
         </is>
       </c>
       <c r="P11" s="6" t="inlineStr">
         <is>
-          <t>10.1080/1369118x.2026.2686314</t>
+          <t>10.1080/1369118x.2026.2685121</t>
         </is>
       </c>
       <c r="Q11" s="6" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1080/1369118x.2026.2686314</t>
+          <t>https://doi.org/10.1080/1369118x.2026.2685121</t>
         </is>
       </c>
       <c r="R11" s="2" t="inlineStr">
@@ -1700,11 +1692,11 @@
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>57</v>
-      </c>
-      <c r="B12" s="4" t="inlineStr">
-        <is>
-          <t>黄色</t>
+        <v>55</v>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
@@ -1719,22 +1711,22 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>The viral gender antagonism on social media: examining the role of multimodal framing and gender identity</t>
+          <t>Latent communicative figurations: mapping quasi-visible strategic relational structures on Facebook</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>社交媒体上的性别对立现象：探究多模态框架与性别认同的作用</t>
+          <t>潜在的沟通模式：在Facebook上映射几乎可视化的战略关系结构</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>Xinran Zhang, Yuhan Wei, X J Wang</t>
+          <t>Chamil Rathnayake, Daniel D. Suthers</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1744,42 +1736,42 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>社交媒体分析；多模态框架；性别对抗；微博数据</t>
+          <t>社交媒体；网络分析；Facebook；传播结构</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>大规模平台数据建模</t>
+          <t>网络分析</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>议题符合，且摘要明确显示：2.29 万帖文、115 万评论与广义线性混合模型。</t>
+          <t>议题符合，且方法证据显示：Facebook 品牌帖文构成的四个二部网络。</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>研究基于微博22,925条帖子和115万条评论，运用广义线性混合模型分析多模态框架和性别身份对性别对抗性话语的影响，发现煽情化和个性化框架加剧对抗，娱乐化框架减弱对抗，且性别动态具有调节作用。</t>
+          <t>本文提出潜在传播构型概念，利用Facebook可再生能源相关品牌帖子构建双模网络，揭示战略伙伴与页面间的隐性关系，并探讨平台逻辑对新闻媒体角色的影响。</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>是什么驱动了社交媒体上关于性别对立的言论？本研究旨在探讨多模态框架构建和性别身份线索在其中的作用。我们分析了在中国最受欢迎的社交媒体平台之一——微博上，与性暴力相关的22,925条帖子和115万条评论。广义线性混合模型的分析结果显示，包括煽动性和个性化框架构建在内的多模态框架策略显著加剧了性别对立，尤其是当信息由属于“外群体”性别的人发布时。相比之下，娱乐性的框架构建能够减少性别对立，而解释性的框架构建则没有明显影响。性别动态也起着关键作用：女性评论者对男性发布的煽动性帖子反应更为强烈。这些研究结果强调了框架构建策略和身份认知在塑造性别议题讨论中的重要性，为社交媒体治理和女性主义传播实践提供了有益的启示。</t>
+          <t>本文探讨了“潜在的沟通结构”（latent communicative figurations）的概念。这些结构是通过社交媒体的功能（例如合作伙伴广告系统所提供的功能）形成的、近乎可视化的关系网络。我们认为，这些潜在的沟通结构得以实现，得益于平台所提供的功能，这些功能使得用户能够控制内容的可见性，从而建立潜在的联系，进而动员合作伙伴共同创建和发布符合特定战略目标的社交媒体内容。研究提出了一种系统化的方法，用于分析两种类型的行为者的定位：合作伙伴（投资者）和页面（发布内容的主体）。这两种行为者位于平台设计者与更广泛的网络公众之间。研究以与可再生能源相关的品牌化Facebook帖子为例，构建了四个双边网络，揭示了这些网络中的潜在关系结构及主导行为者。研究结果表明，主要形成了以组织和专业行为者为主体的潜在联系网络，这些网络能够引发公众对可再生能源问题的关注。研究还发现了一个双重过程：一方面是行为的“去制度化”（deinstitutionalisation），另一方面是行为的“再制度化”（reinstitutionalisation）——例如新闻媒体等传统机构的行为者需要转变其传统角色，以适应以盈利为导向的社交媒体平台逻辑。这种转变过程中存在的矛盾（即行为者需要在战略合作伙伴的期望与公众利益之间找到平衡）揭示了网络化社交环境中的根本对立关系。</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>What drives viral gender-antagonistic discourse on social media? This study proposes to examine the role of multimodal framing and gender identity cues. We analyzed 22,925 posts and 1.15 million comments related to sexual violence on Weibo, one of the most prominent social media platforms in China. Results from generalized linear mixed models show that multimodal framing strategies including sensationalizing and personalizing framing significantly increase gender antagonism, particularly when the message is posted by someone of the outgroup gender. In contrast, entertaining framing reduces gender antagonism, while explanatory framing has a neutral effect. Gender dynamics also play a critical role: female commenters are more reactive to male-authored sensationalizing posts. These results highlight the importance of framing strategies and identity perceptions in shaping discourse on gender issues, offering insights for social media governance and feminist communication practices.</t>
+          <t>This study conceptualises latent communicative figurations, which are quasi-visible relational structures formed through social media affordances, for example as provided by partnership advertisement systems. We argue that latent communicative figurations are facilitated by platform affordances that enable the curation of visibility, allowing actors to form latent ties for mobilising partners to create and publish social media content that serve specific strategic interests. A systematic approach is proposed to map the positionality of two types of actors – partners (investors) and pages – who contribute to latent communicative figurations, situated between platform designers and the broader networked publics. A sample of branded Facebook posts related to renewable energy is used to construct four bi-partite networks, revealing the structure of latent relations and dominant actors within them. The results show the emergence of a primarily organisational and professional set of latent ties, which mobilises public reactions surrounding renewable energy. The results evidence a dual process of deinstitutionalisation and reinstitutionalisation where actors such as news media transition from their conventional roles to those that are demanded by profit-driven platform logics. The tensions inherent in this transition – where actors must balance the expectations of strategic partners against the public interest – reveal the fundamental antagonisms within networked social environments.</t>
         </is>
       </c>
       <c r="P12" s="6" t="inlineStr">
         <is>
-          <t>10.1080/1369118x.2026.2686315</t>
+          <t>10.1080/1369118x.2026.2686314</t>
         </is>
       </c>
       <c r="Q12" s="6" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1080/1369118x.2026.2686315</t>
+          <t>https://doi.org/10.1080/1369118x.2026.2686314</t>
         </is>
       </c>
       <c r="R12" s="2" t="inlineStr">
@@ -1795,11 +1787,11 @@
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>72</v>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>无</t>
+        <v>57</v>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>黄色</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
@@ -1814,22 +1806,22 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>Targeting and/or tailoring?! A theoretical framework and its application to political social media advertising</t>
+          <t>The viral gender antagonism on social media: examining the role of multimodal framing and gender identity</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>定向投放与/或个性化定制？！一个理论框架及其在政治社交媒体广告中的应用</t>
+          <t>社交媒体上的性别对立现象：探究多模态框架与性别认同的作用</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>Christina Gahn, Simon Kruschinski</t>
+          <t>Xinran Zhang, Yuhan Wei, X J Wang</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1839,42 +1831,42 @@
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>政治广告；社交媒体；数据驱动竞选；广告定向</t>
+          <t>社交媒体分析；多模态框架；性别对抗；微博数据</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>平台数据＋多模态分析</t>
+          <t>大规模平台数据建模</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>议题符合，且摘要明确显示：Meta 广告与定向数据集、4760 条广告的多模态编码。</t>
+          <t>议题符合，且方法证据显示：2.29 万帖文、115 万评论与广义线性混合模型。</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>提出targeting与tailoring的理论框架，基于2021年德国大选Facebook和Instagram广告数据，测量政党广告策略及其对曝光量的影响。</t>
+          <t>研究基于微博22,925条帖子和115万条评论，运用广义线性混合模型分析多模态框架和性别身份对性别对抗性话语的影响，发现煽情化和个性化框架加剧对抗，娱乐化框架减弱对抗，且性别动态具有调节作用。</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>尽管数据驱动的竞选活动（Data-Driven Campaigning, DDC）被广泛使用，但对于政党如何在社交媒体上运用“定位”（决定通过广告接触哪些受众）和“定制”（根据特定目标群体调整广告内容）这两种广告策略，目前仍缺乏清晰的概念界定和实证理解。关于这些策略单独或结合使用后如何影响广告效果（如广告的展示次数——这是评估广告在竞选活动中可见性的关键指标），我们知之甚少。在本文中，我们提出了一个关于“定位”和“定制”这两种策略的新理论框架，并展示了如何分别测量它们。我们将这一框架应用于2021年德国大选期间在Meta平台（Facebook和Instagram）上的竞选活动，分析了六个德国政党及其主要候选人在竞选最后四周发布的所有广告（共4760条）。我们结合了多模态的手动内容分析数据、Meta Ad Targeting数据集以及Meta Ad Library来独立测量这两个概念。研究结果表明，“定位”和“定制”是两个不同的理论概念，在实践中很少被同时使用；德国政党倾向于单独运用这两种策略。这两种策略对广告展示次数的影响也有所不同：其中“定位”对广告展示次数有显著影响，而“定制”则没有这种效果。这些发现强调了在数据驱动的竞选活动中将“定位”和“定制”视为不同现象的重要性，并为未来关于社交媒体广告在政治竞选中战略应用的研究奠定了基础。</t>
+          <t>是什么驱动了社交媒体上关于性别对立的言论？本研究旨在探讨多模态框架构建和性别身份线索在其中的作用。我们分析了在中国最受欢迎的社交媒体平台之一——微博上，与性暴力相关的22,925条帖子和115万条评论。广义线性混合模型的分析结果显示，包括煽动性和个性化框架构建在内的多模态框架策略显著加剧了性别对立，尤其是当信息由属于“外群体”性别的人发布时。相比之下，娱乐性的框架构建能够减少性别对立，而解释性的框架构建则没有明显影响。性别动态也起着关键作用：女性评论者对男性发布的煽动性帖子反应更为强烈。这些研究结果强调了框架构建策略和身份认知在塑造性别议题讨论中的重要性，为社交媒体治理和女性主义传播实践提供了有益的启示。</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>Despite the widespread use of data-driven campaigning (DDC), there is limited conceptual clarity and empirical understanding of how political parties employ the advertising strategies of targeting (deciding which audiences to reach with ads) and tailoring (adapting ad content to specific target groups) on social media. Little is known about how these strategies, individually or in combination, influence outcome variables such as impressions of an ad, a key metric for assessing the visibility of ads in campaigns. In this paper we provide a novel theoretical conceptualization of the related yet distinct strategies of targeting and tailoring and demonstrate how they can be measured separately. We apply our framework to the 2021 German election campaign on the Meta platforms Facebook and Instagram. We do this by analyzing all ads (n = 4760) purchased by six German parties and their top candidates during the final four weeks of the campaign. We combine multi-modal manual content analysis data of ad tailoring with the Meta Ad Targeting Dataset and the Meta Ad Library to measure the two concepts independently. Our findings show that targeting and tailoring are distinct theoretical concepts that are rarely combined in practice. German parties tend to use these strategies independently. Targeting and tailoring have separate effects on ad impressions, with targeting showing a significant association while tailoring does not. These results underscore the importance of treating targeting and tailoring as distinct phenomena within DDC and provide a foundation for future research on the strategic use of social media advertising in political campaigns.</t>
+          <t>What drives viral gender-antagonistic discourse on social media? This study proposes to examine the role of multimodal framing and gender identity cues. We analyzed 22,925 posts and 1.15 million comments related to sexual violence on Weibo, one of the most prominent social media platforms in China. Results from generalized linear mixed models show that multimodal framing strategies including sensationalizing and personalizing framing significantly increase gender antagonism, particularly when the message is posted by someone of the outgroup gender. In contrast, entertaining framing reduces gender antagonism, while explanatory framing has a neutral effect. Gender dynamics also play a critical role: female commenters are more reactive to male-authored sensationalizing posts. These results highlight the importance of framing strategies and identity perceptions in shaping discourse on gender issues, offering insights for social media governance and feminist communication practices.</t>
         </is>
       </c>
       <c r="P13" s="6" t="inlineStr">
         <is>
-          <t>10.1080/1369118x.2026.2652497</t>
+          <t>10.1080/1369118x.2026.2686315</t>
         </is>
       </c>
       <c r="Q13" s="6" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1080/1369118x.2026.2652497</t>
+          <t>https://doi.org/10.1080/1369118x.2026.2686315</t>
         </is>
       </c>
       <c r="R13" s="2" t="inlineStr">
@@ -1890,7 +1882,7 @@
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
@@ -1904,72 +1896,60 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>摘要明确</t>
+          <t>出版方全文方法明确</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-24</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>Examining the influence of social media cues and platform perceptions on fake news detection</t>
+          <t>Stigma to skepticism: online consumer narratives of obesity management medications</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>研究社交媒体线索和平台认知对虚假新闻检测的影响</t>
+          <t>对怀疑态度的污名化：在线消费者关于肥胖管理药物的叙述</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>J.H. Tang, Barbara Millet</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>传统量化分析</t>
-        </is>
-      </c>
+          <t>Rumaila Abbas, Munyaradzi W. Nyadzayo</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr"/>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>社交媒体；虚假信息检测；在线实验</t>
+          <t>健康传播；在线叙事；消费者视角</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>在线实验</t>
+          <t>计算文本分析＋LLM</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>议题符合，且摘要明确显示：2×2×2 的社交媒体假新闻在线实验。</t>
+          <t>议题符合，且方法证据显示：Python 抓取 5789 条 Reddit 评论，使用 Top2Vec 与 LLM 辅助主题整理。</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>通过在线实验探究来源可信度、集体社会认可和用户对Twitter有用性感知对虚假新闻检测的影响，发现真实性偏差及平台感知降低虚假新闻识别准确性。</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>本研究探讨了信息来源的可信度、集体社会的认可度以及用户对Twitter在新闻消费中的帮助程度的认知，这些因素如何影响社交媒体上虚假新闻的识别。我们进行了一项在线实验（N = 271），实验设置了2个因素（真实性：真实 vs. 虚假）× 2个因素（信息来源的可信度：可信 vs. 不可信）× 2个因素（集体社会的认可度：低 vs. 高）。实验结果表明存在“真实性偏见”：参与者中有60%认为帖子是真实的。参与者在识别真实新闻（77%）方面的准确率高于识别虚假新闻（57%）。信息来源的可信度与新闻的真实性之间存在交互作用，提高了对真实新闻的识别准确率，但降低了对虚假新闻的识别能力。集体社会的认可度对虚假新闻的识别没有显著影响。值得注意的是，用户对Twitter在获取信息方面的帮助程度的认知影响了虚假新闻的识别能力——那些认为Twitter帮助较大的用户，在识别虚假新闻时的准确率较低。这些发现为打击网络虚假信息提供了新的思路。</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>This study investigates how source credibility, collective social endorsement, and users’ perceptions of Twitter's helpfulness for news consumption influence fake news detection on social media. We conducted a 2 (Veracity: real vs. fake) × 2 (Source Credibility: credible vs. non-credible) × 2 (Collective Social Endorsement: low vs. high) online experiment (N = 271). Results revealed a truth bias, with participants judging 60% of posts as real. Participants showed higher accuracy in identifying real news (77%) compared to fake news (57%). Source credibility interacted with news veracity, enhancing accuracy for real news while impairing detection of fake news. Collective social endorsement showed no significant effect. Notably, users’ perceptions of Twitter's helpfulness in staying informed impacted fake news detection – participants with higher perceptions of Twitter's helpfulness were less accurate in identifying fake news. The findings suggest new directions for combating online misinformation.</t>
-        </is>
-      </c>
+          <t>论文探讨在线消费者关于肥胖管理药物的叙事，分析从污名到怀疑的转变，可能基于社交媒体内容，但方法未明确。</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr"/>
+      <c r="O14" s="2" t="inlineStr"/>
       <c r="P14" s="6" t="inlineStr">
         <is>
-          <t>10.1080/1369118x.2026.2667914</t>
+          <t>10.1080/1369118x.2026.2678364</t>
         </is>
       </c>
       <c r="Q14" s="6" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1080/1369118x.2026.2667914</t>
+          <t>https://doi.org/10.1080/1369118x.2026.2678364</t>
         </is>
       </c>
       <c r="R14" s="2" t="inlineStr">
@@ -1985,7 +1965,7 @@
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
@@ -2004,22 +1984,22 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>Bad domains: exposure to malicious content online</t>
+          <t>Targeting and/or tailoring?! A theoretical framework and its application to political social media advertising</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>糟糕的网站：在线接触恶意内容的风险</t>
+          <t>定向投放与/或个性化定制？！一个理论框架及其在政治社交媒体广告中的应用</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>Lucas Shen, Gaurav Sood</t>
+          <t>Christina Gahn, Simon Kruschinski</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
@@ -2029,42 +2009,42 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>数字不平等；在线安全；浏览数据；恶意网站</t>
+          <t>政治广告；社交媒体；数据驱动竞选；广告定向</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>被动数字痕迹</t>
+          <t>平台数据＋多模态分析</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>议题符合，且摘要明确显示：代表性样本的被动浏览记录与恶意域名数据匹配。</t>
+          <t>议题符合，且方法证据显示：Meta 广告与定向数据集、4760 条广告的多模态编码。</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>利用美国千人代表性样本的域名级浏览数据，结合恶意域名库，分析不同人口特征群体对恶意网站的暴露差异，发现暴露集中于少数用户，且差异主要由上网强度解释。</t>
+          <t>提出targeting与tailoring的理论框架，基于2021年德国大选Facebook和Instagram广告数据，测量政党广告策略及其对曝光量的影响。</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>关于美国数字不平等的担忧已经不仅仅局限于数字接入和技能问题，还扩展到了在线安全方面的差异。我们研究了人们在接触恶意网站方面的群体差异，这是导致在线伤害的重要因素。我们结合了来自一千多名美国人的代表性样本的被动观测到的域名级浏览数据，以及恶意网站的相关数据，来评估哪些人群更容易受到恶意网站的影响，以及这些差异是否可以由在线活动的不同所解释。研究发现，在为期一个月的观测期间，51%的受访者至少访问过一个恶意网站；不过，这种接触情况存在高度集中现象：中位数的用户只访问了一个恶意网站，而第95百分位的用户则访问了八个恶意网站。在未进行任何调整的比较中，男性、非裔美国人和受教育程度较低的人群比同龄人更容易受到恶意网站的影响。此外，接触恶意网站的情况还与年龄有关——25岁以下的受访者受影响最大，而35至49岁的受访者受影响最小。然而，一旦考虑到在线活动因素，这些差异就会显著减弱，这表明接触恶意网站的差异更多地反映了浏览行为的强度，而不仅仅是人口统计特征本身的差异。</t>
+          <t>尽管数据驱动的竞选活动（Data-Driven Campaigning, DDC）被广泛使用，但对于政党如何在社交媒体上运用“定位”（决定通过广告接触哪些受众）和“定制”（根据特定目标群体调整广告内容）这两种广告策略，目前仍缺乏清晰的概念界定和实证理解。关于这些策略单独或结合使用后如何影响广告效果（如广告的展示次数——这是评估广告在竞选活动中可见性的关键指标），我们知之甚少。在本文中，我们提出了一个关于“定位”和“定制”这两种策略的新理论框架，并展示了如何分别测量它们。我们将这一框架应用于2021年德国大选期间在Meta平台（Facebook和Instagram）上的竞选活动，分析了六个德国政党及其主要候选人在竞选最后四周发布的所有广告（共4760条）。我们结合了多模态的手动内容分析数据、Meta Ad Targeting数据集以及Meta Ad Library来独立测量这两个概念。研究结果表明，“定位”和“定制”是两个不同的理论概念，在实践中很少被同时使用；德国政党倾向于单独运用这两种策略。这两种策略对广告展示次数的影响也有所不同：其中“定位”对广告展示次数有显著影响，而“定制”则没有这种效果。这些发现强调了在数据驱动的竞选活动中将“定位”和“定制”视为不同现象的重要性，并为未来关于社交媒体广告在政治竞选中战略应用的研究奠定了基础。</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>Concerns about digital inequality in the United States increasingly extend beyond access and skills to differences in online safety. We examine demographic inequality in exposure to malicious websites, an important precursor to online harm. We combine passively observed domain-level browsing data from a representative sample of more than one thousand Americans with data on malicious domains to assess who is most exposed and whether observed disparities are explained by differences in online activity. We find that 51% of respondents visited at least one malicious domain during the month-long observation period, though exposure is highly concentrated: the median user visited one malicious domain, while the 95th percentile visited eight. In unadjusted comparisons, men, African Americans, and individuals with lower levels of education are more exposed than their respective counterparts. Exposure also varies by age, with respondents under 25 the most exposed and those aged 35–49 the least exposed. These differences, however, attenuate substantially once we account for online activity, suggesting that disparities in exposure reflect differences in browsing intensity more than demographic characteristics alone.</t>
+          <t>Despite the widespread use of data-driven campaigning (DDC), there is limited conceptual clarity and empirical understanding of how political parties employ the advertising strategies of targeting (deciding which audiences to reach with ads) and tailoring (adapting ad content to specific target groups) on social media. Little is known about how these strategies, individually or in combination, influence outcome variables such as impressions of an ad, a key metric for assessing the visibility of ads in campaigns. In this paper we provide a novel theoretical conceptualization of the related yet distinct strategies of targeting and tailoring and demonstrate how they can be measured separately. We apply our framework to the 2021 German election campaign on the Meta platforms Facebook and Instagram. We do this by analyzing all ads (n = 4760) purchased by six German parties and their top candidates during the final four weeks of the campaign. We combine multi-modal manual content analysis data of ad tailoring with the Meta Ad Targeting Dataset and the Meta Ad Library to measure the two concepts independently. Our findings show that targeting and tailoring are distinct theoretical concepts that are rarely combined in practice. German parties tend to use these strategies independently. Targeting and tailoring have separate effects on ad impressions, with targeting showing a significant association while tailoring does not. These results underscore the importance of treating targeting and tailoring as distinct phenomena within DDC and provide a foundation for future research on the strategic use of social media advertising in political campaigns.</t>
         </is>
       </c>
       <c r="P15" s="6" t="inlineStr">
         <is>
-          <t>10.1080/1369118x.2026.2665253</t>
+          <t>10.1080/1369118x.2026.2652497</t>
         </is>
       </c>
       <c r="Q15" s="6" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1080/1369118x.2026.2665253</t>
+          <t>https://doi.org/10.1080/1369118x.2026.2652497</t>
         </is>
       </c>
       <c r="R15" s="2" t="inlineStr">
@@ -2080,11 +2060,11 @@
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>82</v>
-      </c>
-      <c r="B16" s="7" t="inlineStr">
-        <is>
-          <t>棕色</t>
+        <v>73</v>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
@@ -2099,67 +2079,67 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>Public discourses on sex work in Reddit digital communities: a computational approach</t>
+          <t>Examining the influence of social media cues and platform perceptions on fake news detection</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>在Reddit数字社区中关于性工作的公共讨论：一种计算方法</t>
+          <t>研究社交媒体线索和平台认知对虚假新闻检测的影响</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>Pablo Romero-Seseña, Rocío Martínez-Almanza, Alba Marsol-Gutiérrez</t>
+          <t>J.H. Tang, Barbara Millet</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>计算传播学</t>
+          <t>传统量化分析</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>社交媒体分析；主题建模；数字社区；性工作话语</t>
+          <t>社交媒体；虚假信息检测；在线实验</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>计算文本分析</t>
+          <t>在线实验</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>议题符合，且摘要明确显示：3.8 万条 Reddit 评论的结构主题模型。</t>
+          <t>议题符合，且方法证据显示：2×2×2 的社交媒体假新闻在线实验。</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>运用结构主题建模和定性内容分析，研究Reddit上r/SexWorkers和r/OnlyFans社区超3.8万条评论，归纳17个主题，揭示平台在污名化与支持之间的双重角色。</t>
+          <t>通过在线实验探究来源可信度、集体社会认可和用户对Twitter有用性感知对虚假新闻检测的影响，发现真实性偏差及平台感知降低虚假新闻识别准确性。</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>本研究探讨了数字社区在Reddit上如何讨论与性工作相关的问题，通过结构化主题建模和定性内容分析方法，分析了来自r/SexWorkers和r/OnlyFans的38,000多条评论。研究将17个主题分为五个类别：平台治理、法律框架、受害者遭遇、经济实践以及与主题无关的内容。研究结果表明，Reddit是一个具有矛盾性的网络空间：它一方面延续了对性工作者的污名化和负面态度，另一方面也为受害者提供了支持、推动了减少伤害的策略，并引发了关于监管和道德合法性的深入讨论。用户们在平台上分享自己的遭遇、提供帮助，并参与基于实践的理论构建，这凸显了Reddit作为一个非正式支持渠道和知识生产平台的双重作用。这项研究为数字受害者研究及性工作相关领域做出了贡献，为政策制定和在线受害者支持服务的发展提供了有益的见解。</t>
+          <t>本研究探讨了信息来源的可信度、集体社会的认可度以及用户对Twitter在新闻消费中的帮助程度的认知，这些因素如何影响社交媒体上虚假新闻的识别。我们进行了一项在线实验（N = 271），实验设置了2个因素（真实性：真实 vs. 虚假）× 2个因素（信息来源的可信度：可信 vs. 不可信）× 2个因素（集体社会的认可度：低 vs. 高）。实验结果表明存在“真实性偏见”：参与者中有60%认为帖子是真实的。参与者在识别真实新闻（77%）方面的准确率高于识别虚假新闻（57%）。信息来源的可信度与新闻的真实性之间存在交互作用，提高了对真实新闻的识别准确率，但降低了对虚假新闻的识别能力。集体社会的认可度对虚假新闻的识别没有显著影响。值得注意的是，用户对Twitter在获取信息方面的帮助程度的认知影响了虚假新闻的识别能力——那些认为Twitter帮助较大的用户，在识别虚假新闻时的准确率较低。这些发现为打击网络虚假信息提供了新的思路。</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>This study examines how digital communities discuss sex work related issues on Reddit, analyzing over 38,000 comments from r/SexWorkers and r/OnlyFans using structural topic modeling and qualitative content analysis. Seventeen topics were grouped into five clusters: platform governance, legal frameworks, victimization, economic practices, and off-topic content. Findings reveal Reddit as an ambivalent cyberplace, reproducing stigma and toxicity while enabling support, harm-reduction strategies, and nuanced debates on regulation and moral legitimacy. Users disclose victimization, share guidance, and engage in grassroots theorization, highlighting the platform's dual role as a site of informal support and knowledge production. This research advances digital victimology and sex work literature, offering insights for policy and the development of online victim support services.</t>
+          <t>This study investigates how source credibility, collective social endorsement, and users’ perceptions of Twitter's helpfulness for news consumption influence fake news detection on social media. We conducted a 2 (Veracity: real vs. fake) × 2 (Source Credibility: credible vs. non-credible) × 2 (Collective Social Endorsement: low vs. high) online experiment (N = 271). Results revealed a truth bias, with participants judging 60% of posts as real. Participants showed higher accuracy in identifying real news (77%) compared to fake news (57%). Source credibility interacted with news veracity, enhancing accuracy for real news while impairing detection of fake news. Collective social endorsement showed no significant effect. Notably, users’ perceptions of Twitter's helpfulness in staying informed impacted fake news detection – participants with higher perceptions of Twitter's helpfulness were less accurate in identifying fake news. The findings suggest new directions for combating online misinformation.</t>
         </is>
       </c>
       <c r="P16" s="6" t="inlineStr">
         <is>
-          <t>10.1080/1369118x.2026.2665252</t>
+          <t>10.1080/1369118x.2026.2667914</t>
         </is>
       </c>
       <c r="Q16" s="6" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1080/1369118x.2026.2665252</t>
+          <t>https://doi.org/10.1080/1369118x.2026.2667914</t>
         </is>
       </c>
       <c r="R16" s="2" t="inlineStr">
@@ -2175,7 +2155,7 @@
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="B17" s="7" t="inlineStr">
         <is>
@@ -2189,27 +2169,27 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>摘要明确</t>
+          <t>出版方全文方法明确</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>Temporal stability and cross-topic re-emergence of ideological divides on X</t>
+          <t>From player to asset: venture labor in axie infinity</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>X平台上意识形态分歧的时间稳定性与跨主题的重新出现。</t>
+          <t>从玩家到资产：《Axie Infinity》中的风险劳动（From player to asset: Venture labor in Axie Infinity）</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>Jasmin Riedl, Wiebke Drews, Andreas Dafnos, Andreas Neumeier</t>
+          <t>Daniel Nielsen, Anne Mette Thorhauge</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2219,42 +2199,46 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>社交媒体分析；政治极化；回声室；网络分析</t>
+          <t>社交媒体数据；数字劳动；游戏经济</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>网络分析＋计算文本</t>
+          <t>计算采集与预处理＋质性分析</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>议题符合，且摘要明确显示：400 万条 X 帖文、转发网络、语言对齐与回音室分数。</t>
+          <t>议题符合，且方法证据显示：Discord 导出 1.33 万条申请，使用 R、正则表达式与随机抽样后开展主题分析。</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>研究德国语境下X平台三类危机话语中极化社区的结构持续性，结合回声室分数与定性分析发现，回声室在议题内稳定并在跨议题中重现，少数高可见用户通过激活熟悉叙事起核心作用。</t>
+          <t>通过爬取Discord社区数据，分析Axie Infinity奖学金申请者的申请文本，揭示其自我资产化策略，即玩家将劳动与困境呈现为投资资产以争取机会。</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>本研究探讨了在X平台（前身为Twitter）上，极化数字社群在德语讨论中的结构持续性，这些讨论涉及三次重大危机：2021年的COVID-19疫情、2022年的俄乌战争以及2023年的加沙战争。通过对超过四百万条帖子的分析，我们结合了“回音室得分”（Echo Chamber Score, ECS）这一指标（该指标同时衡量用户之间的同质性互动以及转发网络中的语言一致性）与定性社区分析方法，来追踪具有相似意识形态的公众群体如何随时间推移以及在不同议题上发生变化。研究发现存在两种关键动态：一是同一议题内的时间稳定性；二是不同议题之间极化社群的重新出现。在单一议题下，这些“回音室”社群能够在数周内保持稳定；更值得注意的是，它们会在概念上不同的危机中重新出现，这些新出现的社群具有相似的内部凝聚力、参与者构成以及信息框架逻辑。一小部分高影响力的用户——包括（政治）意见领袖、记者、（非主流）媒体人士和政治活动家——通过重新激活熟悉的意识形态叙事，在维持这些社群的稳定中发挥了核心作用。我们的研究结果对基于特定事件或算法的解释提出了挑战，强调了反复出现的参与者网络在构建数字公共舆论中的重要作用。</t>
+          <t>本文通过Axie Infinity（Sky Mavis，引用来源：Citation2018）的案例研究，探讨了“玩即赚”（play-to-earn）游戏中的加密货币经济现象。由于进入成本较高，出现了一种“奖学金”机制：资产所有者（通常是年轻菲律宾成年人）将Axie宠物出租给申请者，并从中获取收益的一部分。我们利用从四个Discord社区收集的数据，分析了这些奖学金申请情况，发现了三种战略性的思维框架：  
+（1）将经济困境视为一种杠杆：申请者将这种不稳定的契约关系重新定义为管理者的慈善行为。  
+（2）将经济不确定性视为一种策略：申请者将自己视为能够产生收益的“资产”，同时接受不稳定的合同条款。  
+（3）将自我剥削和忠诚度视为一种资产：申请者承诺对游戏系统保持忠诚，从而将自身的奉献精神转化为一种额外的“资产”。  
+我们将这种现象称为“自我资产化”（self-assetisation）：个体将自己的劳动力、情感以及社会经济状况视为可投资的资产，同时将自己定位为劳动者和具有投机价值的对象，从而间接参与了剥削过程。</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>This study investigates the structural persistence of polarised digital communities on X (formerly Twitter) across German-language discourse on three crises: the COVID-19 pandemic (2021), the Russo-Ukrainian War (2022), and the Gaza War (2023). Analysing over four million posts, we combine the Echo Chamber Score (ECS), which captures both homophilic user interactions and linguistic alignment in repost networks, with qualitative community analysis to trace how ideologically aligned publics evolve over time and across issues. We identify two key dynamics: within-topic temporal stability and cross-topic re-emergence of polarised communities. Echo chambers remain stable over multi-week periods within a single issue, and, more notably, re-emerge across conceptually distinct crises with similar internal cohesion, actor constellations, and framing logics. A small group of highly visible users – including (political) influencers, journalists, (alternative) media, and political actors – plays a central role in sustaining these formations by reactivating familiar ideological narratives. Our findings challenge event-specific and algorithmic explanations of polarisation, highlighting the role of recurring actor networks in structuring digital publics.</t>
+          <t>This paper examines crypto economies in ‘play-to-earn’ games via a case study of Axie Infinity (Sky Mavis, Citation2018). High entry costs spawned ‘scholarships’ in which asset-owning managers lease Axies to applicants – largely young Filipino adults – in exchange for a share of earnings. Using scraped data from four Discord communities, we analyse scholarship applications, revealing three strategic framings: (1) Hardship as leverage: Applicants recast precarious contracting as managerial philanthropy. (2) Precarity as strategy: Applicants present themselves as return-generating assets while accepting precarious terms. (3) Self-exploitation and allegiance as assets: Applicants pledge loyalty to advance within the system, turning dedication into an additional asset. We theorise this as self-assetisation: individuals present labour, affect, and socio-economic circumstances as investable assets, positioning themselves as both workers and speculative value objects, being indirectly complicit in exploitation.</t>
         </is>
       </c>
       <c r="P17" s="6" t="inlineStr">
         <is>
-          <t>10.1080/1369118x.2026.2659287</t>
+          <t>10.1080/1369118x.2026.2669800</t>
         </is>
       </c>
       <c r="Q17" s="6" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1080/1369118x.2026.2659287</t>
+          <t>https://doi.org/10.1080/1369118x.2026.2669800</t>
         </is>
       </c>
       <c r="R17" s="2" t="inlineStr">
@@ -2270,11 +2254,11 @@
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>86</v>
-      </c>
-      <c r="B18" s="7" t="inlineStr">
-        <is>
-          <t>棕色</t>
+        <v>78</v>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
@@ -2289,22 +2273,22 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>2026-04-19</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>Signalling sustainability under uncertainty: how institutionalized digital platforms shape corporate green transformation in China</t>
+          <t>Bad domains: exposure to malicious content online</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>在不确定性下传递可持续性信号：制度化的数字平台如何塑造中国企业的绿色转型</t>
+          <t>糟糕的网站：在线接触恶意内容的风险</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>Li Jin, Jialin Hu</t>
+          <t>Lucas Shen, Gaurav Sood</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -2314,42 +2298,42 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>数字平台；微博数据；企业绿色转型；DID</t>
+          <t>数字不平等；在线安全；浏览数据；恶意网站</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>平台数据＋因果推断</t>
+          <t>被动数字痕迹</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>议题符合，且摘要明确显示：340 万条微博与双重差分设计。</t>
+          <t>议题符合，且方法证据显示：代表性样本的被动浏览记录与恶意域名数据匹配。</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>研究利用2007-2023年3851家中国上市公司及340万条微博帖子数据，通过DID设计发现国家运营的环境微薄平台通过政策信号和声誉压力促进企业绿色转型，增加环保投资并提高披露质量。</t>
+          <t>利用美国千人代表性样本的域名级浏览数据，结合恶意域名库，分析不同人口特征群体对恶意网站的暴露差异，发现暴露集中于少数用户，且差异主要由上网强度解释。</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>在日益加剧的气候压力下，那些处于监管环境复杂且不确定中的企业，在推进绿色转型过程中面临着持续的信息模糊性。为了理解这种模糊性在实践中是如何被缓解的，本研究探讨了国有环境类微博平台如何作为制度化的数字基础设施，影响中国企业的绿色转型。基于不完全信息理论和平台治理理论，我们提出了两种互补的机制：一是监管不确定性下的政策信号传递；二是通过公开透明度产生的声誉压力。这两种机制通过提高信息的可解释性和企业的合法性评估，重新调整了企业的战略响应。我们使用了一个包含340万条微博帖子和3851家上市公司（2007-2023年）的面板数据集，并采用了分阶段差异分析法，并进行了广泛的稳健性检验。研究发现，平台曝光度促进了企业的绿色转型，具体表现为环境投资的增加和信息披露质量的提升，这些效果通过不同的信号传递和声誉路径得以体现。当内容具有原创性、多媒体丰富性以及社会影响力时，这种促进作用更为显著；同时，在监管关注度较高的企业中，这种效应也更为明显。我们的研究结果表明，国有主导的数字平台通过促进基于解释的一致性和声誉透明度来重塑政府与市场的互动方式，而非依赖命令式的监管手段。这有助于我们更好地理解平台基础设施作为在制度不确定性下实施非强制性治理工具的作用。</t>
+          <t>关于美国数字不平等的担忧已经不仅仅局限于数字接入和技能问题，还扩展到了在线安全方面的差异。我们研究了人们在接触恶意网站方面的群体差异，这是导致在线伤害的重要因素。我们结合了来自一千多名美国人的代表性样本的被动观测到的域名级浏览数据，以及恶意网站的相关数据，来评估哪些人群更容易受到恶意网站的影响，以及这些差异是否可以由在线活动的不同所解释。研究发现，在为期一个月的观测期间，51%的受访者至少访问过一个恶意网站；不过，这种接触情况存在高度集中现象：中位数的用户只访问了一个恶意网站，而第95百分位的用户则访问了八个恶意网站。在未进行任何调整的比较中，男性、非裔美国人和受教育程度较低的人群比同龄人更容易受到恶意网站的影响。此外，接触恶意网站的情况还与年龄有关——25岁以下的受访者受影响最大，而35至49岁的受访者受影响最小。然而，一旦考虑到在线活动因素，这些差异就会显著减弱，这表明接触恶意网站的差异更多地反映了浏览行为的强度，而不仅仅是人口统计特征本身的差异。</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>Amid accelerating climate pressures, firms in fragmented and uncertain regulatory environments confront persistent informational ambiguity in pursuing green transformation. To understand how such ambiguity is mediated in practice, this study investigates how state-operated environmental microblogs function as institutionalized digital infrastructures shaping corporate green transformation in China. Drawing on incomplete information theory and platform governance, we theorize two complementary mechanisms – policy signalling under regulatory uncertainty and reputational pressure through public visibility – that recalibrate firms’ strategic responses via enhanced interpretive clarity and legitimacy evaluation. Using a panel dataset linking 3.4 million Weibo posts to 3851 listed firms (2007–2023) and a staggered difference-in-differences design with extensive robustness checks, we find that platform exposure promotes corporate green transformation, reflected in increased environmental investment and improved disclosure quality along distinct signalling and reputational pathways. These effects are strongest when content is original, multimedia-rich, and socially influential, and among firms with higher regulatory salience. Our findings suggest that state-embedded digital platforms reshape the state-market interface by enabling governance to operate through interpretive alignment and reputational visibility rather than command-based regulation, advancing understanding of platform infrastructures as tools of non-coercive governance under institutional uncertainty.</t>
+          <t>Concerns about digital inequality in the United States increasingly extend beyond access and skills to differences in online safety. We examine demographic inequality in exposure to malicious websites, an important precursor to online harm. We combine passively observed domain-level browsing data from a representative sample of more than one thousand Americans with data on malicious domains to assess who is most exposed and whether observed disparities are explained by differences in online activity. We find that 51% of respondents visited at least one malicious domain during the month-long observation period, though exposure is highly concentrated: the median user visited one malicious domain, while the 95th percentile visited eight. In unadjusted comparisons, men, African Americans, and individuals with lower levels of education are more exposed than their respective counterparts. Exposure also varies by age, with respondents under 25 the most exposed and those aged 35–49 the least exposed. These differences, however, attenuate substantially once we account for online activity, suggesting that disparities in exposure reflect differences in browsing intensity more than demographic characteristics alone.</t>
         </is>
       </c>
       <c r="P18" s="6" t="inlineStr">
         <is>
-          <t>10.1080/1369118x.2026.2659279</t>
+          <t>10.1080/1369118x.2026.2665253</t>
         </is>
       </c>
       <c r="Q18" s="6" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1080/1369118x.2026.2659279</t>
+          <t>https://doi.org/10.1080/1369118x.2026.2665253</t>
         </is>
       </c>
       <c r="R18" s="2" t="inlineStr">
@@ -2365,11 +2349,11 @@
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>89</v>
-      </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>无</t>
+        <v>82</v>
+      </c>
+      <c r="B19" s="7" t="inlineStr">
+        <is>
+          <t>棕色</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
@@ -2384,22 +2368,22 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>Protest movements and the mainstreaming of radical and extremist ideologies: the case of COVID-19 protests</t>
+          <t>Public discourses on sex work in Reddit digital communities: a computational approach</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>抗议运动与激进及极端主义意识形态的主流化：以COVID-19抗议活动为例</t>
+          <t>在Reddit数字社区中关于性工作的公共讨论：一种计算方法</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>Sophia Rothut, Heidi Schulze, Diana Rieger, M Lechner, Brigitte Naderer</t>
+          <t>Pablo Romero-Seseña, Rocío Martínez-Almanza, Alba Marsol-Gutiérrez</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
@@ -2409,42 +2393,42 @@
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>社交媒体；网络分析；激进意识形态；抗议运动；Telegram</t>
+          <t>社交媒体分析；主题建模；数字社区；性工作话语</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>多层平台数据分析</t>
+          <t>计算文本分析</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>议题符合，且摘要明确显示：多层 Telegram 数据、纵向内容、URL 与网络分析。</t>
+          <t>议题符合，且方法证据显示：3.8 万条 Reddit 评论的结构主题模型。</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>研究德国新冠抗议运动‘Querdenken’如何通过社交媒体促进激进和极端意识形态的主流化，使用内容分析、URL分析和网络分析三角验证，揭示其反精英和阴谋叙事及与极右翼社区的连接。</t>
+          <t>运用结构主题建模和定性内容分析，研究Reddit上r/SexWorkers和r/OnlyFans社区超3.8万条评论，归纳17个主题，揭示平台在污名化与支持之间的双重角色。</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>激进和极端主义分子利用社交媒体将他们的世界观悄然融入日常讨论中。基于“主流化理论”（mainstreaming theory），我们探讨了抗议运动是否能够通过创造有利于公众向极端立场转变的环境来促进这一过程。我们将“抗议促进的主流化”（Protest-Facilitated Mainstreaming, PFM）定义为一种通过社交媒体上的内容和连接机制发挥作用的过程，并以德国针对COVID-19措施的抗议运动“Querdenken”为例进行研究。该运动吸引了来自不同背景的同情者的关注。我们利用Telegram的多层数据集，采用定量计算方法，结合纵向内容分析、URL分析和网络分析来研究这一现象。多种方法得出的结果一致表明，“Querdenken”的内容使激进思想更容易被公众接受。研究发现，抗议活动中的沟通主要围绕反精英和阴谋论主题展开，同时越来越多地引用替代性或党派性的信息来源以及边缘化群体。抗议渠道在结构上与德国及国际上的极右翼和阴谋论团体紧密相连。这些现象共同表明，抗议运动能够逐步降低人们接触、重新审视和传播边缘化观点及激进分子的门槛，而这正是主流化的核心过程。最后，我们讨论了这些发现对其他抗议运动以及社会和（平台）治理的启示意义。</t>
+          <t>本研究探讨了数字社区在Reddit上如何讨论与性工作相关的问题，通过结构化主题建模和定性内容分析方法，分析了来自r/SexWorkers和r/OnlyFans的38,000多条评论。研究将17个主题分为五个类别：平台治理、法律框架、受害者遭遇、经济实践以及与主题无关的内容。研究结果表明，Reddit是一个具有矛盾性的网络空间：它一方面延续了对性工作者的污名化和负面态度，另一方面也为受害者提供了支持、推动了减少伤害的策略，并引发了关于监管和道德合法性的深入讨论。用户们在平台上分享自己的遭遇、提供帮助，并参与基于实践的理论构建，这凸显了Reddit作为一个非正式支持渠道和知识生产平台的双重作用。这项研究为数字受害者研究及性工作相关领域做出了贡献，为政策制定和在线受害者支持服务的发展提供了有益的见解。</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>Radical and extremist actors leverage social media to subtly embed their worldviews into everyday discourse. Drawing on mainstreaming theory, we examine whether protest movements can facilitate such processes by creating environments conducive to a public shift toward the extremes. We conceptualize protest-facilitated mainstreaming (PFM) as a process that operates through content and connective mechanisms on social media and explore the case of the German COVID-19-measures protest movement ‘Querdenken,’ which sparked interest from sympathizers of various backgrounds. Using a multi-layered Telegram dataset in a quantitative-computational approach, we triangulate longitudinal content analysis, URL analysis, and network analysis. Across methods, a consistent picture emerged, demonstrating how Querdenken’s content made radical ideas more accessible. Our findings reveal that protest communication was dominated by anti-elite and conspiratorial narratives, with increasing references to alternative/partisan sources and fringe actors. Protest channels were structurally embedded in and bridged to German and international far-right and conspiracist communities. Together, these patterns show how protest movements can lower the threshold for encountering, revisiting, and recirculating fringe frames and actors over time, which is at the core of mainstreaming. We conclude by discussing the applicability of our findings to other protest movements and the implications for society and (platform) governance.</t>
+          <t>This study examines how digital communities discuss sex work related issues on Reddit, analyzing over 38,000 comments from r/SexWorkers and r/OnlyFans using structural topic modeling and qualitative content analysis. Seventeen topics were grouped into five clusters: platform governance, legal frameworks, victimization, economic practices, and off-topic content. Findings reveal Reddit as an ambivalent cyberplace, reproducing stigma and toxicity while enabling support, harm-reduction strategies, and nuanced debates on regulation and moral legitimacy. Users disclose victimization, share guidance, and engage in grassroots theorization, highlighting the platform's dual role as a site of informal support and knowledge production. This research advances digital victimology and sex work literature, offering insights for policy and the development of online victim support services.</t>
         </is>
       </c>
       <c r="P19" s="6" t="inlineStr">
         <is>
-          <t>10.1080/1369118x.2026.2654668</t>
+          <t>10.1080/1369118x.2026.2665252</t>
         </is>
       </c>
       <c r="Q19" s="6" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1080/1369118x.2026.2654668</t>
+          <t>https://doi.org/10.1080/1369118x.2026.2665252</t>
         </is>
       </c>
       <c r="R19" s="2" t="inlineStr">
@@ -2460,11 +2444,11 @@
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>90</v>
-      </c>
-      <c r="B20" s="4" t="inlineStr">
-        <is>
-          <t>黄色</t>
+        <v>84</v>
+      </c>
+      <c r="B20" s="7" t="inlineStr">
+        <is>
+          <t>棕色</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
@@ -2479,22 +2463,22 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>Navigating intersectional expectations: a computational multimodal analysis of the effects of identities and communication styles on public engagement with science on TikTok</t>
+          <t>Temporal stability and cross-topic re-emergence of ideological divides on X</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>应对交叉性期望：一项关于身份和沟通风格对TikTok上公众参与科学活动影响的计算多模态分析</t>
+          <t>X平台上意识形态分歧的时间稳定性与跨主题的重新出现。</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>Yuhan Li, Hang Lu, Chao Yu</t>
+          <t>Jasmin Riedl, Wiebke Drews, Andreas Dafnos, Andreas Neumeier</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2504,42 +2488,42 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>计算多模态分析；TikTok；科学传播；身份与参与</t>
+          <t>社交媒体分析；政治极化；回声室；网络分析</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>计算多模态分析</t>
+          <t>网络分析＋计算文本</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>议题符合，且摘要明确显示：TikTok 视频与评论的计算多模态分析。</t>
+          <t>议题符合，且方法证据显示：400 万条 X 帖文、转发网络、语言对齐与回音室分数。</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>基于10,800个视频和448,002条评论，分析TikTok科学传播中传播者性别、种族与沟通风格如何影响公众参与，发现交叉身份导致参与差异。</t>
+          <t>研究德国语境下X平台三类危机话语中极化社区的结构持续性，结合回声室分数与定性分析发现，回声室在议题内稳定并在跨议题中重现，少数高可见用户通过激活熟悉叙事起核心作用。</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>传播学研究早已证实了传播者的社会身份对说服效果的影响。然而，很少有研究从交叉性（intersectional）的角度来探讨身份因素，或系统地分析沟通风格的有效性是如何通过基于身份的期望来评估的。本研究聚焦于数字科学传播，利用了一个包含10,800个视频和448,002条评论的独特多模态数据集，探讨了传播者的性别、种族及其与沟通风格的互动如何影响人们的参与度和评论行为。研究结果表明，有色人种女性（尤其是拉丁裔/西班牙裔女性）在在线传播科学信息时常常面临角色冲突的问题，她们的参与度明显低于那些仅具有单一边缘化身份的传播者。观众对那些采用与自身身份相符的沟通风格的在线传播者更感兴趣（例如，女性倾向于使用情感化的语言，而男性则更倾向于使用直接、具有说服力的语言）。这项研究揭示了与身份相关的认知机制如何逐渐塑造人们在以视觉为主的平台上的参与行为。</t>
+          <t>本研究探讨了在X平台（前身为Twitter）上，极化数字社群在德语讨论中的结构持续性，这些讨论涉及三次重大危机：2021年的COVID-19疫情、2022年的俄乌战争以及2023年的加沙战争。通过对超过四百万条帖子的分析，我们结合了“回音室得分”（Echo Chamber Score, ECS）这一指标（该指标同时衡量用户之间的同质性互动以及转发网络中的语言一致性）与定性社区分析方法，来追踪具有相似意识形态的公众群体如何随时间推移以及在不同议题上发生变化。研究发现存在两种关键动态：一是同一议题内的时间稳定性；二是不同议题之间极化社群的重新出现。在单一议题下，这些“回音室”社群能够在数周内保持稳定；更值得注意的是，它们会在概念上不同的危机中重新出现，这些新出现的社群具有相似的内部凝聚力、参与者构成以及信息框架逻辑。一小部分高影响力的用户——包括（政治）意见领袖、记者、（非主流）媒体人士和政治活动家——通过重新激活熟悉的意识形态叙事，在维持这些社群的稳定中发挥了核心作用。我们的研究结果对基于特定事件或算法的解释提出了挑战，强调了反复出现的参与者网络在构建数字公共舆论中的重要作用。</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>Communication research has long established the impact of the communicator's social identity on persuasion. However, few communication studies have applied an intersectional lens to examine identities or systematically examined how the effectiveness of communication styles has been evaluated through identity-based expectations. Focusing on digital science communication, we used a unique multimodal dataset of 10,800 videos and 448,002 comments to explore how people's engagement and commenting behaviors were influenced by a communicator's gender, race, and their interaction with communication styles. Our results show that women of color, particularly Latina/Hispanic women, often faced dual role incongruity when communicating science online, receiving significantly lower engagement than those with a single marginalized identity. Audiences showed more engagement with online communicators who adopted role-congruent communication styles to communicate science (i.e., favoring affective tone from women and aggressiveness from men). This study sheds light on how identity-related heuristics increasingly shape engagement behaviors in visual-oriented platforms.</t>
+          <t>This study investigates the structural persistence of polarised digital communities on X (formerly Twitter) across German-language discourse on three crises: the COVID-19 pandemic (2021), the Russo-Ukrainian War (2022), and the Gaza War (2023). Analysing over four million posts, we combine the Echo Chamber Score (ECS), which captures both homophilic user interactions and linguistic alignment in repost networks, with qualitative community analysis to trace how ideologically aligned publics evolve over time and across issues. We identify two key dynamics: within-topic temporal stability and cross-topic re-emergence of polarised communities. Echo chambers remain stable over multi-week periods within a single issue, and, more notably, re-emerge across conceptually distinct crises with similar internal cohesion, actor constellations, and framing logics. A small group of highly visible users – including (political) influencers, journalists, (alternative) media, and political actors – plays a central role in sustaining these formations by reactivating familiar ideological narratives. Our findings challenge event-specific and algorithmic explanations of polarisation, highlighting the role of recurring actor networks in structuring digital publics.</t>
         </is>
       </c>
       <c r="P20" s="6" t="inlineStr">
         <is>
-          <t>10.1080/1369118x.2026.2659280</t>
+          <t>10.1080/1369118x.2026.2659287</t>
         </is>
       </c>
       <c r="Q20" s="6" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1080/1369118x.2026.2659280</t>
+          <t>https://doi.org/10.1080/1369118x.2026.2659287</t>
         </is>
       </c>
       <c r="R20" s="2" t="inlineStr">
@@ -2555,11 +2539,11 @@
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>92</v>
-      </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>无</t>
+        <v>86</v>
+      </c>
+      <c r="B21" s="7" t="inlineStr">
+        <is>
+          <t>棕色</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
@@ -2574,22 +2558,22 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-19</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>Wrap your head around it: algorithmic self-making and performances of taste on Spotify Wrapped</t>
+          <t>Signalling sustainability under uncertainty: how institutionalized digital platforms shape corporate green transformation in China</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>理解这个概念：Spotify Wrapped中的算法自我生成机制与用户品味表现</t>
+          <t>在不确定性下传递可持续性信号：制度化的数字平台如何塑造中国企业的绿色转型</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>Vanessa Valiati, Ludmila Lupinacci, Felipe Bonow Soares</t>
+          <t>Li Jin, Jialin Hu</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
@@ -2599,42 +2583,42 @@
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>算法想象；Spotify Wrapped；社交网络分析；平台研究</t>
+          <t>数字平台；微博数据；企业绿色转型；DID</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>网络分析＋混合方法</t>
+          <t>平台数据＋因果推断</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>议题符合，且摘要明确显示：X 帖文的社会网络分析，并与访谈互证。</t>
+          <t>议题符合，且方法证据显示：340 万条微博与双重差分设计。</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>研究巴西用户对Spotify Wrapped的算法想象与品味表演，通过Twitter社交网络分析和访谈，揭示算法事件中分散、短暂共享体验及受限能动性。</t>
+          <t>研究利用2007-2023年3851家中国上市公司及340万条微博帖子数据，通过DID设计发现国家运营的环境微薄平台通过政策信号和声誉压力促进企业绿色转型，增加环保投资并提高披露质量。</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>本文探讨了巴西用户对Spotify Wrapped的认知与理解方式，分析了围绕这一功能的算法机制（Bucher, 2017），以及音乐消费的数据化处理和可视化展示如何影响用户的品味表达（Airoldi, 2021; Prey, 2018）。我们将Spotify Wrapped视为一个年度性的“算法事件”（Annabell &amp; Rasmussen, 2024），并将其置于关于音乐平台化、算法在身份构建中的作用、数字记忆以及媒体事件的持续讨论背景之中。通过对Twitter/X上的相关帖子进行社会网络分析，以及对38位Spotify用户的半结构化访谈进行主题分析，我们发现：在巴西，Spotify Wrapped的“事件性”特征表现为分散的、聚集的但联系较为松散的现象；用户们通过这种平台体验产生短暂、流动且易逝的共享感受与认同感，而非形成稳定的社区。研究还强调了用户在日常使用中如何巧妙地运用数据化消费和算法机制来获得理想的结果，同时希望算法能够理解用户的听歌情境，仅记录那些值得被纳入Spotify Wrapped统计的数据。最后，我们指出了这一现象与现有关于日常数据文化理论（Burgess et al., 2022）之间的连续性与差异性，并为音乐流媒体研究、平台研究及算法批判理论的发展做出了贡献。</t>
+          <t>在日益加剧的气候压力下，那些处于监管环境复杂且不确定中的企业，在推进绿色转型过程中面临着持续的信息模糊性。为了理解这种模糊性在实践中是如何被缓解的，本研究探讨了国有环境类微博平台如何作为制度化的数字基础设施，影响中国企业的绿色转型。基于不完全信息理论和平台治理理论，我们提出了两种互补的机制：一是监管不确定性下的政策信号传递；二是通过公开透明度产生的声誉压力。这两种机制通过提高信息的可解释性和企业的合法性评估，重新调整了企业的战略响应。我们使用了一个包含340万条微博帖子和3851家上市公司（2007-2023年）的面板数据集，并采用了分阶段差异分析法，并进行了广泛的稳健性检验。研究发现，平台曝光度促进了企业的绿色转型，具体表现为环境投资的增加和信息披露质量的提升，这些效果通过不同的信号传递和声誉路径得以体现。当内容具有原创性、多媒体丰富性以及社会影响力时，这种促进作用更为显著；同时，在监管关注度较高的企业中，这种效应也更为明显。我们的研究结果表明，国有主导的数字平台通过促进基于解释的一致性和声誉透明度来重塑政府与市场的互动方式，而非依赖命令式的监管手段。这有助于我们更好地理解平台基础设施作为在制度不确定性下实施非强制性治理工具的作用。</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>This paper examines how Spotify Wrapped is perceived and understood by Brazilian users, exploring the algorithmic imaginaries (Bucher, 2017). that surround its appropriation in everyday life and how the datafication and the dashboarding of music consumption are incorporated into performances of taste (Airoldi, 2021; Prey, 2018). Focusing on Wrapped as an annual ‘algorithmic event' (Annabell &amp; Rasmussen, 2024) we contextualise it as part of ongoing discussions on the platformisation of music and the algorithmic mediation of identity, as well as debates about digital memory and media events. Based on a social network analysis of posts collected from Twitter/X and a thematic analysis of semi-structured interviews with 38 Spotify users, we argue that in Brazil the ‘eventness' of Spotify Wrapped is distributed, clustered but sparsely connected, and marked by fleeting, fluid and ephemeral feelings of shared experience and recognition rather than by enduring communities. Foregrounding ordinary acts of constrained agency (Siles, et al., 2022), our findings also indicate that Brazilian users playfully and skilfully incorporate the perceived logics of datafied consumption and algorithmic mediation to produce desirable Wrapped results - whilst also hoping that 'the algorithm’ would be able to understand listening contexts and only capture those sessions that are 'Wrapped-worthy'. We conclude by highlighting the continuities and specificities of the phenomenon in relation to existing theorisations of everyday data cultures (Burgess et al., 2022). In doing so, we contribute to the growing body of literature on music streaming studies, platform studies, and critical algorithm studies.</t>
+          <t>Amid accelerating climate pressures, firms in fragmented and uncertain regulatory environments confront persistent informational ambiguity in pursuing green transformation. To understand how such ambiguity is mediated in practice, this study investigates how state-operated environmental microblogs function as institutionalized digital infrastructures shaping corporate green transformation in China. Drawing on incomplete information theory and platform governance, we theorize two complementary mechanisms – policy signalling under regulatory uncertainty and reputational pressure through public visibility – that recalibrate firms’ strategic responses via enhanced interpretive clarity and legitimacy evaluation. Using a panel dataset linking 3.4 million Weibo posts to 3851 listed firms (2007–2023) and a staggered difference-in-differences design with extensive robustness checks, we find that platform exposure promotes corporate green transformation, reflected in increased environmental investment and improved disclosure quality along distinct signalling and reputational pathways. These effects are strongest when content is original, multimedia-rich, and socially influential, and among firms with higher regulatory salience. Our findings suggest that state-embedded digital platforms reshape the state-market interface by enabling governance to operate through interpretive alignment and reputational visibility rather than command-based regulation, advancing understanding of platform infrastructures as tools of non-coercive governance under institutional uncertainty.</t>
         </is>
       </c>
       <c r="P21" s="6" t="inlineStr">
         <is>
-          <t>10.1080/1369118x.2026.2647352</t>
+          <t>10.1080/1369118x.2026.2659279</t>
         </is>
       </c>
       <c r="Q21" s="6" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1080/1369118x.2026.2647352</t>
+          <t>https://doi.org/10.1080/1369118x.2026.2659279</t>
         </is>
       </c>
       <c r="R21" s="2" t="inlineStr">
@@ -2650,11 +2634,11 @@
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>94</v>
-      </c>
-      <c r="B22" s="4" t="inlineStr">
-        <is>
-          <t>黄色</t>
+        <v>89</v>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
@@ -2669,22 +2653,22 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>Online interactions and the gravity model</t>
+          <t>Protest movements and the mainstreaming of radical and extremist ideologies: the case of COVID-19 protests</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>在线互动与引力模型</t>
+          <t>抗议运动与激进及极端主义意识形态的主流化：以COVID-19抗议活动为例</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>Constantin Bürgi, Zuzanna Studnicka</t>
+          <t>Sophia Rothut, Heidi Schulze, Diana Rieger, M Lechner, Brigitte Naderer</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -2694,42 +2678,42 @@
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>在线互动；数字全球化；多人在线游戏；大规模数据集；计算社会科学</t>
+          <t>社交媒体；网络分析；激进意识形态；抗议运动；Telegram</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>大规模行为数据建模</t>
+          <t>多层平台数据分析</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>议题符合，且摘要明确显示：2500 万场在线比赛的个体数据与结构引力模型。</t>
+          <t>议题符合，且方法证据显示：多层 Telegram 数据、纵向内容、URL 与网络分析。</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>论文基于《帝国时代II》2500万场多人比赛数据，构建在线互动模型并用结构重力模型估计，发现文化邻近性和外部社交网络对跨国在线互动有重要影响，为数字全球化和在线社区研究提供实证。</t>
+          <t>研究德国新冠抗议运动‘Querdenken’如何通过社交媒体促进激进和极端意识形态的主流化，使用内容分析、URL分析和网络分析三角验证，揭示其反精英和阴谋叙事及与极右翼社区的连接。</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>我们研究了全球范围内人们之间的数字互动。我们开发了一个简单的在线互动模型，该模型融合了来自传播学的见解，并可以使用国际经济学中使用的结构引力模型进行测试。为了估计我们的模型，我们利用《帝国时代II：决定版》这款游戏中超过2500万场多人对战的数据集，计算了不同国家之间以及同一国家内部玩家之间的在线互动量。我们发现，即使物理交易成本可以忽略不计，文化相似性和外部社交网络在塑造在线互动方面仍然起着关键作用。这表明，影响物理贸易流动的相同因素在网络上仍然具有重要意义。我们的研究结果对数字全球化、在线平台的营销策略以及在线社区的演变具有更广泛的意义。</t>
+          <t>激进和极端主义分子利用社交媒体将他们的世界观悄然融入日常讨论中。基于“主流化理论”（mainstreaming theory），我们探讨了抗议运动是否能够通过创造有利于公众向极端立场转变的环境来促进这一过程。我们将“抗议促进的主流化”（Protest-Facilitated Mainstreaming, PFM）定义为一种通过社交媒体上的内容和连接机制发挥作用的过程，并以德国针对COVID-19措施的抗议运动“Querdenken”为例进行研究。该运动吸引了来自不同背景的同情者的关注。我们利用Telegram的多层数据集，采用定量计算方法，结合纵向内容分析、URL分析和网络分析来研究这一现象。多种方法得出的结果一致表明，“Querdenken”的内容使激进思想更容易被公众接受。研究发现，抗议活动中的沟通主要围绕反精英和阴谋论主题展开，同时越来越多地引用替代性或党派性的信息来源以及边缘化群体。抗议渠道在结构上与德国及国际上的极右翼和阴谋论团体紧密相连。这些现象共同表明，抗议运动能够逐步降低人们接触、重新审视和传播边缘化观点及激进分子的门槛，而这正是主流化的核心过程。最后，我们讨论了这些发现对其他抗议运动以及社会和（平台）治理的启示意义。</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>We study digital interactions between people across the globe. We develop a simple model of online interactions that incorporates insights from communication studies and can be tested using the structural gravity model used in international economics. To estimate our model, we calculate the volume of online interactions between players in different countries and within a country, using a unique individual-level dataset from over 25 million multiplayer matches in the game Age of Empires II: Definitive Edition. We find that cultural proximity and external social networks are crucial in shaping online interactions, even when physical trade costs are negligible. This suggests that the same factors underlying physical trade flows continue to matter online. Our insights offer broader implications for digital globalization, marketing strategies of online platforms, and the evolution of online communities.</t>
+          <t>Radical and extremist actors leverage social media to subtly embed their worldviews into everyday discourse. Drawing on mainstreaming theory, we examine whether protest movements can facilitate such processes by creating environments conducive to a public shift toward the extremes. We conceptualize protest-facilitated mainstreaming (PFM) as a process that operates through content and connective mechanisms on social media and explore the case of the German COVID-19-measures protest movement ‘Querdenken,’ which sparked interest from sympathizers of various backgrounds. Using a multi-layered Telegram dataset in a quantitative-computational approach, we triangulate longitudinal content analysis, URL analysis, and network analysis. Across methods, a consistent picture emerged, demonstrating how Querdenken’s content made radical ideas more accessible. Our findings reveal that protest communication was dominated by anti-elite and conspiratorial narratives, with increasing references to alternative/partisan sources and fringe actors. Protest channels were structurally embedded in and bridged to German and international far-right and conspiracist communities. Together, these patterns show how protest movements can lower the threshold for encountering, revisiting, and recirculating fringe frames and actors over time, which is at the core of mainstreaming. We conclude by discussing the applicability of our findings to other protest movements and the implications for society and (platform) governance.</t>
         </is>
       </c>
       <c r="P22" s="6" t="inlineStr">
         <is>
-          <t>10.1080/1369118x.2026.2648695</t>
+          <t>10.1080/1369118x.2026.2654668</t>
         </is>
       </c>
       <c r="Q22" s="6" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1080/1369118x.2026.2648695</t>
+          <t>https://doi.org/10.1080/1369118x.2026.2654668</t>
         </is>
       </c>
       <c r="R22" s="2" t="inlineStr">
@@ -2745,7 +2729,7 @@
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>97</v>
+        <v>90</v>
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
@@ -2764,67 +2748,67 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>Social media platforms and the spreading of hate speech targeting sexual and gender minorities: a scoping review</t>
+          <t>Navigating intersectional expectations: a computational multimodal analysis of the effects of identities and communication styles on public engagement with science on TikTok</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>社交媒体平台与针对性少数群体和性别少数群体的仇恨言论的传播：一项范围综述</t>
+          <t>应对交叉性期望：一项关于身份和沟通风格对TikTok上公众参与科学活动影响的计算多模态分析</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>Anne Møller Clausen, Lena Frischlich, Peter Mayer</t>
+          <t>Yuhan Li, Hang Lu, Chao Yu</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>综述</t>
+          <t>计算传播学</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>仇恨言论；社交媒体平台；BERTopic；平台可供性</t>
+          <t>计算多模态分析；TikTok；科学传播；身份与参与</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>计算型综述</t>
+          <t>计算多模态分析</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>议题符合，且摘要明确显示：145 篇全文的 BERTopic 建模。</t>
+          <t>议题符合，且方法证据显示：TikTok 视频与评论的计算多模态分析。</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>通过范围综述和BERTopic主题建模，系统梳理了145篇研究，分析不同社交媒体平台特性（内容模态、可供性）与针对性少数群体仇恨言论传播的关系，发现Twitter/X研究最多，文本内容为主，并呼吁关注视觉内容与平台动态。</t>
+          <t>基于10,800个视频和448,002条评论，分析TikTok科学传播中传播者性别、种族与沟通风格如何影响公众参与，发现交叉身份导致参与差异。</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>如今，社交媒体用户可以访问各种具有不同特性的社交媒体平台，这些平台为仇恨言论的传播提供了不同的机会。然而，关于社交媒体平台（包括其内容形式和功能特性）与针对边缘化群体（如性少数群体和性别少数群体（LGBTQIA+）的仇恨言论传播之间的关系，我们知之甚少。本研究通过开展一项基于PRISMA扩展框架（PRISMA-ScR）的文献综述来填补这一知识空白。考虑到仇恨言论研究的跨学科性质，我们检索了专门针对传播学的学术数据库以及综合性学术数据库（Communication Source、Scopus、Web of Science和Academic Search Premier）。最终共收集到145篇全文论文。分析采用了混合方法：手动对论文中的社交媒体平台、内容形式和功能特性进行了编码，并使用BERTopic模型来识别文献中的关键主题。研究结果表明，Twitter/X是最常被研究的平台，其次是YouTube、Facebook和Instagram；在内容形式方面，文本内容是最受关注的研究对象，而视觉和音视频内容则相对较少被研究。虽然很少有论文明确提及平台的功能特性，但部分研究指出匿名性和可见性是促进仇恨言论传播的因素。主要研究焦点集中在仇恨言论检测模型和数据集的开发上。我们的研究结果呼吁未来的研究关注其他社交媒体平台、视觉和音视频内容，以及平台的功能特性，并将研究重点从单纯的检测模型开发扩展到更广泛的角度，以深入理解平台动态如何影响仇恨言论的传播。</t>
+          <t>传播学研究早已证实了传播者的社会身份对说服效果的影响。然而，很少有研究从交叉性（intersectional）的角度来探讨身份因素，或系统地分析沟通风格的有效性是如何通过基于身份的期望来评估的。本研究聚焦于数字科学传播，利用了一个包含10,800个视频和448,002条评论的独特多模态数据集，探讨了传播者的性别、种族及其与沟通风格的互动如何影响人们的参与度和评论行为。研究结果表明，有色人种女性（尤其是拉丁裔/西班牙裔女性）在在线传播科学信息时常常面临角色冲突的问题，她们的参与度明显低于那些仅具有单一边缘化身份的传播者。观众对那些采用与自身身份相符的沟通风格的在线传播者更感兴趣（例如，女性倾向于使用情感化的语言，而男性则更倾向于使用直接、具有说服力的语言）。这项研究揭示了与身份相关的认知机制如何逐渐塑造人们在以视觉为主的平台上的参与行为。</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>Today, social media users can access various social media platforms with different characteristics that offer distinct opportunity structures for the spread of hate speech. Yet little is known about the relationship between social media platforms with their unique characteristics, including content modalities and affordances, and the spreading of hate speech towards marginalized groups, including sexual and gender minorities (LGBTQIA+). This scoping review contributes to closing this gap. We conducted a scoping review according to the PRISMA Extension for Scoping Reviews (PRISMA-ScR). To account for the interdisciplinary nature of hate speech research, we searched communication-specific and broad academic databases (Communication Source, Scopus, Web of Science and Academic Search Premier). The full-text database includes n = 145 full-text papers. The analysis encompassed a mixed-methods approach: Texts were manually coded for social media platforms, content modalities and affordances, and a BERTopic model was trained to identify key topics across literature. Findings show that Twitter/X was the most researched platform, followed by YouTube, Facebook, and Instagram. Textual content was the most researched content modality, compared to visual and audiovisual content. Few publications explicitly mentioned platform affordances, while some pointed to anonymity and visibility as facilitators of the spreading of hate speech. Key topics revolved around the development of models and datasets for hate speech detection. Our findings call for future studies to investigate alternative platforms, visual and audiovisual content, platform affordances, and apply a research focus beyond the development of detection models to understand how platform dynamics contribute to the spreading of hate speech.</t>
+          <t>Communication research has long established the impact of the communicator's social identity on persuasion. However, few communication studies have applied an intersectional lens to examine identities or systematically examined how the effectiveness of communication styles has been evaluated through identity-based expectations. Focusing on digital science communication, we used a unique multimodal dataset of 10,800 videos and 448,002 comments to explore how people's engagement and commenting behaviors were influenced by a communicator's gender, race, and their interaction with communication styles. Our results show that women of color, particularly Latina/Hispanic women, often faced dual role incongruity when communicating science online, receiving significantly lower engagement than those with a single marginalized identity. Audiences showed more engagement with online communicators who adopted role-congruent communication styles to communicate science (i.e., favoring affective tone from women and aggressiveness from men). This study sheds light on how identity-related heuristics increasingly shape engagement behaviors in visual-oriented platforms.</t>
         </is>
       </c>
       <c r="P23" s="6" t="inlineStr">
         <is>
-          <t>10.1080/1369118x.2026.2636138</t>
+          <t>10.1080/1369118x.2026.2659280</t>
         </is>
       </c>
       <c r="Q23" s="6" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1080/1369118x.2026.2636138</t>
+          <t>https://doi.org/10.1080/1369118x.2026.2659280</t>
         </is>
       </c>
       <c r="R23" s="2" t="inlineStr">
@@ -2840,11 +2824,11 @@
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>100</v>
-      </c>
-      <c r="B24" s="7" t="inlineStr">
-        <is>
-          <t>棕色</t>
+        <v>92</v>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
@@ -2859,22 +2843,22 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>Racism, resistance, and Reddit: how popular culture sparks online reckonings</t>
+          <t>Wrap your head around it: algorithmic self-making and performances of taste on Spotify Wrapped</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>种族主义、抵抗与Reddit：流行文化如何引发网络上的讨论与反思</t>
+          <t>理解这个概念：Spotify Wrapped中的算法自我生成机制与用户品味表现</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>Sherry Mason, Tawfiq Ammari</t>
+          <t>Vanessa Valiati, Ludmila Lupinacci, Felipe Bonow Soares</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -2884,42 +2868,42 @@
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>社交媒体分析；主题建模；批判性话语分析；Reddit；种族叙事</t>
+          <t>算法想象；Spotify Wrapped；社交网络分析；平台研究</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>计算文本分析</t>
+          <t>网络分析＋混合方法</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>议题符合，且摘要明确显示：3879 条 Reddit 评论的主题建模。</t>
+          <t>议题符合，且方法证据显示：X 帖文的社会网络分析，并与访谈互证。</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>研究分析Reddit用户对两部种族主题剧集的评论，结合主题建模与批判话语分析，揭示用户角色流动及平台匿名性对种族讨论的影响。</t>
+          <t>研究巴西用户对Spotify Wrapped的算法想象与品味表演，通过Twitter社交网络分析和访谈，揭示算法事件中分散、短暂共享体验及受限能动性。</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>本研究探讨了Reddit用户如何参与HBO电视剧《守望者》（2019年）和《洛夫克拉夫特之乡》（2020年）中的种族叙事。这两部剧集重新诠释了历史上的种族创伤。我们运用多步骤流动理论（multistep flow theory）和批判性技术文化话语分析（critical technocultural discourse analysis，CTDA），通过对3,879条Reddit评论进行主题建模和批判性话语分析来展开研究。我们识别出三种动态的社会角色：支持者（advocates）、反对者（adversaries）和适应者（adapters），并分析了用户在这些角色之间如何转换以应对相关的种族议题。研究结果表明，Reddit的匿名特性影响了角色的流动性、意见领导力以及用户的道德参与度。反对者认为剧中的种族主义和暴力情节被夸大了，而支持者则分享自己的经历和资源来反驳这些观点；适应者则随着时间的推移改变了自己的立场，这表明在线公众能够促进对种族问题的批判性思考。本研究强调了流行文化和参与式平台在塑造关于种族和历史记忆的集体意义构建过程中的相互作用。</t>
+          <t>本文探讨了巴西用户对Spotify Wrapped的认知与理解方式，分析了围绕这一功能的算法机制（Bucher, 2017），以及音乐消费的数据化处理和可视化展示如何影响用户的品味表达（Airoldi, 2021; Prey, 2018）。我们将Spotify Wrapped视为一个年度性的“算法事件”（Annabell &amp; Rasmussen, 2024），并将其置于关于音乐平台化、算法在身份构建中的作用、数字记忆以及媒体事件的持续讨论背景之中。通过对Twitter/X上的相关帖子进行社会网络分析，以及对38位Spotify用户的半结构化访谈进行主题分析，我们发现：在巴西，Spotify Wrapped的“事件性”特征表现为分散的、聚集的但联系较为松散的现象；用户们通过这种平台体验产生短暂、流动且易逝的共享感受与认同感，而非形成稳定的社区。研究还强调了用户在日常使用中如何巧妙地运用数据化消费和算法机制来获得理想的结果，同时希望算法能够理解用户的听歌情境，仅记录那些值得被纳入Spotify Wrapped统计的数据。最后，我们指出了这一现象与现有关于日常数据文化理论（Burgess et al., 2022）之间的连续性与差异性，并为音乐流媒体研究、平台研究及算法批判理论的发展做出了贡献。</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>This study examines how Reddit users engaged with the racial narratives of HBO’s Watchmen (2019) and Lovecraft Country (2020), two television series that reimagine historical racial trauma. Drawing on multistep flow theory and critical technocultural discourse analysis (CTDA), we analyze 3,879 Reddit comments using topic modeling and critical discourse analysis. We identify three dynamic social roles – advocates, adversaries, and adaptives – and explore how users move between them in response to racial discourse. Findings reveal how Reddit’s pseudonymous affordances shape role fluidity, opinion leadership, and moral engagement. While adversaries minimized or rejected the shows’ portrayals of racism and violence as exaggerated, advocates shared standpoint experiences and resources to challenge these claims. Adaptive users shifted perspectives over time, demonstrating how online publics can foster critical racial learning. This research highlights how popular culture and participatory platforms intersect in shaping collective meaning-making around race and historical memory.</t>
+          <t>This paper examines how Spotify Wrapped is perceived and understood by Brazilian users, exploring the algorithmic imaginaries (Bucher, 2017). that surround its appropriation in everyday life and how the datafication and the dashboarding of music consumption are incorporated into performances of taste (Airoldi, 2021; Prey, 2018). Focusing on Wrapped as an annual ‘algorithmic event' (Annabell &amp; Rasmussen, 2024) we contextualise it as part of ongoing discussions on the platformisation of music and the algorithmic mediation of identity, as well as debates about digital memory and media events. Based on a social network analysis of posts collected from Twitter/X and a thematic analysis of semi-structured interviews with 38 Spotify users, we argue that in Brazil the ‘eventness' of Spotify Wrapped is distributed, clustered but sparsely connected, and marked by fleeting, fluid and ephemeral feelings of shared experience and recognition rather than by enduring communities. Foregrounding ordinary acts of constrained agency (Siles, et al., 2022), our findings also indicate that Brazilian users playfully and skilfully incorporate the perceived logics of datafied consumption and algorithmic mediation to produce desirable Wrapped results - whilst also hoping that 'the algorithm’ would be able to understand listening contexts and only capture those sessions that are 'Wrapped-worthy'. We conclude by highlighting the continuities and specificities of the phenomenon in relation to existing theorisations of everyday data cultures (Burgess et al., 2022). In doing so, we contribute to the growing body of literature on music streaming studies, platform studies, and critical algorithm studies.</t>
         </is>
       </c>
       <c r="P24" s="6" t="inlineStr">
         <is>
-          <t>10.1080/1369118x.2026.2655885</t>
+          <t>10.1080/1369118x.2026.2647352</t>
         </is>
       </c>
       <c r="Q24" s="6" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1080/1369118x.2026.2655885</t>
+          <t>https://doi.org/10.1080/1369118x.2026.2647352</t>
         </is>
       </c>
       <c r="R24" s="2" t="inlineStr">
@@ -2935,11 +2919,11 @@
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>110</v>
-      </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>无</t>
+        <v>94</v>
+      </c>
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t>黄色</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
@@ -2954,22 +2938,22 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>Between disclosure and conspiracy: the transparency effect on r/UFO and r/UAP subreddits</t>
+          <t>Online interactions and the gravity model</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>在披露与阴谋论之间：透明度对 r/UFO 和 r/UAP 这两个 Reddit 子版块的影响</t>
+          <t>在线互动与引力模型</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>Marco Bastos, Marisa Elena Duarte</t>
+          <t>Constantin Bürgi, Zuzanna Studnicka</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
@@ -2979,42 +2963,42 @@
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>社交媒体；时间序列分析；虚假信息；阴谋论；Reddit</t>
+          <t>在线互动；数字全球化；多人在线游戏；大规模数据集；计算社会科学</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>平台数据＋时间序列</t>
+          <t>大规模行为数据建模</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>议题符合，且摘要明确显示：Reddit 帖文与评论的事件时间线和时间序列分析。</t>
+          <t>议题符合，且方法证据显示：2500 万场在线比赛的个体数据与结构引力模型。</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>论文分析UFO/UAP子版块的帖子和评论，结合政府披露时间线，用时间序列模型检验官方透明度是否减少阴谋论叙事，发现披露能缓解信任侵蚀，并讨论披露概念的局限。</t>
+          <t>论文基于《帝国时代II》2500万场多人比赛数据，构建在线互动模型并用结构重力模型估计，发现文化邻近性和外部社交网络对跨国在线互动有重要影响，为数字全球化和在线社区研究提供实证。</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>尽管确实存在旨在理解“不明异常现象”（Unidentified Anomalous Phenomena, UAPs）的科学研究，但关于“不明飞行物”（Unidentified Flying Objects, UFOs）的传说却与那些刻意编造的叙事紧密相连，这些叙事旨在误导、混淆公众的看法，并操控公众的认知。历史上，这些叙事的目标群体一直受到持续性的虚假信息传播活动的攻击。在这项研究中，我们分析了公众对UAP相关信息的反应，并将其置于政府虚假信息传播及信息流动受阻的历史背景之下进行考察。为此，我们收集了Reddit平台上UAP和UFO相关社区的帖子和评论，并通过构建政府及情报机构的公告、泄密事件、报告的时间线，以及国会和参议院委员会的听证会、特别新闻报道以及美国国防部（DOD）AARO关于UAP的公开声明等数据，对它们进行了建模分析。利用时间序列分析技术，我们试图验证政府直接介入这一议题是否能够有效减轻这些社区中的虚假信息传播和阴谋论叙事的影响。研究结果表明，政府的透明度举措有效地遏制了由阴谋论叙事所引发的公众信任危机。最后，我们指出了“信息披露”这一概念本身所存在的局限性和挑战——这一术语在意识形态和政治层面都带有倾向性，因此需要在这一领域开展更多的研究。</t>
+          <t>我们研究了全球范围内人们之间的数字互动。我们开发了一个简单的在线互动模型，该模型融合了来自传播学的见解，并可以使用国际经济学中使用的结构引力模型进行测试。为了估计我们的模型，我们利用《帝国时代II：决定版》这款游戏中超过2500万场多人对战的数据集，计算了不同国家之间以及同一国家内部玩家之间的在线互动量。我们发现，即使物理交易成本可以忽略不计，文化相似性和外部社交网络在塑造在线互动方面仍然起着关键作用。这表明，影响物理贸易流动的相同因素在网络上仍然具有重要意义。我们的研究结果对数字全球化、在线平台的营销策略以及在线社区的演变具有更广泛的意义。</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>While there exists genuine scientific inquiry seeking to understand Unidentified Anomalous Phenomena (UAPs), the lore of Unidentified Flying Objects (UFOs) is deeply intertwined with narratives deliberately crafted to mislead, obfuscate, and manipulate public perception with a community historically targeted by sustained disinformation campaigns. In this study, we explore the public reception regarding UAP disclosures against the historical context of government disinformation and obstructive information flows. To this end, we retrieved the posts and comments featured in the UAP and UFO Reddit communities and modeled the data by constructing a timeline of governmental and intelligence announcements, leaks, and reports, but also congressional and senate committee hearings, special news reports, and DOD AARO public statements about UAPs. Using time series analysis techniques, we modeled this data to test whether government direct engagement with the topic has tangible effects in subsiding disinformation concerns and conspiratorial narratives within these communities. Our results show that the transparency effect driven by government disclosures effectively counters the erosion of trust fueled by conspiratorial narratives. We conclude by outlining the limitations and challenges embedded in the very idea of disclosure, a term that is ideologically and politically inflected and calls for further studies in this area.</t>
+          <t>We study digital interactions between people across the globe. We develop a simple model of online interactions that incorporates insights from communication studies and can be tested using the structural gravity model used in international economics. To estimate our model, we calculate the volume of online interactions between players in different countries and within a country, using a unique individual-level dataset from over 25 million multiplayer matches in the game Age of Empires II: Definitive Edition. We find that cultural proximity and external social networks are crucial in shaping online interactions, even when physical trade costs are negligible. This suggests that the same factors underlying physical trade flows continue to matter online. Our insights offer broader implications for digital globalization, marketing strategies of online platforms, and the evolution of online communities.</t>
         </is>
       </c>
       <c r="P25" s="6" t="inlineStr">
         <is>
-          <t>10.1080/1369118x.2026.2645882</t>
+          <t>10.1080/1369118x.2026.2648695</t>
         </is>
       </c>
       <c r="Q25" s="6" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1080/1369118x.2026.2645882</t>
+          <t>https://doi.org/10.1080/1369118x.2026.2648695</t>
         </is>
       </c>
       <c r="R25" s="2" t="inlineStr">
@@ -3030,11 +3014,11 @@
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>118</v>
-      </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>无</t>
+        <v>97</v>
+      </c>
+      <c r="B26" s="4" t="inlineStr">
+        <is>
+          <t>黄色</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
@@ -3049,67 +3033,67 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>Style and substance on The Alex Jones Show predict InfoWars sales: a multi-modal analysis of a media empire</t>
+          <t>Social media platforms and the spreading of hate speech targeting sexual and gender minorities: a scoping review</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>《亚历克斯·琼斯秀》中的风格与内容对“信息战”相关产品的销量有影响：对一个媒体帝国的多模态分析</t>
+          <t>社交媒体平台与针对性少数群体和性别少数群体的仇恨言论的传播：一项范围综述</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>Ross Dahlke, Yunkang Yang, Josephine Lukito, Jason Greenfield, Bin Chen et al.</t>
+          <t>Anne Møller Clausen, Lena Frischlich, Peter Mayer</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>计算传播学</t>
+          <t>综述</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>多模态分析；时间序列；虚假信息；媒体帝国；计算宣传</t>
+          <t>仇恨言论；社交媒体平台；BERTopic；平台可供性</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>计算多模态分析</t>
+          <t>计算型综述</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>议题符合，且摘要明确显示：语言、音频与主题特征的多模态时间序列。</t>
+          <t>议题符合，且方法证据显示：145 篇全文的 BERTopic 建模。</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>结合InfoWars销售数据与电台节目和文章的语言、听觉及主题特征，分析内容风格与话题对次日销售的预测关系，揭示虚假信息生产的经济动因。</t>
+          <t>通过范围综述和BERTopic主题建模，系统梳理了145篇研究，分析不同社交媒体平台特性（内容模态、可供性）与针对性少数群体仇恨言论传播的关系，发现Twitter/X研究最多，文本内容为主，并呼吁关注视觉内容与平台动态。</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>亚历克斯·琼斯（Alex Jones）是一位著名的阴谋论者，他通过自己的媒体帝国“InfoWars”获得了巨大的影响力和财富，该帝国包括《亚历克斯·琼斯秀》（The Alex Jones Show）和InfoWars.com网站。本研究利用了2016年至2018年间InfoWars.com的每日销售数据（这些数据是在他面临诽谤诉讼期间公开的），为人们提供了前所未有的视角来了解亚历克斯·琼斯媒体帝国的财务状况。通过将这些销售数据与琼斯广播节目和在线文章中的语言特征、听觉特征以及讨论主题的时间序列分析相结合，我们发现某些语言风格（如使用脏话）和广播节目中的听觉特征（特别是音调和音量强度），以及节目中讨论的具体主题，能够预测次日的销售情况。此外，我们还发现了一种双向关系：销售数据能够预测未来的内容风格和主题。这项研究通过揭示制造虚假/错误信息背后的经济动机，进一步丰富了我们对媒体帝国的认知，并强调了内容在媒体帝国发展中的重要性。</t>
+          <t>如今，社交媒体用户可以访问各种具有不同特性的社交媒体平台，这些平台为仇恨言论的传播提供了不同的机会。然而，关于社交媒体平台（包括其内容形式和功能特性）与针对边缘化群体（如性少数群体和性别少数群体（LGBTQIA+）的仇恨言论传播之间的关系，我们知之甚少。本研究通过开展一项基于PRISMA扩展框架（PRISMA-ScR）的文献综述来填补这一知识空白。考虑到仇恨言论研究的跨学科性质，我们检索了专门针对传播学的学术数据库以及综合性学术数据库（Communication Source、Scopus、Web of Science和Academic Search Premier）。最终共收集到145篇全文论文。分析采用了混合方法：手动对论文中的社交媒体平台、内容形式和功能特性进行了编码，并使用BERTopic模型来识别文献中的关键主题。研究结果表明，Twitter/X是最常被研究的平台，其次是YouTube、Facebook和Instagram；在内容形式方面，文本内容是最受关注的研究对象，而视觉和音视频内容则相对较少被研究。虽然很少有论文明确提及平台的功能特性，但部分研究指出匿名性和可见性是促进仇恨言论传播的因素。主要研究焦点集中在仇恨言论检测模型和数据集的开发上。我们的研究结果呼吁未来的研究关注其他社交媒体平台、视觉和音视频内容，以及平台的功能特性，并将研究重点从单纯的检测模型开发扩展到更广泛的角度，以深入理解平台动态如何影响仇恨言论的传播。</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>Alex Jones, a prominent conspiracy theorist, has garnered substantial influence and wealth through his InfoWars media empire, which includes The Alex Jones Show and InfoWars.com. This study leverages a dataset of daily sales data from InfoWars.com spanning 2016 to 2018, released during his defamation lawsuits. This dataset provides an unprecedented view into the Alex Jones media empire's finances. By combining this dataset with a time series analysis of linguistic and auditory features and topics from Jones's radio show and online articles, we show that specific linguistic styles – such as the use of swear words – and auditory features in the radio show (specifically pitch and intensity), as well as specific topics discussed on the show, predict next-day sales. Furthermore, we find a bidirectional relationship, as sales predict future content style and topics. This study advances our conceptualization of media empires by highlighting the economic incentives behind producing mis/disinformation and underscores the importance of content in developing media empires.</t>
+          <t>Today, social media users can access various social media platforms with different characteristics that offer distinct opportunity structures for the spread of hate speech. Yet little is known about the relationship between social media platforms with their unique characteristics, including content modalities and affordances, and the spreading of hate speech towards marginalized groups, including sexual and gender minorities (LGBTQIA+). This scoping review contributes to closing this gap. We conducted a scoping review according to the PRISMA Extension for Scoping Reviews (PRISMA-ScR). To account for the interdisciplinary nature of hate speech research, we searched communication-specific and broad academic databases (Communication Source, Scopus, Web of Science and Academic Search Premier). The full-text database includes n = 145 full-text papers. The analysis encompassed a mixed-methods approach: Texts were manually coded for social media platforms, content modalities and affordances, and a BERTopic model was trained to identify key topics across literature. Findings show that Twitter/X was the most researched platform, followed by YouTube, Facebook, and Instagram. Textual content was the most researched content modality, compared to visual and audiovisual content. Few publications explicitly mentioned platform affordances, while some pointed to anonymity and visibility as facilitators of the spreading of hate speech. Key topics revolved around the development of models and datasets for hate speech detection. Our findings call for future studies to investigate alternative platforms, visual and audiovisual content, platform affordances, and apply a research focus beyond the development of detection models to understand how platform dynamics contribute to the spreading of hate speech.</t>
         </is>
       </c>
       <c r="P26" s="6" t="inlineStr">
         <is>
-          <t>10.1080/1369118x.2026.2642851</t>
+          <t>10.1080/1369118x.2026.2636138</t>
         </is>
       </c>
       <c r="Q26" s="6" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1080/1369118x.2026.2642851</t>
+          <t>https://doi.org/10.1080/1369118x.2026.2636138</t>
         </is>
       </c>
       <c r="R26" s="2" t="inlineStr">
@@ -3125,11 +3109,11 @@
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>122</v>
-      </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>无</t>
+        <v>100</v>
+      </c>
+      <c r="B27" s="7" t="inlineStr">
+        <is>
+          <t>棕色</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
@@ -3144,22 +3128,22 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>The impact of metaphorical language on social media engagement: evidence from the presidential run-off and major parliamentary parties during the 2023 Turkish general election</t>
+          <t>Racism, resistance, and Reddit: how popular culture sparks online reckonings</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>隐喻性语言对社交媒体参与度的影响：来自2023年土耳其大选期间总统决选赛及主要政党的证据</t>
+          <t>种族主义、抵抗与Reddit：流行文化如何引发网络上的讨论与反思</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>Utku Bozdağa, Lilla Petronella Szabóa</t>
+          <t>Sherry Mason, Tawfiq Ammari</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
@@ -3169,42 +3153,42 @@
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>社交媒体；政治传播；文本分析；用户参与</t>
+          <t>社交媒体分析；主题建模；批判性话语分析；Reddit；种族叙事</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>计算文本测量</t>
+          <t>计算文本分析</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>议题符合，且摘要明确显示：4131 条推文的隐喻频率与原创性数据化测量。</t>
+          <t>议题符合，且方法证据显示：3879 条 Reddit 评论的主题建模。</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>研究2023土耳其大选中政治人物推文的隐喻对用户互动的影响，发现隐喻频率和原创性可小幅提升点赞与转发，回复影响较弱。</t>
+          <t>研究分析Reddit用户对两部种族主题剧集的评论，结合主题建模与批判话语分析，揭示用户角色流动及平台匿名性对种族讨论的影响。</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>本文挑战了文献中普遍认为的“隐喻能够吸引公民注意力”的观点。我们研究了2023年土耳其大选期间社交媒体帖子中隐喻表达对用户参与度的影响，重点关注了参与决选选举的两位主要总统候选人的推文以及获得议会席位的五个主要政党的推文（样本量N=4131）。我们采用了一种数据驱动的分析框架，测量了每条推文中隐喻的频率和原创性，以评估它们对点赞数、转发数和回复数的影响。研究结果表明，隐喻的频率仅使用户参与度提高了1-2%；而隐喻的原创性对用户参与度的影响更为显著，使点赞数和转发数分别增加了6-7%。然而，回复数受到的影响较小，这反映了“参与度阶梯”理论——即当需要投入更多的心理努力时，人们的互动意愿会降低。此外，随着选举关键日期的临近，隐喻的使用频率有所增加，这表明各政党在试图通过隐喻来吸引受众的注意力。总体而言，尽管隐喻能够增强内容的关联性和记忆度，但我们的研究发现它们对用户参与度的实际影响较为有限，并且这种影响取决于具体的情境因素。</t>
+          <t>本研究探讨了Reddit用户如何参与HBO电视剧《守望者》（2019年）和《洛夫克拉夫特之乡》（2020年）中的种族叙事。这两部剧集重新诠释了历史上的种族创伤。我们运用多步骤流动理论（multistep flow theory）和批判性技术文化话语分析（critical technocultural discourse analysis，CTDA），通过对3,879条Reddit评论进行主题建模和批判性话语分析来展开研究。我们识别出三种动态的社会角色：支持者（advocates）、反对者（adversaries）和适应者（adapters），并分析了用户在这些角色之间如何转换以应对相关的种族议题。研究结果表明，Reddit的匿名特性影响了角色的流动性、意见领导力以及用户的道德参与度。反对者认为剧中的种族主义和暴力情节被夸大了，而支持者则分享自己的经历和资源来反驳这些观点；适应者则随着时间的推移改变了自己的立场，这表明在线公众能够促进对种族问题的批判性思考。本研究强调了流行文化和参与式平台在塑造关于种族和历史记忆的集体意义构建过程中的相互作用。</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>This paper challenges the generally implied view in the literature on political language that metaphors attract citizens’ attention. We examined the influence of metaphorical expressions in social media posts on user engagement during the 2023 Turkish general elections, focusing on tweets by the two main presidential candidates who contested the run-off election and five major political parties that gained parliamentary representation (N = 4131). A data-driven framework measured the frequency and originality of metaphors in each post to assess their impact on likes, reposts, and replies. The results showed that metaphor frequency modestly increased engagement by 1–2%, while metaphor originality had a stronger effect, boosting likes and reposts by 6–7%. Replies, however, were less influenced, reflecting the ‘engagement ladder’ concept – the idea that as more mental effort is required, people tend to interact less. In addition, metaphor use intensified as critical election days approached, indicating strategic efforts to engage the audience. Overall, while metaphors enhance relatability and memorability, our findings showed that their actual impact on user engagement is modest and depends on contextual factors.</t>
+          <t>This study examines how Reddit users engaged with the racial narratives of HBO’s Watchmen (2019) and Lovecraft Country (2020), two television series that reimagine historical racial trauma. Drawing on multistep flow theory and critical technocultural discourse analysis (CTDA), we analyze 3,879 Reddit comments using topic modeling and critical discourse analysis. We identify three dynamic social roles – advocates, adversaries, and adaptives – and explore how users move between them in response to racial discourse. Findings reveal how Reddit’s pseudonymous affordances shape role fluidity, opinion leadership, and moral engagement. While adversaries minimized or rejected the shows’ portrayals of racism and violence as exaggerated, advocates shared standpoint experiences and resources to challenge these claims. Adaptive users shifted perspectives over time, demonstrating how online publics can foster critical racial learning. This research highlights how popular culture and participatory platforms intersect in shaping collective meaning-making around race and historical memory.</t>
         </is>
       </c>
       <c r="P27" s="6" t="inlineStr">
         <is>
-          <t>10.1080/1369118x.2026.2642840</t>
+          <t>10.1080/1369118x.2026.2655885</t>
         </is>
       </c>
       <c r="Q27" s="6" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1080/1369118x.2026.2642840</t>
+          <t>https://doi.org/10.1080/1369118x.2026.2655885</t>
         </is>
       </c>
       <c r="R27" s="2" t="inlineStr">
@@ -3220,7 +3204,7 @@
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>130</v>
+        <v>110</v>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
@@ -3239,22 +3223,22 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-03-29</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>How to do things with a keyword: a cross-cultural analysis of the meanings and functions of ‘values’ on Twitter</t>
+          <t>Between disclosure and conspiracy: the transparency effect on r/UFO and r/UAP subreddits</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>如何利用关键词来处理事务：对Twitter上“价值观”一词的含义和功能的跨文化分析</t>
+          <t>在披露与阴谋论之间：透明度对 r/UFO 和 r/UAP 这两个 Reddit 子版块的影响</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>Avishai Green, Yuya Shibuya, Tommaso Trillò, Saki Mizoroki, Rebecca Scharlach et al.</t>
+          <t>Marco Bastos, Marisa Elena Duarte</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -3264,42 +3248,42 @@
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>Twitter；跨文化分析；计算文本分析；价值观；关键词分析</t>
+          <t>社交媒体；时间序列分析；虚假信息；阴谋论；Reddit</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>大规模多语种计算文本</t>
+          <t>平台数据＋时间序列</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>议题符合，且摘要明确显示：五种语言约 1500 万条推文的计算与质性分析。</t>
+          <t>议题符合，且方法证据显示：Reddit 帖文与评论的事件时间线和时间序列分析。</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>分析五种语言约1500万条推文中'values'的语境与功能，发现跨文化差异与普遍模式，揭示其作为身份锚定和边界工作的工具。</t>
+          <t>论文分析UFO/UAP子版块的帖子和评论，结合政府披露时间线，用时间序列模型检验官方透明度是否减少阴谋论叙事，发现披露能缓解信任侵蚀，并讨论披露概念的局限。</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>尽管人们在日常交流和社交媒体上的政治辩论中经常使用“价值观”这个词，但对其在公共传播中的作用却知之甚少。我们将“价值观”视为日常交流中的一个关键词，提出了以下问题：Twitter用户在不同情境下会如何使用“价值观”这个词？这个词具有哪些话语功能？这些情境和功能在不同语言之间有何差异？为了解答这些问题，我们分析了大约1500万条五种语言（英语、德语、意大利语、日语和韩语）的推文，采用了定量和定性分析方法。研究发现，虽然存在跨文化差异，但也存在一些普遍规律。在不同语言中，使用“价值观”的具体情境差异很大：在英语、德语和意大利语中，“价值观”主要用于划分政治群体之间的界限；而在日语和韩语中，则更多地用来表达个人偏好和调节人际关系。无论语言如何，“价值观”都传达了一种模糊的“善”的概念，但同时具有明确的话语功能——它既用于确立个人身份，也用于通过设定界限来调节人际关系。此外，关于价值观的公共讨论总是围绕两个核心价值观之间的矛盾展开：自主性和真实性。无论内容如何，坚持自己的价值观会受到赞赏；而将自己的价值观强加给他人则会被谴责。从这个角度来看，“价值观”这个词实际上是一种避免争议的工具，它使某些观点免受批评。它并没有促进人们对“善”的共同认知的讨论，反而维护了现有的个人和政治界限。</t>
+          <t>尽管确实存在旨在理解“不明异常现象”（Unidentified Anomalous Phenomena, UAPs）的科学研究，但关于“不明飞行物”（Unidentified Flying Objects, UFOs）的传说却与那些刻意编造的叙事紧密相连，这些叙事旨在误导、混淆公众的看法，并操控公众的认知。历史上，这些叙事的目标群体一直受到持续性的虚假信息传播活动的攻击。在这项研究中，我们分析了公众对UAP相关信息的反应，并将其置于政府虚假信息传播及信息流动受阻的历史背景之下进行考察。为此，我们收集了Reddit平台上UAP和UFO相关社区的帖子和评论，并通过构建政府及情报机构的公告、泄密事件、报告的时间线，以及国会和参议院委员会的听证会、特别新闻报道以及美国国防部（DOD）AARO关于UAP的公开声明等数据，对它们进行了建模分析。利用时间序列分析技术，我们试图验证政府直接介入这一议题是否能够有效减轻这些社区中的虚假信息传播和阴谋论叙事的影响。研究结果表明，政府的透明度举措有效地遏制了由阴谋论叙事所引发的公众信任危机。最后，我们指出了“信息披露”这一概念本身所存在的局限性和挑战——这一术语在意识形态和政治层面都带有倾向性，因此需要在这一领域开展更多的研究。</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>While people regularly employ the term values in mundane interactions and political debates on social media, little is known about its function in public communication. Approaching values as a keyword in everyday communication, we asked: In what contexts do Twitter users invoke the term values? What discursive functions does the term serve? How do these contexts and functions differ across languages? To address these questions, we analyzed approximately 15 million tweets in five languages (English, German, Italian, Japanese, and Korean), using computational and qualitative methods. We found both cross-cultural differences and universal patterns. Topical contexts varied dramatically by language: in English, German, and Italian, values primarily marked boundaries between political groups, while in Japanese and Korean, it expressed individual preferences and negotiated interpersonal relationships. Across languages, values conveyed a vague sense of the good yet served clear discursive functions – anchoring personal identities and mediating relationships through boundary work. Furthermore, public conversations about values are structured by the tension between two specific values: autonomy and authenticity. Standing by one's values, regardless of content, was valorized, while imposing values on others was condemned. In this way, the term values offers a tool of decontestation that shields claims from criticism. Rather than promoting deliberation over shared conceptions of the good, it maintains existing personal and political boundaries.</t>
+          <t>While there exists genuine scientific inquiry seeking to understand Unidentified Anomalous Phenomena (UAPs), the lore of Unidentified Flying Objects (UFOs) is deeply intertwined with narratives deliberately crafted to mislead, obfuscate, and manipulate public perception with a community historically targeted by sustained disinformation campaigns. In this study, we explore the public reception regarding UAP disclosures against the historical context of government disinformation and obstructive information flows. To this end, we retrieved the posts and comments featured in the UAP and UFO Reddit communities and modeled the data by constructing a timeline of governmental and intelligence announcements, leaks, and reports, but also congressional and senate committee hearings, special news reports, and DOD AARO public statements about UAPs. Using time series analysis techniques, we modeled this data to test whether government direct engagement with the topic has tangible effects in subsiding disinformation concerns and conspiratorial narratives within these communities. Our results show that the transparency effect driven by government disclosures effectively counters the erosion of trust fueled by conspiratorial narratives. We conclude by outlining the limitations and challenges embedded in the very idea of disclosure, a term that is ideologically and politically inflected and calls for further studies in this area.</t>
         </is>
       </c>
       <c r="P28" s="6" t="inlineStr">
         <is>
-          <t>10.1080/1369118x.2026.2633222</t>
+          <t>10.1080/1369118x.2026.2645882</t>
         </is>
       </c>
       <c r="Q28" s="6" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1080/1369118x.2026.2633222</t>
+          <t>https://doi.org/10.1080/1369118x.2026.2645882</t>
         </is>
       </c>
       <c r="R28" s="2" t="inlineStr">
@@ -3315,11 +3299,11 @@
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>133</v>
-      </c>
-      <c r="B29" s="7" t="inlineStr">
-        <is>
-          <t>棕色</t>
+        <v>118</v>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
@@ -3334,22 +3318,22 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>Does trending across platforms popularize political topics? A cross-platform spillover framework of public attention</t>
+          <t>Style and substance on The Alex Jones Show predict InfoWars sales: a multi-modal analysis of a media empire</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>跨平台的热度传播是否使政治话题更加流行？一个关于公众注意力跨平台溢出的分析框架</t>
+          <t>《亚历克斯·琼斯秀》中的风格与内容对“信息战”相关产品的销量有影响：对一个媒体帝国的多模态分析</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>Yufan Guo, Cong Lin, Yuhan Li</t>
+          <t>Ross Dahlke, Yunkang Yang, Josephine Lukito, Jason Greenfield, Bin Chen et al.</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
@@ -3359,42 +3343,42 @@
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>跨平台溢出；公共注意力；微博；社交媒体</t>
+          <t>多模态分析；时间序列；虚假信息；媒体帝国；计算宣传</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>跨平台数据建模</t>
+          <t>计算多模态分析</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>议题符合，且摘要明确显示：三平台趋势数据与跨平台注意力效应估计。</t>
+          <t>议题符合，且方法证据显示：语言、音频与主题特征的多模态时间序列。</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>基于中国三大平台2023年数据，以以哈战争为例，探究跨平台同时上榜对微博政治话题关注度的影响，发现负向溢出效应。</t>
+          <t>结合InfoWars销售数据与电台节目和文章的语言、听觉及主题特征，分析内容风格与话题对次日销售的预测关系，揭示虚假信息生产的经济动因。</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>为什么某些话题在数字平台上比其他话题更能吸引公众的关注？在承认并超越以往仅关注平台内部因素的观点的基础上，我们提出了一种动态的跨平台溢出效应解释模型，探讨了跨平台趋势（即同时在两个平台上成为热门话题）如何影响公众对政治话题的关注。借鉴“注意力市场”模型、信息溢出理论以及跨平台研究的成果，我们构建了一个关于公众关注的跨平台溢出效应框架。该框架涵盖了多种机制，这些机制使得不同类型的参与者能够在平台之间产生协同效应或竞争关系。通过实证研究，我们评估了2023年中国三大主要数字平台上跨平台趋势的传播规模。以以色列-哈马斯战争为例，我们进一步分析了跨平台趋势对微博上公众对政治话题关注度的影响。研究结果表明存在负面的跨平台溢出效应：在某些特定情境下，另一个平台上的热门话题反而会抑制微博上同一新闻话题的传播。这项研究有助于我们更深入地理解在日益互联互通、且有时充满竞争的数字媒体生态系统中，公众关注力的分配机制。</t>
+          <t>亚历克斯·琼斯（Alex Jones）是一位著名的阴谋论者，他通过自己的媒体帝国“InfoWars”获得了巨大的影响力和财富，该帝国包括《亚历克斯·琼斯秀》（The Alex Jones Show）和InfoWars.com网站。本研究利用了2016年至2018年间InfoWars.com的每日销售数据（这些数据是在他面临诽谤诉讼期间公开的），为人们提供了前所未有的视角来了解亚历克斯·琼斯媒体帝国的财务状况。通过将这些销售数据与琼斯广播节目和在线文章中的语言特征、听觉特征以及讨论主题的时间序列分析相结合，我们发现某些语言风格（如使用脏话）和广播节目中的听觉特征（特别是音调和音量强度），以及节目中讨论的具体主题，能够预测次日的销售情况。此外，我们还发现了一种双向关系：销售数据能够预测未来的内容风格和主题。这项研究通过揭示制造虚假/错误信息背后的经济动机，进一步丰富了我们对媒体帝国的认知，并强调了内容在媒体帝国发展中的重要性。</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>Why do certain topics attract more public attention than others on digital platforms? Acknowledging but moving beyond previous intra-platform perspectives, we propose a dynamic cross-platform spillover explanation, examining how cross-platform trending (i.e., trending on two platforms concurrently) influences public attention to political topics. Drawing on the marketplace of attention model, the notion of information spillover, and cross-platform literature, we develop a cross-platform spillover framework of public attention. This framework incorporates various mechanisms through which different layers of actors can facilitate inter-platform synergy or competition. Empirically, we assess the scale of cross-platform trending on three leading Chinese platforms in 2023. Focusing on the case of the Israel-Hamas war, we further estimate the effect of cross-platform trending on the public attention to political topics on Weibo. Our results indicate a negative cross-platform spillover: trending on another platform does not popularize, but suppresses the same news topic on Weibo in certain topical contexts. This study enriches our understanding of public attention allocation in an increasingly interconnected, and sometimes competitive, digital media ecosystem.</t>
+          <t>Alex Jones, a prominent conspiracy theorist, has garnered substantial influence and wealth through his InfoWars media empire, which includes The Alex Jones Show and InfoWars.com. This study leverages a dataset of daily sales data from InfoWars.com spanning 2016 to 2018, released during his defamation lawsuits. This dataset provides an unprecedented view into the Alex Jones media empire's finances. By combining this dataset with a time series analysis of linguistic and auditory features and topics from Jones's radio show and online articles, we show that specific linguistic styles – such as the use of swear words – and auditory features in the radio show (specifically pitch and intensity), as well as specific topics discussed on the show, predict next-day sales. Furthermore, we find a bidirectional relationship, as sales predict future content style and topics. This study advances our conceptualization of media empires by highlighting the economic incentives behind producing mis/disinformation and underscores the importance of content in developing media empires.</t>
         </is>
       </c>
       <c r="P29" s="6" t="inlineStr">
         <is>
-          <t>10.1080/1369118x.2026.2633216</t>
+          <t>10.1080/1369118x.2026.2642851</t>
         </is>
       </c>
       <c r="Q29" s="6" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1080/1369118x.2026.2633216</t>
+          <t>https://doi.org/10.1080/1369118x.2026.2642851</t>
         </is>
       </c>
       <c r="R29" s="2" t="inlineStr">
@@ -3410,7 +3394,7 @@
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>137</v>
+        <v>122</v>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
@@ -3429,22 +3413,22 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>2026-02-18</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>Orchestrating scalability: how patents render cloud imaginaries in CAV innovation</t>
+          <t>The impact of metaphorical language on social media engagement: evidence from the presidential run-off and major parliamentary parties during the 2023 Turkish general election</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>协调可扩展性：专利如何将云计算的设想转化为计算机辅助验证（CAV）创新</t>
+          <t>隐喻性语言对社交媒体参与度的影响：来自2023年土耳其大选期间总统决选赛及主要政党的证据</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>Alex Gekker, Sam; id_orcid 0000-0001-8347-3695 Hind, Gabriel Pereira, Fernando van der Vlist</t>
+          <t>Utku Bozdağa, Lilla Petronella Szabóa</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -3454,42 +3438,42 @@
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>自动驾驶；云基础设施；专利分析；AI想象</t>
+          <t>社交媒体；政治传播；文本分析；用户参与</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>大规模计算文本</t>
+          <t>计算文本测量</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>议题符合，且摘要明确显示：69,421 个专利家族的主题聚类。</t>
+          <t>议题符合，且方法证据显示：4131 条推文的隐喻频率与原创性数据化测量。</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>分析云技术如何支撑自动驾驶规模化，基于69,421项专利识别四个主题聚类，揭示云作为编排技术塑造AI未来。</t>
+          <t>研究2023土耳其大选中政治人物推文的隐喻对用户互动的影响，发现隐喻频率和原创性可小幅提升点赞与转发，回复影响较弱。</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>本文探讨了云计算如何推动和塑造联网自动驾驶车辆（CAVs）的规模化发展，并将云计算基础设施视为推动人工智能（AI）规模化发展的关键技术、战略以及核心要素。通过分析69,421个全球专利家族的数据集，我们研究了包括汽车制造商、芯片制造商、电子公司、自动驾驶车辆企业以及电信/地图服务提供商在内的多种参与者如何利用云计算技术来扩展AI功能、管理资源并协调复杂的社会技术系统。从“社会技术想象”的角度出发，我们分析了这些专利如何既编码了技术创新，又体现了对可扩展、基于云计算的自动驾驶车辆未来的构想。研究发现，云计算主要通过四个主题领域实现其功能：车辆通信、机器视觉、网络架构和边缘计算。我们认为，云计算本质上是一种用于协调各种技术资源的技术；其“云化”过程体现了人工智能从实验室研究向全球可扩展系统的转变。本文通过揭示技术、组织结构与想象力这三个维度在推动AI驱动的移动出行发展中的相互作用，为相关讨论做出了贡献。</t>
+          <t>本文挑战了文献中普遍认为的“隐喻能够吸引公民注意力”的观点。我们研究了2023年土耳其大选期间社交媒体帖子中隐喻表达对用户参与度的影响，重点关注了参与决选选举的两位主要总统候选人的推文以及获得议会席位的五个主要政党的推文（样本量N=4131）。我们采用了一种数据驱动的分析框架，测量了每条推文中隐喻的频率和原创性，以评估它们对点赞数、转发数和回复数的影响。研究结果表明，隐喻的频率仅使用户参与度提高了1-2%；而隐喻的原创性对用户参与度的影响更为显著，使点赞数和转发数分别增加了6-7%。然而，回复数受到的影响较小，这反映了“参与度阶梯”理论——即当需要投入更多的心理努力时，人们的互动意愿会降低。此外，随着选举关键日期的临近，隐喻的使用频率有所增加，这表明各政党在试图通过隐喻来吸引受众的注意力。总体而言，尽管隐喻能够增强内容的关联性和记忆度，但我们的研究发现它们对用户参与度的实际影响较为有限，并且这种影响取决于具体的情境因素。</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>This article explores how cloud computing enables and shapes the scaling of connected and autonomous vehicles (CAVs), positioning cloud infrastructure as a technology, strategy, and imaginary central to the scaling of AI. Using a dataset of 69,421 global patent families, we analyse how diverse actors – including automotive manufacturers, chipmakers, electronics companies, autonomous vehicle firms, and telecom/mapping providers – mobilise cloud technologies to expand AI capabilities, manage resources, and coordinate complex socio-technical systems. Approaching patents through ‘sociotechnical imaginaries’, we show how they simultaneously codify technical innovations while projecting visions of scalable, cloud-enabled CAV futures. Our analysis identifies four thematic clusters – vehicle communication, machine vision, network architectures, and edge computing – through which cloud technologies are operationalised and imagined. We argue that the cloud functions as a technology of orchestration, with cloudification exemplifying AI’s industrialisation as it moves from laboratory research to globally scalable systems. The article contributes to debates on scale by highlighting the interplay between technical, organisational, and imaginative dimensions in shaping AI-enabled mobility.</t>
+          <t>This paper challenges the generally implied view in the literature on political language that metaphors attract citizens’ attention. We examined the influence of metaphorical expressions in social media posts on user engagement during the 2023 Turkish general elections, focusing on tweets by the two main presidential candidates who contested the run-off election and five major political parties that gained parliamentary representation (N = 4131). A data-driven framework measured the frequency and originality of metaphors in each post to assess their impact on likes, reposts, and replies. The results showed that metaphor frequency modestly increased engagement by 1–2%, while metaphor originality had a stronger effect, boosting likes and reposts by 6–7%. Replies, however, were less influenced, reflecting the ‘engagement ladder’ concept – the idea that as more mental effort is required, people tend to interact less. In addition, metaphor use intensified as critical election days approached, indicating strategic efforts to engage the audience. Overall, while metaphors enhance relatability and memorability, our findings showed that their actual impact on user engagement is modest and depends on contextual factors.</t>
         </is>
       </c>
       <c r="P30" s="6" t="inlineStr">
         <is>
-          <t>10.1080/1369118x.2026.2631709</t>
+          <t>10.1080/1369118x.2026.2642840</t>
         </is>
       </c>
       <c r="Q30" s="6" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1080/1369118x.2026.2631709</t>
+          <t>https://doi.org/10.1080/1369118x.2026.2642840</t>
         </is>
       </c>
       <c r="R30" s="2" t="inlineStr">
@@ -3505,7 +3489,7 @@
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>141</v>
+        <v>129</v>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
@@ -3519,72 +3503,72 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>摘要明确</t>
+          <t>出版方全文方法明确</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>2026-02-08</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>Algorithmic reproduction of social inequality: language attitude bias in Chinese and English pre-trained language models</t>
+          <t>Nudging against judging? Mitigating anti-LGBTQIA + online hostility by raising bystanders’ awareness and behavioral intentions</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>算法再现社会不平等：中文和英文预训练语言模型中的语言态度偏见</t>
+          <t>“通过提高旁观者的意识和行为倾向来减轻对LGBTQIA群体的敌意”——一种对抗歧视的策略</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>Zhenzhen Zhang, Guowen Huang, Wanting Chen, Sihui Chen, Bingkun Yang</t>
+          <t>Melanie Saumer, Kevin Koban, Jörg Matthes</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>计算传播学</t>
+          <t>传统量化分析</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>预训练语言模型；算法偏见；社会不平等；语言态度</t>
+          <t>在线敌意；旁观者干预；社会助推；LGBTQIA+</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>语言模型审计</t>
+          <t>在线实验</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>议题符合，且摘要明确显示：在中英文预训练语言模型上实施 FMAT 偏见审计。</t>
+          <t>议题符合，且方法证据显示：预注册 3×3 在线实验，操控 Instagram 仿真帖文的敌意类型与提示方式。</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>通过Fill-Mask关联测试分析中英文预训练语言模型在性别、职业和年龄上的语言态度偏见，发现模型复制社会等级和意识形态，呼吁数据治理与公平。</t>
+          <t>实验研究考察社会助推对旁观者干预反LGBTQIA+在线敌意的影响，发现敌意类型影响反应，助推效果不稳定，少数增加负面情绪但未促进行为。</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>预训练的语言模型（PLMs）被广泛应用于教育、招聘和内容审核等领域，这引发了这样一个问题：这些模型是否有可能复制社会等级结构和象征性的权力关系。本研究使用“填充-掩码关联测试”（Fill-Mask Association Test, FMAT）对四种主要的中文PLMs进行了分析，并将其与英文PLMs进行了比较。研究系统地探讨了语言态度偏见与性别、职业和年龄之间的关系。结果表明，中文PLMs在性别评价上表现出更明显的男性偏好；所有模型在职业偏见方面都倾向于高地位的职业；在年龄维度上，中文和英文PLMs都更偏爱年轻群体，不过中文模型内部的变异性更大。此外，地位因素被证明是所有模型中最稳定且方向性最一致的偏见因素。这些研究结果揭示了算法化的语言表达方式如何可能模仿并延续社会意识形态，因此呼吁对这类模型进行严格的审查，并推动多元化的数据治理机制，以实现数字通信中的公平性。</t>
+          <t>旁观者干预是一种有前景的手段，可用于应对网络上日益增多的针对LGBTQIA+群体的敌对行为。这项实验研究通过3×3的设计框架，探讨了不同类型的社交提示（意识提示、意识与行为结合的提示以及无提示[对照组]）以及不同类型的敌对行为（不文明行为、不宽容行为和文明行为[对照组]）对旁观者反应的影响。研究结果证实，敌对行为的类型显著影响了人们对相关行为的接受度、负面情绪、干预意愿以及内容审核的偏好。然而，社交提示的效果并不一致：意识提示有时会加剧负面情绪（尤其是在与不宽容行为结合时），但未能有效促进旁观者的干预行为。这些发现支持了“期望违背理论”（Expectancy Violation Theory）和“旁观者干预模型”（Bystander Intervention Model），表明敌对言论会引发旁观者的反应，而社交提示则可能引发抵触情绪或显得多余。个体差异（包括对LGBTQIA+群体的态度、政治立场以及被动使用社交媒体的习惯）进一步影响了旁观者的干预倾向。文章还讨论了这些发现对数字干预措施和政策制定的启示。</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>Pre-trained language models (PLMs) are used in education, hiring, and moderation, raising the question of whether these models could replicate social hierarchies and symbolic power structures. This study employs the Fill-Mask Association Test (FMAT) in four principal Chinese PLMs with reference to the English PLMs. Language attitude bias is systematically characterized by gender, occupation, and age. The results show that Chinese PLMs display stronger male-oriented bias in gender evaluations; all models consistently favor high-status professions in occupational bias; and in the age dimension, both Chinese and English PLMs prefer younger groups, though the Chinese models show greater internal variability. Status also emerges as the most stable and directionally consistent bias across models. These results illustrate how algorithmic discourse may mimic and sustain social ideologies, making the case for critical scrutiny and diverse data governance as a means to realize equity in digital communication.</t>
+          <t>Bystander interventions are a promising tool to counteract the rising instances of anti-LGBTQIA+ hostility online. This experimental study investigates how social nudges influence bystander reactions within a 3 × 3 design, varying nudge type (awareness nudge vs. awareness &amp; behavioral nudge vs. no nudge [control]) and hostility type (incivility vs. intolerance vs. civil [control]). Results confirmed that hostility type significantly influenced perceived acceptability, negative emotions, intervention intentions, and content moderation preferences. However, nudging effects were inconsistent, with awareness nudging sporadically increasing negative emotions, particularly when combined with intolerance, but failing to enhance intervention behaviors. These findings support the Expectancy Violation Theory and the Bystander Intervention Model, suggesting that hostile speech reliably triggers bystander responses, whereas nudges may induce reactance or appear redundant. Individual differences, including LGBTQIA+ attitudes, political orientation, and passive social media use, further shaped intervention tendencies. Implications for digital interventions and policy development are discussed.</t>
         </is>
       </c>
       <c r="P31" s="6" t="inlineStr">
         <is>
-          <t>10.1080/1369118x.2026.2624702</t>
+          <t>10.1080/1369118x.2026.2636134</t>
         </is>
       </c>
       <c r="Q31" s="6" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1080/1369118x.2026.2624702</t>
+          <t>https://doi.org/10.1080/1369118x.2026.2636134</t>
         </is>
       </c>
       <c r="R31" s="2" t="inlineStr">
@@ -3600,101 +3584,481 @@
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
+        <v>130</v>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>纳入</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>摘要明确</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>2026-02-26</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>How to do things with a keyword: a cross-cultural analysis of the meanings and functions of ‘values’ on Twitter</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>如何利用关键词来处理事务：对Twitter上“价值观”一词的含义和功能的跨文化分析</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>Avishai Green, Yuya Shibuya, Tommaso Trillò, Saki Mizoroki, Rebecca Scharlach et al.</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>计算传播学</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
+          <t>Twitter；跨文化分析；计算文本分析；价值观；关键词分析</t>
+        </is>
+      </c>
+      <c r="K32" s="2" t="inlineStr">
+        <is>
+          <t>大规模多语种计算文本</t>
+        </is>
+      </c>
+      <c r="L32" s="2" t="inlineStr">
+        <is>
+          <t>议题符合，且方法证据显示：五种语言约 1500 万条推文的计算与质性分析。</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr">
+        <is>
+          <t>分析五种语言约1500万条推文中'values'的语境与功能，发现跨文化差异与普遍模式，揭示其作为身份锚定和边界工作的工具。</t>
+        </is>
+      </c>
+      <c r="N32" s="2" t="inlineStr">
+        <is>
+          <t>尽管人们在日常交流和社交媒体上的政治辩论中经常使用“价值观”这个词，但对其在公共传播中的作用却知之甚少。我们将“价值观”视为日常交流中的一个关键词，提出了以下问题：Twitter用户在不同情境下会如何使用“价值观”这个词？这个词具有哪些话语功能？这些情境和功能在不同语言之间有何差异？为了解答这些问题，我们分析了大约1500万条五种语言（英语、德语、意大利语、日语和韩语）的推文，采用了定量和定性分析方法。研究发现，虽然存在跨文化差异，但也存在一些普遍规律。在不同语言中，使用“价值观”的具体情境差异很大：在英语、德语和意大利语中，“价值观”主要用于划分政治群体之间的界限；而在日语和韩语中，则更多地用来表达个人偏好和调节人际关系。无论语言如何，“价值观”都传达了一种模糊的“善”的概念，但同时具有明确的话语功能——它既用于确立个人身份，也用于通过设定界限来调节人际关系。此外，关于价值观的公共讨论总是围绕两个核心价值观之间的矛盾展开：自主性和真实性。无论内容如何，坚持自己的价值观会受到赞赏；而将自己的价值观强加给他人则会被谴责。从这个角度来看，“价值观”这个词实际上是一种避免争议的工具，它使某些观点免受批评。它并没有促进人们对“善”的共同认知的讨论，反而维护了现有的个人和政治界限。</t>
+        </is>
+      </c>
+      <c r="O32" s="2" t="inlineStr">
+        <is>
+          <t>While people regularly employ the term values in mundane interactions and political debates on social media, little is known about its function in public communication. Approaching values as a keyword in everyday communication, we asked: In what contexts do Twitter users invoke the term values? What discursive functions does the term serve? How do these contexts and functions differ across languages? To address these questions, we analyzed approximately 15 million tweets in five languages (English, German, Italian, Japanese, and Korean), using computational and qualitative methods. We found both cross-cultural differences and universal patterns. Topical contexts varied dramatically by language: in English, German, and Italian, values primarily marked boundaries between political groups, while in Japanese and Korean, it expressed individual preferences and negotiated interpersonal relationships. Across languages, values conveyed a vague sense of the good yet served clear discursive functions – anchoring personal identities and mediating relationships through boundary work. Furthermore, public conversations about values are structured by the tension between two specific values: autonomy and authenticity. Standing by one's values, regardless of content, was valorized, while imposing values on others was condemned. In this way, the term values offers a tool of decontestation that shields claims from criticism. Rather than promoting deliberation over shared conceptions of the good, it maintains existing personal and political boundaries.</t>
+        </is>
+      </c>
+      <c r="P32" s="6" t="inlineStr">
+        <is>
+          <t>10.1080/1369118x.2026.2633222</t>
+        </is>
+      </c>
+      <c r="Q32" s="6" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1080/1369118x.2026.2633222</t>
+        </is>
+      </c>
+      <c r="R32" s="2" t="inlineStr">
+        <is>
+          <t>待获取</t>
+        </is>
+      </c>
+      <c r="S32" s="2" t="inlineStr">
+        <is>
+          <t>未开始</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="n">
+        <v>133</v>
+      </c>
+      <c r="B33" s="7" t="inlineStr">
+        <is>
+          <t>棕色</t>
+        </is>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>纳入</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>摘要明确</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>Does trending across platforms popularize political topics? A cross-platform spillover framework of public attention</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>跨平台的热度传播是否使政治话题更加流行？一个关于公众注意力跨平台溢出的分析框架</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>Yufan Guo, Cong Lin, Yuhan Li</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>计算传播学</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
+          <t>跨平台溢出；公共注意力；微博；社交媒体</t>
+        </is>
+      </c>
+      <c r="K33" s="2" t="inlineStr">
+        <is>
+          <t>跨平台数据建模</t>
+        </is>
+      </c>
+      <c r="L33" s="2" t="inlineStr">
+        <is>
+          <t>议题符合，且方法证据显示：三平台趋势数据与跨平台注意力效应估计。</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="inlineStr">
+        <is>
+          <t>基于中国三大平台2023年数据，以以哈战争为例，探究跨平台同时上榜对微博政治话题关注度的影响，发现负向溢出效应。</t>
+        </is>
+      </c>
+      <c r="N33" s="2" t="inlineStr">
+        <is>
+          <t>为什么某些话题在数字平台上比其他话题更能吸引公众的关注？在承认并超越以往仅关注平台内部因素的观点的基础上，我们提出了一种动态的跨平台溢出效应解释模型，探讨了跨平台趋势（即同时在两个平台上成为热门话题）如何影响公众对政治话题的关注。借鉴“注意力市场”模型、信息溢出理论以及跨平台研究的成果，我们构建了一个关于公众关注的跨平台溢出效应框架。该框架涵盖了多种机制，这些机制使得不同类型的参与者能够在平台之间产生协同效应或竞争关系。通过实证研究，我们评估了2023年中国三大主要数字平台上跨平台趋势的传播规模。以以色列-哈马斯战争为例，我们进一步分析了跨平台趋势对微博上公众对政治话题关注度的影响。研究结果表明存在负面的跨平台溢出效应：在某些特定情境下，另一个平台上的热门话题反而会抑制微博上同一新闻话题的传播。这项研究有助于我们更深入地理解在日益互联互通、且有时充满竞争的数字媒体生态系统中，公众关注力的分配机制。</t>
+        </is>
+      </c>
+      <c r="O33" s="2" t="inlineStr">
+        <is>
+          <t>Why do certain topics attract more public attention than others on digital platforms? Acknowledging but moving beyond previous intra-platform perspectives, we propose a dynamic cross-platform spillover explanation, examining how cross-platform trending (i.e., trending on two platforms concurrently) influences public attention to political topics. Drawing on the marketplace of attention model, the notion of information spillover, and cross-platform literature, we develop a cross-platform spillover framework of public attention. This framework incorporates various mechanisms through which different layers of actors can facilitate inter-platform synergy or competition. Empirically, we assess the scale of cross-platform trending on three leading Chinese platforms in 2023. Focusing on the case of the Israel-Hamas war, we further estimate the effect of cross-platform trending on the public attention to political topics on Weibo. Our results indicate a negative cross-platform spillover: trending on another platform does not popularize, but suppresses the same news topic on Weibo in certain topical contexts. This study enriches our understanding of public attention allocation in an increasingly interconnected, and sometimes competitive, digital media ecosystem.</t>
+        </is>
+      </c>
+      <c r="P33" s="6" t="inlineStr">
+        <is>
+          <t>10.1080/1369118x.2026.2633216</t>
+        </is>
+      </c>
+      <c r="Q33" s="6" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1080/1369118x.2026.2633216</t>
+        </is>
+      </c>
+      <c r="R33" s="2" t="inlineStr">
+        <is>
+          <t>待获取</t>
+        </is>
+      </c>
+      <c r="S33" s="2" t="inlineStr">
+        <is>
+          <t>未开始</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="n">
+        <v>137</v>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>纳入</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>摘要明确</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>2026-02-18</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>Orchestrating scalability: how patents render cloud imaginaries in CAV innovation</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>协调可扩展性：专利如何将云计算的设想转化为计算机辅助验证（CAV）创新</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>Alex Gekker, Sam; id_orcid 0000-0001-8347-3695 Hind, Gabriel Pereira, Fernando van der Vlist</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>计算传播学</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
+          <t>自动驾驶；云基础设施；专利分析；AI想象</t>
+        </is>
+      </c>
+      <c r="K34" s="2" t="inlineStr">
+        <is>
+          <t>大规模计算文本</t>
+        </is>
+      </c>
+      <c r="L34" s="2" t="inlineStr">
+        <is>
+          <t>议题符合，且方法证据显示：69,421 个专利家族的主题聚类。</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr">
+        <is>
+          <t>分析云技术如何支撑自动驾驶规模化，基于69,421项专利识别四个主题聚类，揭示云作为编排技术塑造AI未来。</t>
+        </is>
+      </c>
+      <c r="N34" s="2" t="inlineStr">
+        <is>
+          <t>本文探讨了云计算如何推动和塑造联网自动驾驶车辆（CAVs）的规模化发展，并将云计算基础设施视为推动人工智能（AI）规模化发展的关键技术、战略以及核心要素。通过分析69,421个全球专利家族的数据集，我们研究了包括汽车制造商、芯片制造商、电子公司、自动驾驶车辆企业以及电信/地图服务提供商在内的多种参与者如何利用云计算技术来扩展AI功能、管理资源并协调复杂的社会技术系统。从“社会技术想象”的角度出发，我们分析了这些专利如何既编码了技术创新，又体现了对可扩展、基于云计算的自动驾驶车辆未来的构想。研究发现，云计算主要通过四个主题领域实现其功能：车辆通信、机器视觉、网络架构和边缘计算。我们认为，云计算本质上是一种用于协调各种技术资源的技术；其“云化”过程体现了人工智能从实验室研究向全球可扩展系统的转变。本文通过揭示技术、组织结构与想象力这三个维度在推动AI驱动的移动出行发展中的相互作用，为相关讨论做出了贡献。</t>
+        </is>
+      </c>
+      <c r="O34" s="2" t="inlineStr">
+        <is>
+          <t>This article explores how cloud computing enables and shapes the scaling of connected and autonomous vehicles (CAVs), positioning cloud infrastructure as a technology, strategy, and imaginary central to the scaling of AI. Using a dataset of 69,421 global patent families, we analyse how diverse actors – including automotive manufacturers, chipmakers, electronics companies, autonomous vehicle firms, and telecom/mapping providers – mobilise cloud technologies to expand AI capabilities, manage resources, and coordinate complex socio-technical systems. Approaching patents through ‘sociotechnical imaginaries’, we show how they simultaneously codify technical innovations while projecting visions of scalable, cloud-enabled CAV futures. Our analysis identifies four thematic clusters – vehicle communication, machine vision, network architectures, and edge computing – through which cloud technologies are operationalised and imagined. We argue that the cloud functions as a technology of orchestration, with cloudification exemplifying AI’s industrialisation as it moves from laboratory research to globally scalable systems. The article contributes to debates on scale by highlighting the interplay between technical, organisational, and imaginative dimensions in shaping AI-enabled mobility.</t>
+        </is>
+      </c>
+      <c r="P34" s="6" t="inlineStr">
+        <is>
+          <t>10.1080/1369118x.2026.2631709</t>
+        </is>
+      </c>
+      <c r="Q34" s="6" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1080/1369118x.2026.2631709</t>
+        </is>
+      </c>
+      <c r="R34" s="2" t="inlineStr">
+        <is>
+          <t>待获取</t>
+        </is>
+      </c>
+      <c r="S34" s="2" t="inlineStr">
+        <is>
+          <t>未开始</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="n">
+        <v>141</v>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>纳入</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>摘要明确</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>2026-02-08</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>Algorithmic reproduction of social inequality: language attitude bias in Chinese and English pre-trained language models</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>算法再现社会不平等：中文和英文预训练语言模型中的语言态度偏见</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>Zhenzhen Zhang, Guowen Huang, Wanting Chen, Sihui Chen, Bingkun Yang</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>计算传播学</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr">
+        <is>
+          <t>预训练语言模型；算法偏见；社会不平等；语言态度</t>
+        </is>
+      </c>
+      <c r="K35" s="2" t="inlineStr">
+        <is>
+          <t>语言模型审计</t>
+        </is>
+      </c>
+      <c r="L35" s="2" t="inlineStr">
+        <is>
+          <t>议题符合，且方法证据显示：在中英文预训练语言模型上实施 FMAT 偏见审计。</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="inlineStr">
+        <is>
+          <t>通过Fill-Mask关联测试分析中英文预训练语言模型在性别、职业和年龄上的语言态度偏见，发现模型复制社会等级和意识形态，呼吁数据治理与公平。</t>
+        </is>
+      </c>
+      <c r="N35" s="2" t="inlineStr">
+        <is>
+          <t>预训练的语言模型（PLMs）被广泛应用于教育、招聘和内容审核等领域，这引发了这样一个问题：这些模型是否有可能复制社会等级结构和象征性的权力关系。本研究使用“填充-掩码关联测试”（Fill-Mask Association Test, FMAT）对四种主要的中文PLMs进行了分析，并将其与英文PLMs进行了比较。研究系统地探讨了语言态度偏见与性别、职业和年龄之间的关系。结果表明，中文PLMs在性别评价上表现出更明显的男性偏好；所有模型在职业偏见方面都倾向于高地位的职业；在年龄维度上，中文和英文PLMs都更偏爱年轻群体，不过中文模型内部的变异性更大。此外，地位因素被证明是所有模型中最稳定且方向性最一致的偏见因素。这些研究结果揭示了算法化的语言表达方式如何可能模仿并延续社会意识形态，因此呼吁对这类模型进行严格的审查，并推动多元化的数据治理机制，以实现数字通信中的公平性。</t>
+        </is>
+      </c>
+      <c r="O35" s="2" t="inlineStr">
+        <is>
+          <t>Pre-trained language models (PLMs) are used in education, hiring, and moderation, raising the question of whether these models could replicate social hierarchies and symbolic power structures. This study employs the Fill-Mask Association Test (FMAT) in four principal Chinese PLMs with reference to the English PLMs. Language attitude bias is systematically characterized by gender, occupation, and age. The results show that Chinese PLMs display stronger male-oriented bias in gender evaluations; all models consistently favor high-status professions in occupational bias; and in the age dimension, both Chinese and English PLMs prefer younger groups, though the Chinese models show greater internal variability. Status also emerges as the most stable and directionally consistent bias across models. These results illustrate how algorithmic discourse may mimic and sustain social ideologies, making the case for critical scrutiny and diverse data governance as a means to realize equity in digital communication.</t>
+        </is>
+      </c>
+      <c r="P35" s="6" t="inlineStr">
+        <is>
+          <t>10.1080/1369118x.2026.2624702</t>
+        </is>
+      </c>
+      <c r="Q35" s="6" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1080/1369118x.2026.2624702</t>
+        </is>
+      </c>
+      <c r="R35" s="2" t="inlineStr">
+        <is>
+          <t>待获取</t>
+        </is>
+      </c>
+      <c r="S35" s="2" t="inlineStr">
+        <is>
+          <t>未开始</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="n">
         <v>142</v>
       </c>
-      <c r="B32" s="7" t="inlineStr">
+      <c r="B36" s="7" t="inlineStr">
         <is>
           <t>棕色</t>
         </is>
       </c>
-      <c r="C32" s="5" t="inlineStr">
+      <c r="C36" s="5" t="inlineStr">
         <is>
           <t>纳入</t>
         </is>
       </c>
-      <c r="D32" s="2" t="inlineStr">
+      <c r="D36" s="2" t="inlineStr">
         <is>
           <t>摘要明确</t>
         </is>
       </c>
-      <c r="E32" s="2" t="inlineStr">
+      <c r="E36" s="2" t="inlineStr">
         <is>
           <t>2026-02-05</t>
         </is>
       </c>
-      <c r="F32" s="2" t="inlineStr">
+      <c r="F36" s="2" t="inlineStr">
         <is>
           <t>The entangled dynamics leading to the sedimentation of polarisation on political Reddit</t>
         </is>
       </c>
-      <c r="G32" s="2" t="inlineStr">
+      <c r="G36" s="2" t="inlineStr">
         <is>
           <t>导致政治类Reddit平台上极化现象沉淀的复杂动态机制</t>
         </is>
       </c>
-      <c r="H32" s="2" t="inlineStr">
+      <c r="H36" s="2" t="inlineStr">
         <is>
           <t>Ehsan Dehghan, Dominique Carlon, Kateryna Kasianenko, Ashwin Nagappa, Vish Padinjaredath Suresh</t>
         </is>
       </c>
-      <c r="I32" s="2" t="inlineStr">
+      <c r="I36" s="2" t="inlineStr">
         <is>
           <t>计算传播学</t>
         </is>
       </c>
-      <c r="J32" s="2" t="inlineStr">
+      <c r="J36" s="2" t="inlineStr">
         <is>
           <t>社交媒体平台；政治极化；Reddit；网络分析</t>
         </is>
       </c>
-      <c r="K32" s="2" t="inlineStr">
+      <c r="K36" s="2" t="inlineStr">
         <is>
           <t>纵向网络分析</t>
         </is>
       </c>
-      <c r="L32" s="2" t="inlineStr">
-        <is>
-          <t>议题符合，且摘要明确显示：16 年 Reddit 跨版块用户、链接、转帖与评论重叠分析。</t>
-        </is>
-      </c>
-      <c r="M32" s="2" t="inlineStr">
+      <c r="L36" s="2" t="inlineStr">
+        <is>
+          <t>议题符合，且方法证据显示：16 年 Reddit 跨版块用户、链接、转帖与评论重叠分析。</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="inlineStr">
         <is>
           <t>分析11个主要政治子版块16年数据，从用户重叠、信息分享、跨帖、跨评论等维度揭示跨意识形态交流极低，极化由平台设计、治理、话语等多重因素交织导致。</t>
         </is>
       </c>
-      <c r="N32" s="2" t="inlineStr">
+      <c r="N36" s="2" t="inlineStr">
         <is>
           <t>鉴于目前缺乏能够全面评估Reddit各个方面如何导致该平台上政治两极分化的研究，本研究考察了16年间11个主要子版块（subreddits）中跨意识形态交流的动态变化。我们不仅分析了纯粹的文本元素，还探讨了子版块之间可能存在的各种重叠现象，包括共同用户、信息共享、跨版块发布内容、相互评论、链接到其他子版块以及用户所使用的讨论身份（discursive identities）。研究发现，这些重叠现象几乎不存在——即使是在讨论内容高度相似的子版块之间也是如此，而且这种现象并不仅仅局限于左派与右派的二元对立。我们认为，这些现象的产生是平台设计、版主管理方式、用户行为、讨论内容以及更广泛的社会政治背景共同作用的结果。研究结果表明，这种复杂的关系导致了Reddit上政治两极分化的持续存在；政治子版块的分化现象无法仅仅通过讨论内容、用户身份或平台设计来解释。此外，这些发现也挑战了人们将r/politics视为一个促进跨意识形态讨论与交流的“公共广场”的传统观点。</t>
         </is>
       </c>
-      <c r="O32" s="2" t="inlineStr">
+      <c r="O36" s="2" t="inlineStr">
         <is>
           <t>Motivated by the dearth of research providing a comprehensive assessment of how various aspects of Reddit contribute to political polarisation on the platform, this study examines the dynamics of cross-ideological communication across 11 major subreddits over 16 years. Going beyond purely textual elements, we analyse a broad range of possibilities for overlaps between subreddits. This includes common users, information-sharing, cross-posting, cross-commenting, links to other subreddits, and discursive identities. We observe minimal overlaps in all these indicators. This is true even for subreddits with highly similar discourses and extends beyond a left-right dichotomy. These patterns, we argue, emerge from an entanglement of platform design, moderation practices, user agency, discourses, and broader socio-political contexts. Our findings show how this entanglement leads to the sedimentation of polarisation on Reddit, wherein the fragmentation of political subreddits is irreducible to discourses, identities, or platform design alone. These findings also challenge the common framing of r/politics as a town square for cross-ideological deliberation and exposure.</t>
         </is>
       </c>
-      <c r="P32" s="6" t="inlineStr">
+      <c r="P36" s="6" t="inlineStr">
         <is>
           <t>10.1080/1369118x.2026.2623523</t>
         </is>
       </c>
-      <c r="Q32" s="6" t="inlineStr">
+      <c r="Q36" s="6" t="inlineStr">
         <is>
           <t>https://doi.org/10.1080/1369118x.2026.2623523</t>
         </is>
       </c>
-      <c r="R32" s="2" t="inlineStr">
+      <c r="R36" s="2" t="inlineStr">
         <is>
           <t>待获取</t>
         </is>
       </c>
-      <c r="S32" s="2" t="inlineStr">
+      <c r="S36" s="2" t="inlineStr">
         <is>
           <t>未开始</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:S32"/>
+  <autoFilter ref="A1:S36"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q2" r:id="rId2"/>
@@ -3758,6 +4122,14 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q31" r:id="rId60"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P32" r:id="rId61"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q32" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P33" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q33" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P34" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q34" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P35" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q35" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P36" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q36" r:id="rId70"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3769,7 +4141,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S12"/>
+  <dimension ref="A1:S1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -3890,993 +4262,8 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="C2" s="4" t="inlineStr">
-        <is>
-          <t>待全文确认</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>摘要不足</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>Platformed partner markets: online dating and gendered assortative mating in Europe</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="inlineStr">
-        <is>
-          <t>平台化的合作伙伴市场：欧洲的在线约会与基于性别的选择性配对行为</t>
-        </is>
-      </c>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>Zerui Tian</t>
-        </is>
-      </c>
-      <c r="I2" s="2" t="inlineStr">
-        <is>
-          <t>量化分析</t>
-        </is>
-      </c>
-      <c r="J2" s="2" t="inlineStr">
-        <is>
-          <t>在线约会平台；算法匹配；择偶同质性；数字平台</t>
-        </is>
-      </c>
-      <c r="K2" s="2" t="inlineStr">
-        <is>
-          <t>待确认</t>
-        </is>
-      </c>
-      <c r="L2" s="2" t="inlineStr">
-        <is>
-          <t>原表无摘要；需确认在线约会数据来源及是否使用计算方法。</t>
-        </is>
-      </c>
-      <c r="M2" s="2" t="inlineStr">
-        <is>
-          <t>论文考察欧洲在线约会平台中的性别化同质择偶现象，探讨平台化婚恋市场如何与性别化的匹配模式相互作用，但缺少摘要，具体数据与方法不明。</t>
-        </is>
-      </c>
-      <c r="N2" s="2" t="inlineStr"/>
-      <c r="O2" s="2" t="inlineStr"/>
-      <c r="P2" s="6" t="inlineStr">
-        <is>
-          <t>10.1080/1369118x.2026.2729550</t>
-        </is>
-      </c>
-      <c r="Q2" s="6" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.1080/1369118x.2026.2729550</t>
-        </is>
-      </c>
-      <c r="R2" s="2" t="inlineStr">
-        <is>
-          <t>待获取</t>
-        </is>
-      </c>
-      <c r="S2" s="2" t="inlineStr">
-        <is>
-          <t>未开始</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="B3" s="7" t="inlineStr">
-        <is>
-          <t>棕色</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>待全文确认</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>摘要不足</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-17</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>Toward inclusive online safety: evaluating the role of intersectionality on online abuse in the United Kingdom</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>迈向包容性的在线安全：评估交叉性因素在英国网络虐待问题中的作用</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>Kyle Beadle, Enrico Mariconti, Leonie Maria Tanczer, Marie Vasek</t>
-        </is>
-      </c>
-      <c r="I3" s="2" t="inlineStr">
-        <is>
-          <t>计算传播学</t>
-        </is>
-      </c>
-      <c r="J3" s="2" t="inlineStr">
-        <is>
-          <t>在线滥用；交叉性；社交媒体；英国</t>
-        </is>
-      </c>
-      <c r="K3" s="2" t="inlineStr">
-        <is>
-          <t>待确认</t>
-        </is>
-      </c>
-      <c r="L3" s="2" t="inlineStr">
-        <is>
-          <t>原表无摘要，且作者标为棕色待定；需由全文确认在线滥用的计算测量方法。</t>
-        </is>
-      </c>
-      <c r="M3" s="2" t="inlineStr">
-        <is>
-          <t>论文评估交叉性因素在英国在线滥用中的作用，旨在促进包容性在线安全，可能采用数据驱动方法分析网络言论。</t>
-        </is>
-      </c>
-      <c r="N3" s="2" t="inlineStr"/>
-      <c r="O3" s="2" t="inlineStr"/>
-      <c r="P3" s="6" t="inlineStr">
-        <is>
-          <t>10.1080/1369118x.2026.2713666</t>
-        </is>
-      </c>
-      <c r="Q3" s="6" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.1080/1369118x.2026.2713666</t>
-        </is>
-      </c>
-      <c r="R3" s="2" t="inlineStr">
-        <is>
-          <t>待获取</t>
-        </is>
-      </c>
-      <c r="S3" s="2" t="inlineStr">
-        <is>
-          <t>未开始</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="n">
-        <v>16</v>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="C4" s="4" t="inlineStr">
-        <is>
-          <t>待全文确认</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>摘要不足</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-15</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>Where digital hate finds its home: perpetrators' preferred affordances and their experiences with content moderation and user intervention</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>数字仇恨的滋生之地：施害者偏好的传播方式及其在内容审核和用户干预方面的经历</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>Giang-Truong Nguyen, Stephanie Buehrer, Kevin Koban, Jörg Matthes</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr"/>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>数字仇恨；社交媒体；内容审核</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>待确认</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>原表无摘要和方法；标题可能是访谈，也可能含平台行为数据。</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>研究数字仇恨散布者偏好的平台功能及其对内容审核和用户干预的体验。</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr"/>
-      <c r="O4" s="2" t="inlineStr"/>
-      <c r="P4" s="6" t="inlineStr">
-        <is>
-          <t>10.1080/1369118x.2026.2663190</t>
-        </is>
-      </c>
-      <c r="Q4" s="6" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.1080/1369118x.2026.2663190</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>待获取</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>未开始</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="C5" s="4" t="inlineStr">
-        <is>
-          <t>待全文确认</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>摘要不足</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>‘Cool! I wanna try it!’: online exposure to e-cigarette advertisements increases e-cigarette susceptibility among U.S. sexual minority young adults</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>“太酷了！我想试试！”：在线接触电子香烟广告增加了美国性少数群体年轻成年人使用电子香烟的倾向</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>Yuyuan Kylie Lai, Jizhou Francis Ye, M. Liu</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr"/>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>电子烟广告；在线暴露；性少数青年；健康传播</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>待确认</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>标题呈现暴露效应，但原表无摘要；需确认是否为在线随机实验。</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>研究在线电子烟广告暴露如何影响美国性少数青年对电子烟的易感性，关注数字广告的传播效果。</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr"/>
-      <c r="O5" s="2" t="inlineStr"/>
-      <c r="P5" s="6" t="inlineStr">
-        <is>
-          <t>10.1080/1369118x.2026.2713667</t>
-        </is>
-      </c>
-      <c r="Q5" s="6" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.1080/1369118x.2026.2713667</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>待获取</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>未开始</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="n">
-        <v>23</v>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="C6" s="4" t="inlineStr">
-        <is>
-          <t>待全文确认</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>摘要不足</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-05</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>Did you make this for me? A two-country study on individuals’ perceptions of tailoring in online political ads</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>这是你为我准备的吗？一项关于个人对在线政治广告中定制化内容感知的跨国研究</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>Christina Gahn, J.G. Vrielink, Sanne Kruikemeier</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>量化分析</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>政治广告；定制化；在线广告</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>待确认</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>原表无摘要；需区分在线广告实验与一般跨国问卷。</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>跨国研究个体对在线政治广告定制化程度的感知及其影响，属于政治传播领域。</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr"/>
-      <c r="O6" s="2" t="inlineStr"/>
-      <c r="P6" s="6" t="inlineStr">
-        <is>
-          <t>10.1080/1369118x.2026.2703856</t>
-        </is>
-      </c>
-      <c r="Q6" s="6" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.1080/1369118x.2026.2703856</t>
-        </is>
-      </c>
-      <c r="R6" s="2" t="inlineStr">
-        <is>
-          <t>待获取</t>
-        </is>
-      </c>
-      <c r="S6" s="2" t="inlineStr">
-        <is>
-          <t>未开始</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="n">
-        <v>65</v>
-      </c>
-      <c r="B7" s="7" t="inlineStr">
-        <is>
-          <t>棕色</t>
-        </is>
-      </c>
-      <c r="C7" s="4" t="inlineStr">
-        <is>
-          <t>待全文确认</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>摘要不足</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-27</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>Calling out disclosures, protecting followers: the new governors of influencer culture on TikTok</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>揭露虚假信息，保护追随者：TikTok上影响者文化的新“监管者”</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>Taylor Annabell</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr"/>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>TikTok；网红文化；社交媒体平台；平台治理</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>待确认</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>原表无摘要，且作者标为棕色待定；需确认是否含计算数据或在线实验。</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>探讨TikTok上网红信息披露行为及其对关注者的保护，分析平台治理中的新机制。</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr"/>
-      <c r="O7" s="2" t="inlineStr"/>
-      <c r="P7" s="6" t="inlineStr">
-        <is>
-          <t>10.1080/1369118x.2026.2674878</t>
-        </is>
-      </c>
-      <c r="Q7" s="6" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.1080/1369118x.2026.2674878</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>待获取</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>未开始</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="n">
-        <v>67</v>
-      </c>
-      <c r="B8" s="7" t="inlineStr">
-        <is>
-          <t>棕色</t>
-        </is>
-      </c>
-      <c r="C8" s="4" t="inlineStr">
-        <is>
-          <t>待全文确认</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>摘要不足</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-27</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>Price, proficiency, or permission: assessing platform data access for election research</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>价格、熟练度还是许可：评估选举研究中的平台数据访问权限</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>Josephine Lukito, Kayo Mimizuka</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>计算传播学</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>平台数据；选举研究；数据获取</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>待确认</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>原表无摘要，虽标为计算传播学，但标题可能是方法政策研究；需全文确认。</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>论文评估平台数据访问的价格、技能和权限因素，探讨其对选举研究的影响，关注平台API及数据可得性问题。</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr"/>
-      <c r="O8" s="2" t="inlineStr"/>
-      <c r="P8" s="6" t="inlineStr">
-        <is>
-          <t>10.1080/1369118x.2026.2667921</t>
-        </is>
-      </c>
-      <c r="Q8" s="6" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.1080/1369118x.2026.2667921</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>待获取</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>未开始</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="n">
-        <v>70</v>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="C9" s="4" t="inlineStr">
-        <is>
-          <t>待全文确认</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>摘要不足</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-25</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>Algorithmic ambivalence: LGBTQ+ social media and mental health among Chinese gay men</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>算法的矛盾性：中国男同性恋者的社交媒体使用与心理健康</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>Lazar Dragić, KJ Kaixin Deng</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>计算传播学</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>算法；社交媒体；心理健康；LGBTQ+</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>待确认</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>原表无摘要，虽标为计算传播学；需确认算法研究采用的是平台数据还是传统调查。</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>研究中国男同性恋者在社交媒体中算法矛盾心理及其对心理健康的影响，结合算法与社媒使用议题。</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr"/>
-      <c r="O9" s="2" t="inlineStr"/>
-      <c r="P9" s="6" t="inlineStr">
-        <is>
-          <t>10.1080/1369118x.2026.2678366</t>
-        </is>
-      </c>
-      <c r="Q9" s="6" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.1080/1369118x.2026.2678366</t>
-        </is>
-      </c>
-      <c r="R9" s="2" t="inlineStr">
-        <is>
-          <t>待获取</t>
-        </is>
-      </c>
-      <c r="S9" s="2" t="inlineStr">
-        <is>
-          <t>未开始</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="n">
-        <v>71</v>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="C10" s="4" t="inlineStr">
-        <is>
-          <t>待全文确认</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>摘要不足</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-24</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>Stigma to skepticism: online consumer narratives of obesity management medications</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>对怀疑态度的污名化：在线消费者关于肥胖管理药物的叙述</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>Rumaila Abbas, Munyaradzi W. Nyadzayo</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr"/>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>健康传播；在线叙事；消费者视角</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>待确认</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>原表无摘要；需确认‘在线消费者叙事’采用计算文本方法还是质性分析。</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>论文探讨在线消费者关于肥胖管理药物的叙事，分析从污名到怀疑的转变，可能基于社交媒体内容，但方法未明确。</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr"/>
-      <c r="O10" s="2" t="inlineStr"/>
-      <c r="P10" s="6" t="inlineStr">
-        <is>
-          <t>10.1080/1369118x.2026.2678364</t>
-        </is>
-      </c>
-      <c r="Q10" s="6" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.1080/1369118x.2026.2678364</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>待获取</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>未开始</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="n">
-        <v>77</v>
-      </c>
-      <c r="B11" s="7" t="inlineStr">
-        <is>
-          <t>棕色</t>
-        </is>
-      </c>
-      <c r="C11" s="4" t="inlineStr">
-        <is>
-          <t>待全文确认</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>摘要不足</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-08</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>From player to asset: venture labor in axie infinity</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>从玩家到资产：《Axie Infinity》中的风险劳动（From player to asset: Venture labor in Axie Infinity）</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>Daniel Nielsen, Anne Mette Thorhauge</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>计算传播学</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>社交媒体数据；数字劳动；游戏经济</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>待确认</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>摘要仅明确 Discord 数据由爬虫取得，未说明分析技术；需全文确认是否超出人工质性编码。</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>通过爬取Discord社区数据，分析Axie Infinity奖学金申请者的申请文本，揭示其自我资产化策略，即玩家将劳动与困境呈现为投资资产以争取机会。</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>本文通过Axie Infinity（Sky Mavis，引用来源：Citation2018）的案例研究，探讨了“玩即赚”（play-to-earn）游戏中的加密货币经济现象。由于进入成本较高，出现了一种“奖学金”机制：资产所有者（通常是年轻菲律宾成年人）将Axie宠物出租给申请者，并从中获取收益的一部分。我们利用从四个Discord社区收集的数据，分析了这些奖学金申请情况，发现了三种战略性的思维框架：  
-（1）将经济困境视为一种杠杆：申请者将这种不稳定的契约关系重新定义为管理者的慈善行为。  
-（2）将经济不确定性视为一种策略：申请者将自己视为能够产生收益的“资产”，同时接受不稳定的合同条款。  
-（3）将自我剥削和忠诚度视为一种资产：申请者承诺对游戏系统保持忠诚，从而将自身的奉献精神转化为一种额外的“资产”。  
-我们将这种现象称为“自我资产化”（self-assetisation）：个体将自己的劳动力、情感以及社会经济状况视为可投资的资产，同时将自己定位为劳动者和具有投机价值的对象，从而间接参与了剥削过程。</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>This paper examines crypto economies in ‘play-to-earn’ games via a case study of Axie Infinity (Sky Mavis, Citation2018). High entry costs spawned ‘scholarships’ in which asset-owning managers lease Axies to applicants – largely young Filipino adults – in exchange for a share of earnings. Using scraped data from four Discord communities, we analyse scholarship applications, revealing three strategic framings: (1) Hardship as leverage: Applicants recast precarious contracting as managerial philanthropy. (2) Precarity as strategy: Applicants present themselves as return-generating assets while accepting precarious terms. (3) Self-exploitation and allegiance as assets: Applicants pledge loyalty to advance within the system, turning dedication into an additional asset. We theorise this as self-assetisation: individuals present labour, affect, and socio-economic circumstances as investable assets, positioning themselves as both workers and speculative value objects, being indirectly complicit in exploitation.</t>
-        </is>
-      </c>
-      <c r="P11" s="6" t="inlineStr">
-        <is>
-          <t>10.1080/1369118x.2026.2669800</t>
-        </is>
-      </c>
-      <c r="Q11" s="6" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.1080/1369118x.2026.2669800</t>
-        </is>
-      </c>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t>待获取</t>
-        </is>
-      </c>
-      <c r="S11" s="2" t="inlineStr">
-        <is>
-          <t>未开始</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="n">
-        <v>129</v>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="C12" s="4" t="inlineStr">
-        <is>
-          <t>待全文确认</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>摘要不足</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>2026-02-27</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>Nudging against judging? Mitigating anti-LGBTQIA + online hostility by raising bystanders’ awareness and behavioral intentions</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>“通过提高旁观者的意识和行为倾向来减轻对LGBTQIA群体的敌意”——一种对抗歧视的策略</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>Melanie Saumer, Kevin Koban, Jörg Matthes</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>传统量化分析</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>在线敌意；旁观者干预；社会助推；LGBTQIA+</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>待确认</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>摘要明确为 3×3 实验，但未说明是否在线实施；按用户口径暂不直接纳入。</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>实验研究考察社会助推对旁观者干预反LGBTQIA+在线敌意的影响，发现敌意类型影响反应，助推效果不稳定，少数增加负面情绪但未促进行为。</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>旁观者干预是一种有前景的手段，可用于应对网络上日益增多的针对LGBTQIA+群体的敌对行为。这项实验研究通过3×3的设计框架，探讨了不同类型的社交提示（意识提示、意识与行为结合的提示以及无提示[对照组]）以及不同类型的敌对行为（不文明行为、不宽容行为和文明行为[对照组]）对旁观者反应的影响。研究结果证实，敌对行为的类型显著影响了人们对相关行为的接受度、负面情绪、干预意愿以及内容审核的偏好。然而，社交提示的效果并不一致：意识提示有时会加剧负面情绪（尤其是在与不宽容行为结合时），但未能有效促进旁观者的干预行为。这些发现支持了“期望违背理论”（Expectancy Violation Theory）和“旁观者干预模型”（Bystander Intervention Model），表明敌对言论会引发旁观者的反应，而社交提示则可能引发抵触情绪或显得多余。个体差异（包括对LGBTQIA+群体的态度、政治立场以及被动使用社交媒体的习惯）进一步影响了旁观者的干预倾向。文章还讨论了这些发现对数字干预措施和政策制定的启示。</t>
-        </is>
-      </c>
-      <c r="O12" s="2" t="inlineStr">
-        <is>
-          <t>Bystander interventions are a promising tool to counteract the rising instances of anti-LGBTQIA+ hostility online. This experimental study investigates how social nudges influence bystander reactions within a 3 × 3 design, varying nudge type (awareness nudge vs. awareness &amp; behavioral nudge vs. no nudge [control]) and hostility type (incivility vs. intolerance vs. civil [control]). Results confirmed that hostility type significantly influenced perceived acceptability, negative emotions, intervention intentions, and content moderation preferences. However, nudging effects were inconsistent, with awareness nudging sporadically increasing negative emotions, particularly when combined with intolerance, but failing to enhance intervention behaviors. These findings support the Expectancy Violation Theory and the Bystander Intervention Model, suggesting that hostile speech reliably triggers bystander responses, whereas nudges may induce reactance or appear redundant. Individual differences, including LGBTQIA+ attitudes, political orientation, and passive social media use, further shaped intervention tendencies. Implications for digital interventions and policy development are discussed.</t>
-        </is>
-      </c>
-      <c r="P12" s="6" t="inlineStr">
-        <is>
-          <t>10.1080/1369118x.2026.2636134</t>
-        </is>
-      </c>
-      <c r="Q12" s="6" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.1080/1369118x.2026.2636134</t>
-        </is>
-      </c>
-      <c r="R12" s="2" t="inlineStr">
-        <is>
-          <t>待获取</t>
-        </is>
-      </c>
-      <c r="S12" s="2" t="inlineStr">
-        <is>
-          <t>未开始</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:S12"/>
-  <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P2" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q2" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P3" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q3" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P4" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q4" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P5" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q5" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P6" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q6" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P7" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q7" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P8" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q8" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P9" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q9" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P10" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q10" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P11" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q11" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P12" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q12" r:id="rId22"/>
-  </hyperlinks>
+  <autoFilter ref="A1:S1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -5052,7 +4439,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>议题符合，且摘要明确显示：主题建模、文本社群检测与时间比较。</t>
+          <t>议题符合，且方法证据显示：主题建模、文本社群检测与时间比较。</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -5144,24 +4531,24 @@
           <t>无</t>
         </is>
       </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>待全文确认</t>
+      <c r="C3" s="8" t="inlineStr">
+        <is>
+          <t>排除</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>摘要不足</t>
+          <t>出版方全文方法明确</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>原表无摘要；需确认在线约会数据来源及是否使用计算方法。</t>
+          <t>全文显示使用九国 Generations and Gender Survey II 与加权多项 Logit；属于传统调查数据分析。</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>不适用</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -5460,7 +4847,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>议题符合，且摘要明确显示：Meta 广告库全集、投放支出与受众定向数据。</t>
+          <t>议题符合，且方法证据显示：Meta 广告库全集、投放支出与受众定向数据。</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -5564,7 +4951,7 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>议题符合，且摘要明确显示：Facebook 捐赠数字痕迹，并含预注册题序实验。</t>
+          <t>议题符合，且方法证据显示：Facebook 捐赠数字痕迹，并含预注册题序实验。</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -5980,7 +5367,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>议题符合，且摘要明确显示：LLM 分类、动态提及网络与图机器学习。</t>
+          <t>议题符合，且方法证据显示：LLM 分类、动态提及网络与图机器学习。</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -6280,24 +5667,24 @@
           <t>棕色</t>
         </is>
       </c>
-      <c r="C14" s="4" t="inlineStr">
-        <is>
-          <t>待全文确认</t>
+      <c r="C14" s="8" t="inlineStr">
+        <is>
+          <t>排除</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>摘要不足</t>
+          <t>出版方全文方法明确</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>原表无摘要，且作者标为棕色待定；需由全文确认在线滥用的计算测量方法。</t>
+          <t>全文显示使用 Ofcom 多年调查与 MAIHDA；没有平台数字痕迹或计算内容分析。</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>不适用</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6480,24 +5867,24 @@
           <t>无</t>
         </is>
       </c>
-      <c r="C16" s="4" t="inlineStr">
-        <is>
-          <t>待全文确认</t>
+      <c r="C16" s="8" t="inlineStr">
+        <is>
+          <t>排除</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>摘要不足</t>
+          <t>出版方全文方法明确</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>原表无摘要和方法；标题可能是访谈，也可能含平台行为数据。</t>
+          <t>全文显示为四国配额调查、潜在剖面分析与结构模型；属于传统调查研究。</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>不适用</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6876,24 +6263,24 @@
           <t>无</t>
         </is>
       </c>
-      <c r="C20" s="4" t="inlineStr">
-        <is>
-          <t>待全文确认</t>
+      <c r="C20" s="8" t="inlineStr">
+        <is>
+          <t>排除</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>摘要不足</t>
+          <t>出版方全文方法明确</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>标题呈现暴露效应，但原表无摘要；需确认是否为在线随机实验。</t>
+          <t>全文摘要显示使用 PATH 纵向调查，研究自然广告暴露；不是在线实验或计算方法。</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>不适用</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7164,24 +6551,24 @@
           <t>无</t>
         </is>
       </c>
-      <c r="C23" s="4" t="inlineStr">
-        <is>
-          <t>待全文确认</t>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>纳入</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>摘要不足</t>
+          <t>出版方全文方法明确</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>原表无摘要；需区分在线广告实验与一般跨国问卷。</t>
+          <t>议题符合，且方法证据显示：移动经验抽样与真实政治广告截图的数据捐赠。</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>数据捐赠＋数字痕迹</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -7492,7 +6879,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>议题符合，且摘要明确显示：基于代理的社会模拟，操控网络同质性与选择性暴露。</t>
+          <t>议题符合，且方法证据显示：基于代理的社会模拟，操控网络同质性与选择性暴露。</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -8548,7 +7935,7 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>议题符合，且摘要明确显示：1200 万条 Facebook 帖文、LLM 分类、时间序列与回归。</t>
+          <t>议题符合，且方法证据显示：1200 万条 Facebook 帖文、LLM 分类、时间序列与回归。</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -8764,7 +8151,7 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>议题符合，且摘要明确显示：在线评论的词嵌入与语义距离测量。</t>
+          <t>议题符合，且方法证据显示：在线评论的词嵌入与语义距离测量。</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
@@ -9304,7 +8691,7 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>议题符合，且摘要明确显示：6829 篇新闻的主题建模与情感分析。</t>
+          <t>议题符合，且方法证据显示：6829 篇新闻的主题建模与情感分析。</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
@@ -9952,7 +9339,7 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>议题符合，且摘要明确显示：对 ChatGPT-4o mini 选举回答进行系统审计。</t>
+          <t>议题符合，且方法证据显示：对 ChatGPT-4o mini 选举回答进行系统审计。</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
@@ -10600,7 +9987,7 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>议题符合，且摘要明确显示：Facebook 品牌帖文构成的四个二部网络。</t>
+          <t>议题符合，且方法证据显示：Facebook 品牌帖文构成的四个二部网络。</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
@@ -10816,7 +10203,7 @@
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>议题符合，且摘要明确显示：2.29 万帖文、115 万评论与广义线性混合模型。</t>
+          <t>议题符合，且方法证据显示：2.29 万帖文、115 万评论与广义线性混合模型。</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
@@ -11640,24 +11027,24 @@
           <t>棕色</t>
         </is>
       </c>
-      <c r="C65" s="4" t="inlineStr">
-        <is>
-          <t>待全文确认</t>
+      <c r="C65" s="8" t="inlineStr">
+        <is>
+          <t>排除</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>摘要不足</t>
+          <t>出版方全文方法明确</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>原表无摘要，且作者标为棕色待定；需确认是否含计算数据或在线实验。</t>
+          <t>全文显示以少量 TikTok 视频及评论开展话语分析；爬虫只用于取数，核心分析为质性解释。</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>不适用</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
@@ -11852,24 +11239,24 @@
           <t>棕色</t>
         </is>
       </c>
-      <c r="C67" s="4" t="inlineStr">
-        <is>
-          <t>待全文确认</t>
+      <c r="C67" s="8" t="inlineStr">
+        <is>
+          <t>排除</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>摘要不足</t>
+          <t>出版方全文方法明确</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>原表无摘要，虽标为计算传播学，但标题可能是方法政策研究；需全文确认。</t>
+          <t>全文通过人工汇编和系统编码比较 72 种数据访问工具；研究对象与计算方法有关，但本身未使用计算分析。</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>不适用</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
@@ -12160,24 +11547,24 @@
           <t>无</t>
         </is>
       </c>
-      <c r="C70" s="4" t="inlineStr">
-        <is>
-          <t>待全文确认</t>
+      <c r="C70" s="8" t="inlineStr">
+        <is>
+          <t>排除</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>摘要不足</t>
+          <t>出版方全文方法明确</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>原表无摘要，虽标为计算传播学；需确认算法研究采用的是平台数据还是传统调查。</t>
+          <t>全文显示为 23 次半结构化访谈与人工主题分析。</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>不适用</t>
         </is>
       </c>
       <c r="G70" s="2" t="inlineStr">
@@ -12260,24 +11647,24 @@
           <t>无</t>
         </is>
       </c>
-      <c r="C71" s="4" t="inlineStr">
-        <is>
-          <t>待全文确认</t>
+      <c r="C71" s="5" t="inlineStr">
+        <is>
+          <t>纳入</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>摘要不足</t>
+          <t>出版方全文方法明确</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>原表无摘要；需确认‘在线消费者叙事’采用计算文本方法还是质性分析。</t>
+          <t>议题符合，且方法证据显示：Python 抓取 5789 条 Reddit 评论，使用 Top2Vec 与 LLM 辅助主题整理。</t>
         </is>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>计算文本分析＋LLM</t>
         </is>
       </c>
       <c r="G71" s="2" t="inlineStr">
@@ -12368,7 +11755,7 @@
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>议题符合，且摘要明确显示：Meta 广告与定向数据集、4760 条广告的多模态编码。</t>
+          <t>议题符合，且方法证据显示：Meta 广告与定向数据集、4760 条广告的多模态编码。</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr">
@@ -12476,7 +11863,7 @@
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>议题符合，且摘要明确显示：2×2×2 的社交媒体假新闻在线实验。</t>
+          <t>议题符合，且方法证据显示：2×2×2 的社交媒体假新闻在线实验。</t>
         </is>
       </c>
       <c r="F73" s="2" t="inlineStr">
@@ -12896,24 +12283,24 @@
           <t>棕色</t>
         </is>
       </c>
-      <c r="C77" s="4" t="inlineStr">
-        <is>
-          <t>待全文确认</t>
+      <c r="C77" s="5" t="inlineStr">
+        <is>
+          <t>纳入</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>摘要不足</t>
+          <t>出版方全文方法明确</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>摘要仅明确 Discord 数据由爬虫取得，未说明分析技术；需全文确认是否超出人工质性编码。</t>
+          <t>议题符合，且方法证据显示：Discord 导出 1.33 万条申请，使用 R、正则表达式与随机抽样后开展主题分析。</t>
         </is>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>计算采集与预处理＋质性分析</t>
         </is>
       </c>
       <c r="G77" s="2" t="inlineStr">
@@ -13020,7 +12407,7 @@
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>议题符合，且摘要明确显示：代表性样本的被动浏览记录与恶意域名数据匹配。</t>
+          <t>议题符合，且方法证据显示：代表性样本的被动浏览记录与恶意域名数据匹配。</t>
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr">
@@ -13444,7 +12831,7 @@
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>议题符合，且摘要明确显示：3.8 万条 Reddit 评论的结构主题模型。</t>
+          <t>议题符合，且方法证据显示：3.8 万条 Reddit 评论的结构主题模型。</t>
         </is>
       </c>
       <c r="F82" s="2" t="inlineStr">
@@ -13660,7 +13047,7 @@
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>议题符合，且摘要明确显示：400 万条 X 帖文、转发网络、语言对齐与回音室分数。</t>
+          <t>议题符合，且方法证据显示：400 万条 X 帖文、转发网络、语言对齐与回音室分数。</t>
         </is>
       </c>
       <c r="F84" s="2" t="inlineStr">
@@ -13884,7 +13271,7 @@
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>议题符合，且摘要明确显示：340 万条微博与双重差分设计。</t>
+          <t>议题符合，且方法证据显示：340 万条微博与双重差分设计。</t>
         </is>
       </c>
       <c r="F86" s="2" t="inlineStr">
@@ -14216,7 +13603,7 @@
       </c>
       <c r="E89" s="2" t="inlineStr">
         <is>
-          <t>议题符合，且摘要明确显示：多层 Telegram 数据、纵向内容、URL 与网络分析。</t>
+          <t>议题符合，且方法证据显示：多层 Telegram 数据、纵向内容、URL 与网络分析。</t>
         </is>
       </c>
       <c r="F89" s="2" t="inlineStr">
@@ -14324,7 +13711,7 @@
       </c>
       <c r="E90" s="2" t="inlineStr">
         <is>
-          <t>议题符合，且摘要明确显示：TikTok 视频与评论的计算多模态分析。</t>
+          <t>议题符合，且方法证据显示：TikTok 视频与评论的计算多模态分析。</t>
         </is>
       </c>
       <c r="F90" s="2" t="inlineStr">
@@ -14540,7 +13927,7 @@
       </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
-          <t>议题符合，且摘要明确显示：X 帖文的社会网络分析，并与访谈互证。</t>
+          <t>议题符合，且方法证据显示：X 帖文的社会网络分析，并与访谈互证。</t>
         </is>
       </c>
       <c r="F92" s="2" t="inlineStr">
@@ -14756,7 +14143,7 @@
       </c>
       <c r="E94" s="2" t="inlineStr">
         <is>
-          <t>议题符合，且摘要明确显示：2500 万场在线比赛的个体数据与结构引力模型。</t>
+          <t>议题符合，且方法证据显示：2500 万场在线比赛的个体数据与结构引力模型。</t>
         </is>
       </c>
       <c r="F94" s="2" t="inlineStr">
@@ -15080,7 +14467,7 @@
       </c>
       <c r="E97" s="2" t="inlineStr">
         <is>
-          <t>议题符合，且摘要明确显示：145 篇全文的 BERTopic 建模。</t>
+          <t>议题符合，且方法证据显示：145 篇全文的 BERTopic 建模。</t>
         </is>
       </c>
       <c r="F97" s="2" t="inlineStr">
@@ -15404,7 +14791,7 @@
       </c>
       <c r="E100" s="2" t="inlineStr">
         <is>
-          <t>议题符合，且摘要明确显示：3879 条 Reddit 评论的主题建模。</t>
+          <t>议题符合，且方法证据显示：3879 条 Reddit 评论的主题建模。</t>
         </is>
       </c>
       <c r="F100" s="2" t="inlineStr">
@@ -16484,7 +15871,7 @@
       </c>
       <c r="E110" s="2" t="inlineStr">
         <is>
-          <t>议题符合，且摘要明确显示：Reddit 帖文与评论的事件时间线和时间序列分析。</t>
+          <t>议题符合，且方法证据显示：Reddit 帖文与评论的事件时间线和时间序列分析。</t>
         </is>
       </c>
       <c r="F110" s="2" t="inlineStr">
@@ -17348,7 +16735,7 @@
       </c>
       <c r="E118" s="2" t="inlineStr">
         <is>
-          <t>议题符合，且摘要明确显示：语言、音频与主题特征的多模态时间序列。</t>
+          <t>议题符合，且方法证据显示：语言、音频与主题特征的多模态时间序列。</t>
         </is>
       </c>
       <c r="F118" s="2" t="inlineStr">
@@ -17788,7 +17175,7 @@
       </c>
       <c r="E122" s="2" t="inlineStr">
         <is>
-          <t>议题符合，且摘要明确显示：4131 条推文的隐喻频率与原创性数据化测量。</t>
+          <t>议题符合，且方法证据显示：4131 条推文的隐喻频率与原创性数据化测量。</t>
         </is>
       </c>
       <c r="F122" s="2" t="inlineStr">
@@ -18532,24 +17919,24 @@
           <t>无</t>
         </is>
       </c>
-      <c r="C129" s="4" t="inlineStr">
-        <is>
-          <t>待全文确认</t>
+      <c r="C129" s="5" t="inlineStr">
+        <is>
+          <t>纳入</t>
         </is>
       </c>
       <c r="D129" s="2" t="inlineStr">
         <is>
-          <t>摘要不足</t>
+          <t>出版方全文方法明确</t>
         </is>
       </c>
       <c r="E129" s="2" t="inlineStr">
         <is>
-          <t>摘要明确为 3×3 实验，但未说明是否在线实施；按用户口径暂不直接纳入。</t>
+          <t>议题符合，且方法证据显示：预注册 3×3 在线实验，操控 Instagram 仿真帖文的敌意类型与提示方式。</t>
         </is>
       </c>
       <c r="F129" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>在线实验</t>
         </is>
       </c>
       <c r="G129" s="2" t="inlineStr">
@@ -18652,7 +18039,7 @@
       </c>
       <c r="E130" s="2" t="inlineStr">
         <is>
-          <t>议题符合，且摘要明确显示：五种语言约 1500 万条推文的计算与质性分析。</t>
+          <t>议题符合，且方法证据显示：五种语言约 1500 万条推文的计算与质性分析。</t>
         </is>
       </c>
       <c r="F130" s="2" t="inlineStr">
@@ -18984,7 +18371,7 @@
       </c>
       <c r="E133" s="2" t="inlineStr">
         <is>
-          <t>议题符合，且摘要明确显示：三平台趋势数据与跨平台注意力效应估计。</t>
+          <t>议题符合，且方法证据显示：三平台趋势数据与跨平台注意力效应估计。</t>
         </is>
       </c>
       <c r="F133" s="2" t="inlineStr">
@@ -19416,7 +18803,7 @@
       </c>
       <c r="E137" s="2" t="inlineStr">
         <is>
-          <t>议题符合，且摘要明确显示：69,421 个专利家族的主题聚类。</t>
+          <t>议题符合，且方法证据显示：69,421 个专利家族的主题聚类。</t>
         </is>
       </c>
       <c r="F137" s="2" t="inlineStr">
@@ -19848,7 +19235,7 @@
       </c>
       <c r="E141" s="2" t="inlineStr">
         <is>
-          <t>议题符合，且摘要明确显示：在中英文预训练语言模型上实施 FMAT 偏见审计。</t>
+          <t>议题符合，且方法证据显示：在中英文预训练语言模型上实施 FMAT 偏见审计。</t>
         </is>
       </c>
       <c r="F141" s="2" t="inlineStr">
@@ -19956,7 +19343,7 @@
       </c>
       <c r="E142" s="2" t="inlineStr">
         <is>
-          <t>议题符合，且摘要明确显示：16 年 Reddit 跨版块用户、链接、转帖与评论重叠分析。</t>
+          <t>议题符合，且方法证据显示：16 年 Reddit 跨版块用户、链接、转帖与评论重叠分析。</t>
         </is>
       </c>
       <c r="F142" s="2" t="inlineStr">

--- a/outputs/ICS-2026-计算传播学精选.xlsx
+++ b/outputs/ICS-2026-计算传播学精选.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="筛选说明" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="明确纳入" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="待全文确认" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="完整筛选记录" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="筛选说明" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="明确纳入" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="待全文确认" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="完整筛选记录" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'明确纳入'!$A$1:$X$36</definedName>
@@ -866,7 +866,7 @@
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>以主题模型与文本社群检测分析欧盟委员会虚假信息话语，议题与方法均属计算传播。</t>
+          <t>值得关注的地方在于，论文没有把“虚假信息”当作现成标签，而是把政策机构如何定义问题本身变成研究对象。计算分析显示，欧盟委员会长期借助战争和传染病隐喻，将责任推向敌对国家、平台和易受骗的公民；到 2023—2024 年，AI 又被纳入放大风险的叙事。它适合用于讨论问题框架如何预先限定平台治理、内容清除和媒介素养等政策答案。</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
@@ -978,7 +978,7 @@
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>使用Meta广告库API采集选举广告数据，分析政党在社交平台的定向策略，属计算传播研究。</t>
+          <t>这篇文章把政治传播研究中常被忽略的付费广告置于中心，并同时观察广告说了什么、花了多少钱、投给了谁。结果显示瑞典左右翼政党在负面竞选和人口定向上采取不同策略，也说明平台的付费功能并非中性的传播通道，而会进入政党的受众选择与资源配置。</t>
         </is>
       </c>
       <c r="Q3" s="2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>使用Facebook数字追踪数据与调查对比，分析政治活动测量的准确性，属社交媒体与计算方法结合。</t>
+          <t>这是一篇很有用的方法校准研究。它直接拿问卷回答与同一人的 Facebook 行为记录比较，发现用户往往低估一般使用、又高估政治参与，而且题目从总体到具体的排列更可靠。对依赖自报社交媒体行为的研究来说，这些结果能具体说明测量误差会出现在哪里，也展示了数据捐赠怎样用于验证传统问卷。</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>使用大规模X数据、LLM分类、网络分析与图机器学习，属于典型计算方法研究传播议题。</t>
+          <t>论文把立场识别、不文明语言测量和互动网络连在一起，研究的不只是“哪一方更不文明”，而是不文明表达怎样沿着提及关系扩散并跨越意识形态边界。它为冲突螺旋理论提供了可追踪的动态证据，也适合作为大型语言模型与网络分析组合使用的案例。</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -1318,7 +1318,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>使用基于代理的模拟方法研究社交媒体过滤气泡与网络结构对回音室的影响，属计算传播核心议题。</t>
+          <t>这篇文章适合用来检验一个经常被过度简化的判断：过滤算法是否会自动制造并固化回音室。模型把网络同质性与选择性暴露分开操控，结果显示信息暴露确实会影响回音室的形成，但人为形成的回音室即使处在过滤算法下也未必长期维持。它的价值在于把“算法—网络结构—意见变化”拆成可重复检验的条件；作者还在 OSF 公开了模型、输入和输出数据。</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1434,7 +1434,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>使用LLM分类、时间序列分析和回归建模，分析Facebook党派网络的纵向情感参与，属典型计算传播研究。</t>
+          <t>文章用三年纵向数据挑战了“高度党派化社群始终按固定方式运作”的想象。卢拉就职和 2023 年 1 月事件之后，这些亲博索纳罗社群的情绪强度下降、内部讨论增加，说明政治事件会重新组织看似封闭的回音室。两个行为指标也为长期比较情感反应与互动方式提供了可复用的测量思路。</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1550,7 +1550,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>使用词嵌入分析社交媒体评论，研究在线性别辩论中的道德框架，属计算传播典型议题。</t>
+          <t>它把“如何称呼事件中的人”与“如何对他们作道德判断”放进同一计算框架。研究发现，性别化称谓更容易连接广泛而两极化的道德基础，性别中立称谓则更偏向程序和角色评价。这种设计能把网络性别争论中的道德边界从抽象概念转成可比较的语义关系。</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1666,7 +1666,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>使用主题建模和情感分析等计算方法，研究AI媒体框架与政治传播议题，属计算传播。</t>
+          <t>文章兼有长时段、跨地区与可比较的媒体样本，能看到 AI 报道从技术想象走向政治化的过程。剑桥分析事件和 ChatGPT 发布构成两个转折点，全球北方媒体整体更悲观、南方媒体更乐观。它提供了一幅地缘政治、风险认知与 AI 媒体框架相互作用的经验地图。</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1782,7 +1782,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>研究生成式AI在选举中的信息准确性与治理影响，采用混合方法审计ChatGPT输出，主题和方法均属计算传播。</t>
+          <t>这篇文章的贡献不只在于列出 ChatGPT 的错误，而是提出“生成性治理”这一观察角度：平台已经从筛选人类内容转向直接生产用户看到的政治信息。选举期间出现的不准确、遗漏和回避性回答因此被放进平台权力与问责问题中考察，很适合作为生成式 AI 政治传播审计的案例。</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1898,7 +1898,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>使用Facebook数据构建双模网络，分析社交媒体平台上的隐性关系结构，属于计算传播研究。</t>
+          <t>论文抓住了平台界面中一种容易被忽略的关系：品牌帖文背后的合作伙伴与发布页面如何结成战略网络。四个二部网络让这些近乎不可见的合作变得可观察，也揭示新闻媒体等传统机构在平台盈利逻辑下如何重新安排角色。它对研究平台化传播中的组织关系很有启发。</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -2014,7 +2014,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>使用微博大规模数据和多模态框架分析，探讨性别对抗话语的传播机制，属典型计算传播研究。</t>
+          <t>文章把帖文的文字与视觉框架、发布者身份和评论反应放进同一模型。结果显示，煽动性和个性化框架会加剧性别对立，外群体身份发布时更明显，而娱乐性框架反而减弱对立。它把“性别冲突为什么会病毒式扩散”落实到了可检验的内容形式与身份线索上。</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -2126,7 +2126,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>研究 Reddit 上肥胖管理药物的消费者叙事，使用 Python 抓取、Top2Vec 与 LLM 辅助主题整理，议题与计算文本方法均符合本项目口径。</t>
+          <t>这篇文章呈现了肥胖管理药物讨论中并存的四组张力：污名、获取不平等、品牌与错误信息混淆，以及对疗效和风险的怀疑。它的价值在于把主题发现与网络社群中的意义协商结合起来，既保留大规模文本的轮廓，也没有把健康传播简化成词频排名。</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -2242,7 +2242,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>研究政治社交媒体广告，使用Meta广告数据和多模态内容分析，典型的计算传播研究。</t>
+          <t>论文先澄清“把广告投给谁”和“为受众改写什么”是两个不同概念，再用德国大选广告检验二者的实际效果。结果显示政党很少同时使用定位和定制，且只有定位显著影响展示次数。这一操作化框架能帮助后续研究避免把两种数据驱动竞选策略混为一谈。</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -2358,7 +2358,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>研究社交媒体平台上的虚假信息检测，涉及平台线索与用户认知，属计算传播领域议题。</t>
+          <t>实验发现参与者有明显的“真实性偏见”，识别真新闻比识别假新闻容易；高可信来源有助于确认真新闻，却可能降低对假新闻的警觉。社会认同线索没有显著作用，而越认为 Twitter 有助于获取信息的人，识别假新闻反而越不准确。它为平台线索如何改变判断提供了直接的因果比较。</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2474,7 +2474,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>使用被动浏览大数据分析恶意网站暴露差异，属计算社会科学与数字不平等议题。</t>
+          <t>文章把数字不平等从接入和技能推进到在线风险暴露。超过一半的参与者在一个月内访问过恶意网站，但暴露高度集中；人口差异在控制浏览强度后明显减弱。这个结果提醒研究者，群体差异可能来自不同的在线活动路径，不能只停在人口属性比较。</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2590,7 +2590,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>使用结构主题建模分析Reddit社区性工作话语，属计算方法和社交媒体议题结合。</t>
+          <t>这篇研究没有把 Reddit 简单描述成污名传播空间。结构主题模型与质性分析共同显示，平台一面延续对性工作者的负面评价，一面又承担互助、减害和实践知识生产的功能。它适合用来讨论数字社群如何同时产生伤害与支持。</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2706,7 +2706,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>研究社交媒体平台X上的极化社区，结合网络分析与文本对齐计算方法，属典型计算传播研究。</t>
+          <t>最值得注意的是，极化社群不仅会在一次危机中持续数周，还会在主题完全不同的新危机中重新出现。少数意见领袖、记者、非主流媒体和活动者通过重新激活熟悉叙事维持群体。这个发现把解释重点从单次事件或单一算法移向反复出现的参与者网络。</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2822,7 +2822,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>使用340万条微博数据和DID方法分析数字平台对企业绿色转型的影响，属于计算传播研究。</t>
+          <t>文章把平台传播与企业的实际绿色行动相连，而不只测量线上声量。结果显示平台曝光与环境投资、披露质量上升相关，原创性、多媒体丰富度和社会影响力会强化这种作用。它提供了一个观察数字平台如何通过政策信号和声誉压力介入组织决策的案例。</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2938,7 +2938,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>使用Telegram多层面数据，结合内容分析、网络分析等计算方法，研究社交媒体抗议运动中的激进意识形态传播，属于计算传播典型议题。</t>
+          <t>这篇论文用内容、来源和关系网络三层证据说明抗议运动如何降低接触激进观点的门槛。Querdenken 的讨论逐渐围绕反精英和阴谋论展开，链接更多替代性、党派性来源，并在网络上靠近极右翼与阴谋论群组。多种分析指向同一过程，使“主流化”不再只是修辞判断。</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -3054,7 +3054,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>使用计算多模态方法分析TikTok大数据，研究身份与沟通风格对公众参与的影响，属计算传播领域。</t>
+          <t>文章在大规模短视频资料中同时处理身份交叉与表达风格。结果显示有色人种女性科学传播者面临更明显的角色冲突，身份与风格符合受众预期时参与度更高。它能帮助解释 TikTok 的注意力分配为何不仅取决于内容质量，也受身份化期待影响。</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -3170,7 +3170,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>结合算法想象、平台数据化，运用Twitter社交网络分析与访谈，属计算传播核心议题。</t>
+          <t>论文把 Spotify Wrapped 看作一年一度的算法事件。网络分析显示它制造的是短暂、松散的共同感，而访谈进一步揭示用户会主动“训练”或规避算法，希望年度画像只记录值得展示的音乐。它把算法想象、身份表演和日常数据实践连到了具体的平台仪式。</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>使用2500万场比赛的个体级大数据分析全球在线互动，涉及数字传播与计算社会科学，方法为大规模数据处理与建模。</t>
+          <t>即使游戏中的互动几乎没有物理运输成本，文化相似性和既有社会联系仍明显影响跨国玩家是否相遇。这个结果用 2,500 万场真实互动说明，数字空间并没有抹平地理和社会边界。它为数字全球化和在线社群研究提供了一个少见的跨国行为数据基准。</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -3402,7 +3402,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>研究社交媒体平台仇恨言论，使用BERTopic等计算方法，涉及计算传播核心议题。</t>
+          <t>这不是只按人工分类汇总的范围综述。BERTopic 与人工编码共同揭示现有研究过度集中于 X、文本内容和检测模型，而视觉、音视频及平台功能受到的关注不足。它既能快速把握仇恨言论研究版图，也清楚指出下一步值得补的经验空白。</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3518,7 +3518,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>使用Reddit评论数据、主题建模等计算方法，分析社交媒体上的种族传播，属典型计算传播研究。</t>
+          <t>文章关注流行文化作品如何触发关于种族历史的公共讨论，并追踪用户在支持、反对和修正立场之间的移动。Reddit 的匿名性既影响意见领袖的形成，也给部分用户改变看法留下空间。计算主题发现与批判性话语分析的组合，让研究能够同时看到总体结构和角色转换。</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3634,7 +3634,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>使用Reddit社区数据和时间序列分析等计算方法，研究政府披露对阴谋论和虚假信息的影响，属典型计算传播研究。</t>
+          <t>研究把 Reddit 讨论与一系列政府披露事件对齐，发现透明度举措能够缓解由阴谋叙事引发的信任危机。它的意义在于不只描述阴谋论内容，而是利用事件时序观察官方信息介入后的变化，也提示“披露”本身带有政治含义，不能被当作单纯的信息增量。</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3750,7 +3750,7 @@
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>采用多模态时间序列分析等计算方法，研究虚假信息媒体帝国的经济激励，议题与方法均属计算传播。</t>
+          <t>这篇文章把虚假信息内容与商业收益直接连在一起。节目中的脏话、音高、音量和特定主题能够预测次日销售，销售变化又会反过来预测后续内容风格。双向关系让“错误信息为何持续生产”从抽象的注意力激励落到可观察的经济反馈。</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3866,7 +3866,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>研究社交媒体中的反 LGBTQIA+ 敌意与旁观者干预，采用预注册 3×3 在线实验；根据本项目对计算相关在线实验的纳入规则，列为明确相关。</t>
+          <t>实验结果对“加一个提示就能改善评论环境”的直觉提出了限制。敌意类型稳定影响情绪、干预意愿和审核偏好，但提示并未提高旁观者干预，有时还增加负面情绪。它为平台助推设计提供了一个重要的无效或反作用案例，也符合本项目纳入在线传播实验的口径。</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3982,7 +3982,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>使用大规模Twitter数据和计算方法研究价值观关键词的跨文化传播，明确属于计算传播领域。</t>
+          <t>文章利用五种语言的大规模推文说明，同一个看似普遍的关键词在不同文化中承担不同功能：欧美语言中更常划分政治群体边界，日语和韩语中则更多调节个人偏好与关系。它把跨文化差异与共同的话语规律放在同一设计中，适合用于讨论计算文本研究如何避免英语中心。</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -4098,7 +4098,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>研究跨平台趋势对公共注意力的影响，使用大规模平台数据与计量模型，属于计算传播学核心议题。</t>
+          <t>文章挑战了“一个平台上榜会带动其他平台同步升温”的直觉。在部分政治议题上，其他平台的热榜反而压低微博对同一新闻的注意力。这个负向溢出结果把跨平台关系从简单协同改写为注意力竞争，也为研究平台生态提供了可检验的框架。</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -4214,7 +4214,7 @@
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>研究AI预训练语言模型中的社会偏见，使用计算方法（FMAT），属于计算传播议题。</t>
+          <t>研究发现中文模型在性别评价上表现出更强的男性偏好，中英文模型都偏向高地位职业和年轻群体，其中地位偏差最稳定。它把语言模型中的社会不平等落到可重复的关联测试上，也提醒教育、招聘和内容审核中的模型应用可能复制既有等级。</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -4330,7 +4330,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>研究Reddit平台政治极化，使用16年跨子版块多指标重叠网络分析，属计算传播学。</t>
+          <t>文章同时检查六类跨版块重叠，发现即便话语内容相近，政治子版块之间的用户、链接和互动交叉仍非常有限。这个长时段结果说明 Reddit 极化不能只归因于内容、身份或平台设计中的单一因素，也直接挑战了把 r/politics 想象成跨立场公共广场的说法。</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -4450,7 +4450,7 @@
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>研究在线政治广告的个性化感知，并结合移动经验抽样与真实广告截图数据捐赠；议题明确属于数字政治传播，但计算分析的中心性较弱，因此列为中等相关。</t>
+          <t>研究的亮点是把真实收到的政治广告与受众当下的主观评价配对。美国和德国样本都显示，党派一致会增强“这是为我定制的”感受，而这种感受又带来更积极的广告评价。它对理解个性化广告的心理过程很有价值；不过核心分析仍以经验抽样、数据捐赠和一般统计为主，因此在本目录中列为中等相关。</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4570,7 +4570,7 @@
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>研究平台化游戏中的数字劳动，使用 Discord 大规模数据、R 清洗和正则识别，但核心解释仍依赖抽样后的主题分析，因此列为中等相关。</t>
+          <t>论文提出“自我资产化”来解释玩家如何把经济困境、忠诚和自我剥削包装成可投资价值。这个概念对理解平台化游戏劳动很有启发，但计算工具主要用于整理和抽样 Discord 材料，核心发现来自质性主题分析，所以更适合作为计算传播的边界案例。</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4694,7 +4694,7 @@
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>使用数据驱动文本分析框架研究社交媒体政治推文的隐喻效果，属计算传播范畴。</t>
+          <t>结果区分了隐喻“用得多”和“用得新”两种效果：频率只带来约 1%—2% 的参与增长，原创性则使点赞和转发提高约 6%—7%，对回复的影响较弱。它为政治语言如何影响平台参与提供了量化证据；但摘要没有清楚说明隐喻识别是否自动化，因此列为中等相关。</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4814,7 +4814,7 @@
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>使用大规模专利数据与计算文本聚类分析AI云基础设施的社会技术想象，属计算传播学。</t>
+          <t>文章从大规模专利中识别车辆通信、机器视觉、网络架构和边缘计算四个主题，借此说明云不只是后台设施，也承载了 AI 规模化的产业想象。计算文本部分扎实，但研究对象更接近基础设施与创新研究，和传播过程的联系较间接，因此作为中等相关论文保留。</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -5306,7 +5306,7 @@
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>以主题模型与文本社群检测分析欧盟委员会虚假信息话语，议题与方法均属计算传播。</t>
+          <t>值得关注的地方在于，论文没有把“虚假信息”当作现成标签，而是把政策机构如何定义问题本身变成研究对象。计算分析显示，欧盟委员会长期借助战争和传染病隐喻，将责任推向敌对国家、平台和易受骗的公民；到 2023—2024 年，AI 又被纳入放大风险的叙事。它适合用于讨论问题框架如何预先限定平台治理、内容清除和媒介素养等政策答案。</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
@@ -5766,7 +5766,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>使用Meta广告库API采集选举广告数据，分析政党在社交平台的定向策略，属计算传播研究。</t>
+          <t>这篇文章把政治传播研究中常被忽略的付费广告置于中心，并同时观察广告说了什么、花了多少钱、投给了谁。结果显示瑞典左右翼政党在负面竞选和人口定向上采取不同策略，也说明平台的付费功能并非中性的传播通道，而会进入政党的受众选择与资源配置。</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -5886,7 +5886,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>使用Facebook数字追踪数据与调查对比，分析政治活动测量的准确性，属社交媒体与计算方法结合。</t>
+          <t>这是一篇很有用的方法校准研究。它直接拿问卷回答与同一人的 Facebook 行为记录比较，发现用户往往低估一般使用、又高估政治参与，而且题目从总体到具体的排列更可靠。对依赖自报社交媒体行为的研究来说，这些结果能具体说明测量误差会出现在哪里，也展示了数据捐赠怎样用于验证传统问卷。</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -6354,7 +6354,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>使用大规模X数据、LLM分类、网络分析与图机器学习，属于典型计算方法研究传播议题。</t>
+          <t>论文把立场识别、不文明语言测量和互动网络连在一起，研究的不只是“哪一方更不文明”，而是不文明表达怎样沿着提及关系扩散并跨越意识形态边界。它为冲突螺旋理论提供了可追踪的动态证据，也适合作为大型语言模型与网络分析组合使用的案例。</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -7702,7 +7702,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>研究在线政治广告的个性化感知，并结合移动经验抽样与真实广告截图数据捐赠；议题明确属于数字政治传播，但计算分析的中心性较弱，因此列为中等相关。</t>
+          <t>研究的亮点是把真实收到的政治广告与受众当下的主观评价配对。美国和德国样本都显示，党派一致会增强“这是为我定制的”感受，而这种感受又带来更积极的广告评价。它对理解个性化广告的心理过程很有价值；不过核心分析仍以经验抽样、数据捐赠和一般统计为主，因此在本目录中列为中等相关。</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -8066,7 +8066,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>使用基于代理的模拟方法研究社交媒体过滤气泡与网络结构对回音室的影响，属计算传播核心议题。</t>
+          <t>这篇文章适合用来检验一个经常被过度简化的判断：过滤算法是否会自动制造并固化回音室。模型把网络同质性与选择性暴露分开操控，结果显示信息暴露确实会影响回音室的形成，但人为形成的回音室即使处在过滤算法下也未必长期维持。它的价值在于把“算法—网络结构—意见变化”拆成可重复检验的条件；作者还在 OSF 公开了模型、输入和输出数据。</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -9246,7 +9246,7 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>使用LLM分类、时间序列分析和回归建模，分析Facebook党派网络的纵向情感参与，属典型计算传播研究。</t>
+          <t>文章用三年纵向数据挑战了“高度党派化社群始终按固定方式运作”的想象。卢拉就职和 2023 年 1 月事件之后，这些亲博索纳罗社群的情绪强度下降、内部讨论增加，说明政治事件会重新组织看似封闭的回音室。两个行为指标也为长期比较情感反应与互动方式提供了可复用的测量思路。</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
@@ -9490,7 +9490,7 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>使用词嵌入分析社交媒体评论，研究在线性别辩论中的道德框架，属计算传播典型议题。</t>
+          <t>它把“如何称呼事件中的人”与“如何对他们作道德判断”放进同一计算框架。研究发现，性别化称谓更容易连接广泛而两极化的道德基础，性别中立称谓则更偏向程序和角色评价。这种设计能把网络性别争论中的道德边界从抽象概念转成可比较的语义关系。</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
@@ -10094,7 +10094,7 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>使用主题建模和情感分析等计算方法，研究AI媒体框架与政治传播议题，属计算传播。</t>
+          <t>文章兼有长时段、跨地区与可比较的媒体样本，能看到 AI 报道从技术想象走向政治化的过程。剑桥分析事件和 ChatGPT 发布构成两个转折点，全球北方媒体整体更悲观、南方媒体更乐观。它提供了一幅地缘政治、风险认知与 AI 媒体框架相互作用的经验地图。</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
@@ -10818,7 +10818,7 @@
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>研究生成式AI在选举中的信息准确性与治理影响，采用混合方法审计ChatGPT输出，主题和方法均属计算传播。</t>
+          <t>这篇文章的贡献不只在于列出 ChatGPT 的错误，而是提出“生成性治理”这一观察角度：平台已经从筛选人类内容转向直接生产用户看到的政治信息。选举期间出现的不准确、遗漏和回避性回答因此被放进平台权力与问责问题中考察，很适合作为生成式 AI 政治传播审计的案例。</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
@@ -11542,7 +11542,7 @@
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>使用Facebook数据构建双模网络，分析社交媒体平台上的隐性关系结构，属于计算传播研究。</t>
+          <t>论文抓住了平台界面中一种容易被忽略的关系：品牌帖文背后的合作伙伴与发布页面如何结成战略网络。四个二部网络让这些近乎不可见的合作变得可观察，也揭示新闻媒体等传统机构在平台盈利逻辑下如何重新安排角色。它对研究平台化传播中的组织关系很有启发。</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
@@ -11786,7 +11786,7 @@
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>使用微博大规模数据和多模态框架分析，探讨性别对抗话语的传播机制，属典型计算传播研究。</t>
+          <t>文章把帖文的文字与视觉框架、发布者身份和评论反应放进同一模型。结果显示，煽动性和个性化框架会加剧性别对立，外群体身份发布时更明显，而娱乐性框架反而减弱对立。它把“性别冲突为什么会病毒式扩散”落实到了可检验的内容形式与身份线索上。</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
@@ -13414,7 +13414,7 @@
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>研究 Reddit 上肥胖管理药物的消费者叙事，使用 Python 抓取、Top2Vec 与 LLM 辅助主题整理，议题与计算文本方法均符合本项目口径。</t>
+          <t>这篇文章呈现了肥胖管理药物讨论中并存的四组张力：污名、获取不平等、品牌与错误信息混淆，以及对疗效和风险的怀疑。它的价值在于把主题发现与网络社群中的意义协商结合起来，既保留大规模文本的轮廓，也没有把健康传播简化成词频排名。</t>
         </is>
       </c>
       <c r="I71" s="2" t="inlineStr">
@@ -13534,7 +13534,7 @@
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>研究政治社交媒体广告，使用Meta广告数据和多模态内容分析，典型的计算传播研究。</t>
+          <t>论文先澄清“把广告投给谁”和“为受众改写什么”是两个不同概念，再用德国大选广告检验二者的实际效果。结果显示政党很少同时使用定位和定制，且只有定位显著影响展示次数。这一操作化框架能帮助后续研究避免把两种数据驱动竞选策略混为一谈。</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr">
@@ -13658,7 +13658,7 @@
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>研究社交媒体平台上的虚假信息检测，涉及平台线索与用户认知，属计算传播领域议题。</t>
+          <t>实验发现参与者有明显的“真实性偏见”，识别真新闻比识别假新闻容易；高可信来源有助于确认真新闻，却可能降低对假新闻的警觉。社会认同线索没有显著作用，而越认为 Twitter 有助于获取信息的人，识别假新闻反而越不准确。它为平台线索如何改变判断提供了直接的因果比较。</t>
         </is>
       </c>
       <c r="I73" s="2" t="inlineStr">
@@ -14146,7 +14146,7 @@
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>研究平台化游戏中的数字劳动，使用 Discord 大规模数据、R 清洗和正则识别，但核心解释仍依赖抽样后的主题分析，因此列为中等相关。</t>
+          <t>论文提出“自我资产化”来解释玩家如何把经济困境、忠诚和自我剥削包装成可投资价值。这个概念对理解平台化游戏劳动很有启发，但计算工具主要用于整理和抽样 Discord 材料，核心发现来自质性主题分析，所以更适合作为计算传播的边界案例。</t>
         </is>
       </c>
       <c r="I77" s="2" t="inlineStr">
@@ -14274,7 +14274,7 @@
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>使用被动浏览大数据分析恶意网站暴露差异，属计算社会科学与数字不平等议题。</t>
+          <t>文章把数字不平等从接入和技能推进到在线风险暴露。超过一半的参与者在一个月内访问过恶意网站，但暴露高度集中；人口差异在控制浏览强度后明显减弱。这个结果提醒研究者，群体差异可能来自不同的在线活动路径，不能只停在人口属性比较。</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr">
@@ -14750,7 +14750,7 @@
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>使用结构主题建模分析Reddit社区性工作话语，属计算方法和社交媒体议题结合。</t>
+          <t>这篇研究没有把 Reddit 简单描述成污名传播空间。结构主题模型与质性分析共同显示，平台一面延续对性工作者的负面评价，一面又承担互助、减害和实践知识生产的功能。它适合用来讨论数字社群如何同时产生伤害与支持。</t>
         </is>
       </c>
       <c r="I82" s="2" t="inlineStr">
@@ -14994,7 +14994,7 @@
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>研究社交媒体平台X上的极化社区，结合网络分析与文本对齐计算方法，属典型计算传播研究。</t>
+          <t>最值得注意的是，极化社群不仅会在一次危机中持续数周，还会在主题完全不同的新危机中重新出现。少数意见领袖、记者、非主流媒体和活动者通过重新激活熟悉叙事维持群体。这个发现把解释重点从单次事件或单一算法移向反复出现的参与者网络。</t>
         </is>
       </c>
       <c r="I84" s="2" t="inlineStr">
@@ -15246,7 +15246,7 @@
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>使用340万条微博数据和DID方法分析数字平台对企业绿色转型的影响，属于计算传播研究。</t>
+          <t>文章把平台传播与企业的实际绿色行动相连，而不只测量线上声量。结果显示平台曝光与环境投资、披露质量上升相关，原创性、多媒体丰富度和社会影响力会强化这种作用。它提供了一个观察数字平台如何通过政策信号和声誉压力介入组织决策的案例。</t>
         </is>
       </c>
       <c r="I86" s="2" t="inlineStr">
@@ -15618,7 +15618,7 @@
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
-          <t>使用Telegram多层面数据，结合内容分析、网络分析等计算方法，研究社交媒体抗议运动中的激进意识形态传播，属于计算传播典型议题。</t>
+          <t>这篇论文用内容、来源和关系网络三层证据说明抗议运动如何降低接触激进观点的门槛。Querdenken 的讨论逐渐围绕反精英和阴谋论展开，链接更多替代性、党派性来源，并在网络上靠近极右翼与阴谋论群组。多种分析指向同一过程，使“主流化”不再只是修辞判断。</t>
         </is>
       </c>
       <c r="I89" s="2" t="inlineStr">
@@ -15742,7 +15742,7 @@
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t>使用计算多模态方法分析TikTok大数据，研究身份与沟通风格对公众参与的影响，属计算传播领域。</t>
+          <t>文章在大规模短视频资料中同时处理身份交叉与表达风格。结果显示有色人种女性科学传播者面临更明显的角色冲突，身份与风格符合受众预期时参与度更高。它能帮助解释 TikTok 的注意力分配为何不仅取决于内容质量，也受身份化期待影响。</t>
         </is>
       </c>
       <c r="I90" s="2" t="inlineStr">
@@ -15986,7 +15986,7 @@
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
-          <t>结合算法想象、平台数据化，运用Twitter社交网络分析与访谈，属计算传播核心议题。</t>
+          <t>论文把 Spotify Wrapped 看作一年一度的算法事件。网络分析显示它制造的是短暂、松散的共同感，而访谈进一步揭示用户会主动“训练”或规避算法，希望年度画像只记录值得展示的音乐。它把算法想象、身份表演和日常数据实践连到了具体的平台仪式。</t>
         </is>
       </c>
       <c r="I92" s="2" t="inlineStr">
@@ -16230,7 +16230,7 @@
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
-          <t>使用2500万场比赛的个体级大数据分析全球在线互动，涉及数字传播与计算社会科学，方法为大规模数据处理与建模。</t>
+          <t>即使游戏中的互动几乎没有物理运输成本，文化相似性和既有社会联系仍明显影响跨国玩家是否相遇。这个结果用 2,500 万场真实互动说明，数字空间并没有抹平地理和社会边界。它为数字全球化和在线社群研究提供了一个少见的跨国行为数据基准。</t>
         </is>
       </c>
       <c r="I94" s="2" t="inlineStr">
@@ -16594,7 +16594,7 @@
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
-          <t>研究社交媒体平台仇恨言论，使用BERTopic等计算方法，涉及计算传播核心议题。</t>
+          <t>这不是只按人工分类汇总的范围综述。BERTopic 与人工编码共同揭示现有研究过度集中于 X、文本内容和检测模型，而视觉、音视频及平台功能受到的关注不足。它既能快速把握仇恨言论研究版图，也清楚指出下一步值得补的经验空白。</t>
         </is>
       </c>
       <c r="I97" s="2" t="inlineStr">
@@ -16958,7 +16958,7 @@
       </c>
       <c r="H100" s="2" t="inlineStr">
         <is>
-          <t>使用Reddit评论数据、主题建模等计算方法，分析社交媒体上的种族传播，属典型计算传播研究。</t>
+          <t>文章关注流行文化作品如何触发关于种族历史的公共讨论，并追踪用户在支持、反对和修正立场之间的移动。Reddit 的匿名性既影响意见领袖的形成，也给部分用户改变看法留下空间。计算主题发现与批判性话语分析的组合，让研究能够同时看到总体结构和角色转换。</t>
         </is>
       </c>
       <c r="I100" s="2" t="inlineStr">
@@ -18162,7 +18162,7 @@
       </c>
       <c r="H110" s="2" t="inlineStr">
         <is>
-          <t>使用Reddit社区数据和时间序列分析等计算方法，研究政府披露对阴谋论和虚假信息的影响，属典型计算传播研究。</t>
+          <t>研究把 Reddit 讨论与一系列政府披露事件对齐，发现透明度举措能够缓解由阴谋叙事引发的信任危机。它的意义在于不只描述阴谋论内容，而是利用事件时序观察官方信息介入后的变化，也提示“披露”本身带有政治含义，不能被当作单纯的信息增量。</t>
         </is>
       </c>
       <c r="I110" s="2" t="inlineStr">
@@ -19126,7 +19126,7 @@
       </c>
       <c r="H118" s="2" t="inlineStr">
         <is>
-          <t>采用多模态时间序列分析等计算方法，研究虚假信息媒体帝国的经济激励，议题与方法均属计算传播。</t>
+          <t>这篇文章把虚假信息内容与商业收益直接连在一起。节目中的脏话、音高、音量和特定主题能够预测次日销售，销售变化又会反过来预测后续内容风格。双向关系让“错误信息为何持续生产”从抽象的注意力激励落到可观察的经济反馈。</t>
         </is>
       </c>
       <c r="I118" s="2" t="inlineStr">
@@ -19622,7 +19622,7 @@
       </c>
       <c r="H122" s="2" t="inlineStr">
         <is>
-          <t>使用数据驱动文本分析框架研究社交媒体政治推文的隐喻效果，属计算传播范畴。</t>
+          <t>结果区分了隐喻“用得多”和“用得新”两种效果：频率只带来约 1%—2% 的参与增长，原创性则使点赞和转发提高约 6%—7%，对回复的影响较弱。它为政治语言如何影响平台参与提供了量化证据；但摘要没有清楚说明隐喻识别是否自动化，因此列为中等相关。</t>
         </is>
       </c>
       <c r="I122" s="2" t="inlineStr">
@@ -20466,7 +20466,7 @@
       </c>
       <c r="H129" s="2" t="inlineStr">
         <is>
-          <t>研究社交媒体中的反 LGBTQIA+ 敌意与旁观者干预，采用预注册 3×3 在线实验；根据本项目对计算相关在线实验的纳入规则，列为明确相关。</t>
+          <t>实验结果对“加一个提示就能改善评论环境”的直觉提出了限制。敌意类型稳定影响情绪、干预意愿和审核偏好，但提示并未提高旁观者干预，有时还增加负面情绪。它为平台助推设计提供了一个重要的无效或反作用案例，也符合本项目纳入在线传播实验的口径。</t>
         </is>
       </c>
       <c r="I129" s="2" t="inlineStr">
@@ -20590,7 +20590,7 @@
       </c>
       <c r="H130" s="2" t="inlineStr">
         <is>
-          <t>使用大规模Twitter数据和计算方法研究价值观关键词的跨文化传播，明确属于计算传播领域。</t>
+          <t>文章利用五种语言的大规模推文说明，同一个看似普遍的关键词在不同文化中承担不同功能：欧美语言中更常划分政治群体边界，日语和韩语中则更多调节个人偏好与关系。它把跨文化差异与共同的话语规律放在同一设计中，适合用于讨论计算文本研究如何避免英语中心。</t>
         </is>
       </c>
       <c r="I130" s="2" t="inlineStr">
@@ -20962,7 +20962,7 @@
       </c>
       <c r="H133" s="2" t="inlineStr">
         <is>
-          <t>研究跨平台趋势对公共注意力的影响，使用大规模平台数据与计量模型，属于计算传播学核心议题。</t>
+          <t>文章挑战了“一个平台上榜会带动其他平台同步升温”的直觉。在部分政治议题上，其他平台的热榜反而压低微博对同一新闻的注意力。这个负向溢出结果把跨平台关系从简单协同改写为注意力竞争，也为研究平台生态提供了可检验的框架。</t>
         </is>
       </c>
       <c r="I133" s="2" t="inlineStr">
@@ -21450,7 +21450,7 @@
       </c>
       <c r="H137" s="2" t="inlineStr">
         <is>
-          <t>使用大规模专利数据与计算文本聚类分析AI云基础设施的社会技术想象，属计算传播学。</t>
+          <t>文章从大规模专利中识别车辆通信、机器视觉、网络架构和边缘计算四个主题，借此说明云不只是后台设施，也承载了 AI 规模化的产业想象。计算文本部分扎实，但研究对象更接近基础设施与创新研究，和传播过程的联系较间接，因此作为中等相关论文保留。</t>
         </is>
       </c>
       <c r="I137" s="2" t="inlineStr">
@@ -21934,7 +21934,7 @@
       </c>
       <c r="H141" s="2" t="inlineStr">
         <is>
-          <t>研究AI预训练语言模型中的社会偏见，使用计算方法（FMAT），属于计算传播议题。</t>
+          <t>研究发现中文模型在性别评价上表现出更强的男性偏好，中英文模型都偏向高地位职业和年轻群体，其中地位偏差最稳定。它把语言模型中的社会不平等落到可重复的关联测试上，也提醒教育、招聘和内容审核中的模型应用可能复制既有等级。</t>
         </is>
       </c>
       <c r="I141" s="2" t="inlineStr">
@@ -22058,7 +22058,7 @@
       </c>
       <c r="H142" s="2" t="inlineStr">
         <is>
-          <t>研究Reddit平台政治极化，使用16年跨子版块多指标重叠网络分析，属计算传播学。</t>
+          <t>文章同时检查六类跨版块重叠，发现即便话语内容相近，政治子版块之间的用户、链接和互动交叉仍非常有限。这个长时段结果说明 Reddit 极化不能只归因于内容、身份或平台设计中的单一因素，也直接挑战了把 r/politics 想象成跨立场公共广场的说法。</t>
         </is>
       </c>
       <c r="I142" s="2" t="inlineStr">

--- a/outputs/ICS-2026-计算传播学精选.xlsx
+++ b/outputs/ICS-2026-计算传播学精选.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="筛选说明" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="明确纳入" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="待全文确认" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="完整筛选记录" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="筛选说明" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="明确纳入" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="待全文确认" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="完整筛选记录" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'明确纳入'!$A$1:$Z$36</definedName>
@@ -7940,12 +7940,12 @@
       <c r="E21" s="2" t="inlineStr"/>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>摘要明确或原表方法明确</t>
+          <t>出版方全文方法明确</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>摘要未显示计算方法或与计算传播相关的在线实验。</t>
+          <t>全文显示为荷兰代表性样本的预注册横截面在线问卷（n=2,196），使用 EFA、CFA、SEM 和调节分析；没有计算传播方法或实验操控。</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr"/>
@@ -8302,12 +8302,12 @@
       <c r="E24" s="2" t="inlineStr"/>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>摘要明确或原表方法明确</t>
+          <t>出版方全文方法明确</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>访谈、民族志、批判分析或其他质性方法；未使用计算方法。</t>
+          <t>全文以 Kiwi Farms 的公开帖文、平台文件与新闻材料重建平台迁移过程，采用质性案例分析；没有计算分析。</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr"/>
@@ -8424,12 +8424,12 @@
       <c r="E25" s="2" t="inlineStr"/>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>摘要明确或原表方法明确</t>
+          <t>出版方全文方法明确</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>传统调查、面板或一般统计分析；摘要未显示计算方法或明确的在线实验。</t>
+          <t>全文显示为 Prolific 横截面在线问卷（n=375）与 PLS-SEM；没有实验操控或计算传播方法。</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr"/>
@@ -9160,12 +9160,12 @@
       <c r="E31" s="2" t="inlineStr"/>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>摘要明确或原表方法明确</t>
+          <t>出版方全文方法明确</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>传统调查、面板或一般统计分析；摘要未显示计算方法或明确的在线实验。</t>
+          <t>全文显示为瑞典四波面板问卷（n=3,530），使用 RI-CLPM 与 LGCM；属于传统纵向调查分析。</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr"/>
@@ -12876,12 +12876,12 @@
       <c r="E61" s="2" t="inlineStr"/>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>摘要明确或原表方法明确</t>
+          <t>出版方全文方法明确</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>传统调查、面板或一般统计分析；摘要未显示计算方法或明确的在线实验。</t>
+          <t>全文显示为两次相互关联的在线调查；第二次核验任务由人工按量规评分，分析使用 t 检验、相关和 OLS，不是随机实验。</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr"/>
@@ -12998,12 +12998,12 @@
       <c r="E62" s="2" t="inlineStr"/>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>摘要明确或原表方法明确</t>
+          <t>出版方全文方法明确</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>摘要未显示计算方法或与计算传播相关的在线实验。</t>
+          <t>出版方页面标明该文为书评，不是经验研究论文。</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr"/>
@@ -16108,12 +16108,12 @@
       <c r="E87" s="2" t="inlineStr"/>
       <c r="F87" s="2" t="inlineStr">
         <is>
-          <t>摘要明确或原表方法明确</t>
+          <t>出版方全文方法明确</t>
         </is>
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>摘要未显示计算方法或与计算传播相关的在线实验。</t>
+          <t>全文虽查询 Stack Exchange Data Dumps，但只用查询取得讨论串，核心材料缩减为 22 个线程并作溯因式质性分析；没有计算分析。</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr"/>
@@ -17632,12 +17632,12 @@
       <c r="E99" s="2" t="inlineStr"/>
       <c r="F99" s="2" t="inlineStr">
         <is>
-          <t>摘要明确或原表方法明确</t>
+          <t>出版方全文方法明确</t>
         </is>
       </c>
       <c r="G99" s="2" t="inlineStr">
         <is>
-          <t>访谈、民族志、批判分析或其他质性方法；未使用计算方法。</t>
+          <t>全文使用 Wakoopa 数字踪迹制作个体访谈提示材料，核心证据来自 73 次访谈及反思式主题分析；踪迹没有进入计算建模。</t>
         </is>
       </c>
       <c r="H99" s="2" t="inlineStr"/>
@@ -19242,12 +19242,12 @@
       <c r="E112" s="2" t="inlineStr"/>
       <c r="F112" s="2" t="inlineStr">
         <is>
-          <t>摘要明确或原表方法明确</t>
+          <t>出版方全文方法明确</t>
         </is>
       </c>
       <c r="G112" s="2" t="inlineStr">
         <is>
-          <t>理论、概念或政策讨论；没有计算性经验方法。</t>
+          <t>全文先人工核验 407 个短视频，再选取 22 个视频进行人工多模态编码和质性解释；没有自动化或计算多模态分析。</t>
         </is>
       </c>
       <c r="H112" s="2" t="inlineStr"/>
@@ -20116,12 +20116,12 @@
       <c r="E119" s="2" t="inlineStr"/>
       <c r="F119" s="2" t="inlineStr">
         <is>
-          <t>摘要明确或原表方法明确</t>
+          <t>出版方全文方法明确</t>
         </is>
       </c>
       <c r="G119" s="2" t="inlineStr">
         <is>
-          <t>传统调查、面板或一般统计分析；摘要未显示计算方法或明确的在线实验。</t>
+          <t>全文为全国在线问卷（n=2,373），向受访者展示带标签的既有图片并询问是否见过；只随机了题项顺序，没有随机处理条件。</t>
         </is>
       </c>
       <c r="H119" s="2" t="inlineStr"/>
@@ -24502,12 +24502,12 @@
       <c r="E154" s="2" t="inlineStr"/>
       <c r="F154" s="2" t="inlineStr">
         <is>
-          <t>摘要明确或原表方法明确</t>
+          <t>出版方全文方法明确</t>
         </is>
       </c>
       <c r="G154" s="2" t="inlineStr">
         <is>
-          <t>传统调查、面板或一般统计分析；摘要未显示计算方法或明确的在线实验。</t>
+          <t>全文确认为 2×4 随机组间在线情境实验；但研究涉及 AI 生成性影像虐待及色情网站情境，按用户本轮主题选择不收录。</t>
         </is>
       </c>
       <c r="H154" s="2" t="inlineStr"/>
